--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Documents\로컬라이징\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\stopresent\Unity\RE001\Assets\@Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70AA30F7-95EA-43F8-B83F-E15B8B62E437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D82F86-5DBC-4A08-B18A-7A9DFC32E758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="937" activeTab="5" xr2:uid="{91B0F9F1-9572-42A8-B1AA-AE512853DD32}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="937" xr2:uid="{91B0F9F1-9572-42A8-B1AA-AE512853DD32}"/>
   </bookViews>
   <sheets>
     <sheet name="GlobalButtons" sheetId="36" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="343">
   <si>
     <t>Kor</t>
   </si>
@@ -1358,6 +1358,21 @@
   </si>
   <si>
     <t>공세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TestKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>This is Test.This is Test.This is Test.This is Test.This is Test.This is Test.This is Test.This is Test.This is Test.This is Test.This is Test.This is Test.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[&lt;#2DFF00&gt;&lt;b&gt;여정&lt;/b&gt;&lt;/color&gt;]이 해금되었습니다.
+&lt;size=10&gt;이제 소유한 통행증의 허가 범위 내 
+알게 된 모든 장소들로 자유로운 
+이동이 가능해 졌습니다.&lt;/size&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1365,7 +1380,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1417,7 +1432,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1428,6 +1443,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1744,13 +1762,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97AFE29F-27AA-4C15-8BF4-4F0A52E1C497}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -1761,7 +1779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>256</v>
       </c>
@@ -1772,7 +1790,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>257</v>
       </c>
@@ -1783,7 +1801,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>258</v>
       </c>
@@ -1792,6 +1810,17 @@
       </c>
       <c r="C4" t="s">
         <v>260</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A5" t="s">
+        <v>340</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C5" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -1803,12 +1832,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0915254-3021-4CCF-A608-F4ABAF521607}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="25.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -1837,7 +1866,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -1845,7 +1874,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -1856,7 +1885,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -1873,12 +1902,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{694D12D2-CCB5-4FDE-80B5-17DEE59D4C15}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -1907,7 +1936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -1915,7 +1944,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1932,9 +1961,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED4F5044-6FD2-4B5F-9619-812F92439F15}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -1963,7 +1992,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>216</v>
       </c>
@@ -1971,7 +2000,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>217</v>
       </c>
@@ -1979,7 +2008,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>219</v>
       </c>
@@ -1996,12 +2025,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3D6C88-7DA2-4E50-B1BB-1CF8BEA208F7}">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="24.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2030,7 +2059,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -2038,7 +2067,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -2046,7 +2075,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>56</v>
       </c>
@@ -2054,7 +2083,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>52</v>
       </c>
@@ -2062,7 +2091,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -2085,9 +2114,9 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2116,7 +2145,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2127,7 +2156,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>222</v>
       </c>
@@ -2147,12 +2176,12 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4642966-F9C7-436F-B32B-713FDF338185}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2181,7 +2210,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -2210,7 +2239,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -2218,7 +2247,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -2235,12 +2264,12 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F28F60-DED8-41AD-B96B-123DAA0F391E}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="27.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2269,7 +2298,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2277,7 +2306,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
@@ -2294,9 +2323,9 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88D0DBF0-942D-4EE6-B362-E4CF41BCFA04}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2325,7 +2354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -2333,7 +2362,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -2341,7 +2370,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -2379,12 +2408,12 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E08D396-C0E1-475A-B880-DAAC444925C0}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2413,7 +2442,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -2421,7 +2450,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -2429,7 +2458,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>69</v>
       </c>
@@ -2467,12 +2496,12 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E674144E-C543-458F-876A-050424890EDF}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2501,7 +2530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>77</v>
       </c>
@@ -2509,7 +2538,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>78</v>
       </c>
@@ -2520,7 +2549,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>79</v>
       </c>
@@ -2540,12 +2569,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{174938F3-68B5-4AC4-B525-4822846F33FD}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="22.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2556,7 +2585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>235</v>
       </c>
@@ -2567,7 +2596,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>236</v>
       </c>
@@ -2578,7 +2607,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>237</v>
       </c>
@@ -2589,7 +2618,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>238</v>
       </c>
@@ -2600,7 +2629,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>239</v>
       </c>
@@ -2611,7 +2640,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>240</v>
       </c>
@@ -2631,12 +2660,12 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B4ADE3C-C1AD-44A5-9E28-96B2DAB7DF23}">
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="24.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2665,7 +2694,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -2673,7 +2702,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -2684,7 +2713,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>87</v>
       </c>
@@ -2692,7 +2721,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>88</v>
       </c>
@@ -2709,12 +2738,12 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27D3AF6E-37B8-45B5-9E5E-2724ED345A17}">
   <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="70.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2743,7 +2772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>95</v>
       </c>
@@ -2751,7 +2780,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -2759,7 +2788,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -2767,7 +2796,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>100</v>
       </c>
@@ -2775,7 +2804,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>102</v>
       </c>
@@ -2783,7 +2812,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>226</v>
       </c>
@@ -2791,7 +2820,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>104</v>
       </c>
@@ -2799,7 +2828,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>106</v>
       </c>
@@ -2807,7 +2836,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>108</v>
       </c>
@@ -2815,7 +2844,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -2823,7 +2852,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
         <v>112</v>
       </c>
@@ -2831,7 +2860,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
         <v>114</v>
       </c>
@@ -2839,7 +2868,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
         <v>116</v>
       </c>
@@ -2847,7 +2876,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>118</v>
       </c>
@@ -2855,7 +2884,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A16" t="s">
         <v>119</v>
       </c>
@@ -2863,7 +2892,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -2871,7 +2900,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A18" t="s">
         <v>123</v>
       </c>
@@ -2879,7 +2908,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A19" t="s">
         <v>125</v>
       </c>
@@ -2887,7 +2916,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A20" t="s">
         <v>127</v>
       </c>
@@ -2895,7 +2924,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A21" t="s">
         <v>129</v>
       </c>
@@ -2903,7 +2932,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A22" t="s">
         <v>131</v>
       </c>
@@ -2911,7 +2940,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A23" t="s">
         <v>133</v>
       </c>
@@ -2919,7 +2948,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.6">
       <c r="A24" t="s">
         <v>135</v>
       </c>
@@ -2936,12 +2965,12 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A639FE92-3E64-4FF3-B22D-5D39EE7D8D10}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="23.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2970,7 +2999,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>137</v>
       </c>
@@ -2987,12 +3016,12 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4AED28B-1BCD-48C1-A341-4CEFB97992EE}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="24.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3021,7 +3050,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -3029,7 +3058,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>140</v>
       </c>
@@ -3046,9 +3075,9 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE2575BD-013B-45C1-8DA5-B0D296FBDE26}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3077,7 +3106,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>142</v>
       </c>
@@ -3085,7 +3114,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -3102,12 +3131,12 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E45B1690-222D-4E4F-A5C1-8930ED660C34}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3136,7 +3165,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>145</v>
       </c>
@@ -3144,7 +3173,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>146</v>
       </c>
@@ -3161,12 +3190,12 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58DE56D8-C5BA-4BA7-9F53-4DFEA032378E}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="24.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3195,7 +3224,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -3203,7 +3232,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>139</v>
       </c>
@@ -3211,7 +3240,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>148</v>
       </c>
@@ -3219,7 +3248,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>149</v>
       </c>
@@ -3227,7 +3256,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>150</v>
       </c>
@@ -3235,7 +3264,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -3252,12 +3281,12 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34ACF0F8-F03D-4F0E-A5B2-F899C228B6FB}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="19.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3286,7 +3315,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -3294,7 +3323,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>157</v>
       </c>
@@ -3302,7 +3331,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>158</v>
       </c>
@@ -3310,7 +3339,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>159</v>
       </c>
@@ -3318,7 +3347,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>160</v>
       </c>
@@ -3326,7 +3355,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>161</v>
       </c>
@@ -3343,12 +3372,12 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29F390A-367B-47A8-8D73-A14F68B82ED0}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="32" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -3377,7 +3406,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -3385,7 +3414,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>173</v>
       </c>
@@ -3393,7 +3422,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" s="1" t="s">
         <v>174</v>
       </c>
@@ -3401,7 +3430,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" s="1" t="s">
         <v>175</v>
       </c>
@@ -3409,7 +3438,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" s="1" t="s">
         <v>176</v>
       </c>
@@ -3417,7 +3446,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A7" s="1" t="s">
         <v>177</v>
       </c>
@@ -3425,7 +3454,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A8" s="1" t="s">
         <v>178</v>
       </c>
@@ -3433,7 +3462,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A9" s="1" t="s">
         <v>179</v>
       </c>
@@ -3450,12 +3479,12 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA8004A0-75CF-4997-BF7C-E3207CA522D5}">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="26.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3484,7 +3513,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -3492,7 +3521,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>180</v>
       </c>
@@ -3500,7 +3529,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>156</v>
       </c>
@@ -3508,7 +3537,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>157</v>
       </c>
@@ -3516,7 +3545,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>158</v>
       </c>
@@ -3533,14 +3562,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8B94602-974E-49C2-8A82-9FC5BAA9CF98}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3551,7 +3580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>252</v>
       </c>
@@ -3562,7 +3591,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>269</v>
       </c>
@@ -3573,7 +3602,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>253</v>
       </c>
@@ -3584,7 +3613,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>274</v>
       </c>
@@ -3595,7 +3624,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>254</v>
       </c>
@@ -3606,7 +3635,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>275</v>
       </c>
@@ -3617,7 +3646,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>282</v>
       </c>
@@ -3628,7 +3657,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>281</v>
       </c>
@@ -3639,7 +3668,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
     </row>
@@ -3652,12 +3681,12 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6813DEB8-9C60-4C72-BBC3-2270F3D69765}">
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="26.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3686,7 +3715,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>182</v>
       </c>
@@ -3694,7 +3723,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>183</v>
       </c>
@@ -3702,7 +3731,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>148</v>
       </c>
@@ -3710,7 +3739,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>184</v>
       </c>
@@ -3730,9 +3759,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3773,9 +3802,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3813,12 +3842,12 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{821CE188-DCEF-46EC-918E-F35D8EEA634E}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="25.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3847,7 +3876,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>192</v>
       </c>
@@ -3855,7 +3884,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>187</v>
       </c>
@@ -3863,7 +3892,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>188</v>
       </c>
@@ -3871,7 +3900,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>189</v>
       </c>
@@ -3879,7 +3908,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>190</v>
       </c>
@@ -3887,7 +3916,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>191</v>
       </c>
@@ -3895,7 +3924,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>204</v>
       </c>
@@ -3903,7 +3932,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>203</v>
       </c>
@@ -3911,7 +3940,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>201</v>
       </c>
@@ -3919,7 +3948,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>199</v>
       </c>
@@ -3936,12 +3965,12 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A687DB44-3E63-4A9D-8C81-4E18819073B2}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="33.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -3970,7 +3999,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -3978,7 +4007,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -3986,7 +4015,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>208</v>
       </c>
@@ -4015,7 +4044,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>214</v>
       </c>
@@ -4044,22 +4073,22 @@
         <v>215</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>211</v>
       </c>
@@ -4076,9 +4105,9 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -4107,7 +4136,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>233</v>
       </c>
@@ -4115,7 +4144,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>231</v>
       </c>
@@ -4123,7 +4152,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>230</v>
       </c>
@@ -4131,7 +4160,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>228</v>
       </c>
@@ -4148,14 +4177,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62AE716C-8063-4537-BCD0-E1A221532824}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.25" customWidth="1"/>
     <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -4166,7 +4195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>293</v>
       </c>
@@ -4174,7 +4203,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>295</v>
       </c>
@@ -4182,7 +4211,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>297</v>
       </c>
@@ -4190,7 +4219,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>299</v>
       </c>
@@ -4198,7 +4227,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>303</v>
       </c>
@@ -4206,7 +4235,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>305</v>
       </c>
@@ -4214,7 +4243,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>307</v>
       </c>
@@ -4222,7 +4251,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
         <v>309</v>
       </c>
@@ -4230,7 +4259,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
         <v>311</v>
       </c>
@@ -4238,7 +4267,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
         <v>313</v>
       </c>
@@ -4246,7 +4275,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A12" t="s">
         <v>315</v>
       </c>
@@ -4254,7 +4283,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A13" t="s">
         <v>319</v>
       </c>
@@ -4262,7 +4291,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A14" t="s">
         <v>318</v>
       </c>
@@ -4270,7 +4299,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A15" t="s">
         <v>321</v>
       </c>
@@ -4278,7 +4307,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A16" t="s">
         <v>323</v>
       </c>
@@ -4286,7 +4315,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A17" t="s">
         <v>325</v>
       </c>
@@ -4294,7 +4323,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A18" t="s">
         <v>327</v>
       </c>
@@ -4302,7 +4331,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A19" t="s">
         <v>329</v>
       </c>
@@ -4319,14 +4348,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4BB9733-CE9E-4CEC-94DE-5B3DF2D9CAA6}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="27.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -4337,7 +4366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>284</v>
       </c>
@@ -4348,7 +4377,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>286</v>
       </c>
@@ -4359,7 +4388,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>290</v>
       </c>
@@ -4370,7 +4399,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>301</v>
       </c>
@@ -4381,7 +4410,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>331</v>
       </c>
@@ -4392,7 +4421,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>319</v>
       </c>
@@ -4403,7 +4432,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>334</v>
       </c>
@@ -4423,13 +4452,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627E103F-0FC0-47F1-B0B6-9EC27192ADCC}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="38.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -4458,7 +4487,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4466,7 +4495,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -4474,7 +4503,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -4482,7 +4511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -4490,7 +4519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -4498,7 +4527,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -4506,7 +4535,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -4523,12 +4552,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D258F21B-C9F6-40D1-B747-2BA142D14E6D}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="69.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -4557,7 +4586,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4565,7 +4594,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -4573,7 +4602,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -4590,12 +4619,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C0D23D1-2785-4F8F-B469-597FD0D147F9}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="27.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -4624,7 +4653,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4632,7 +4661,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -4649,12 +4678,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE24C5D8-840E-4E8C-A56C-7BCA317EC95E}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="28.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -4683,7 +4712,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -4691,7 +4720,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -4702,7 +4731,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -4710,7 +4739,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -4718,7 +4747,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -4726,7 +4755,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
         <v>34</v>
       </c>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C827"/>
+  <dimension ref="A1:C886"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14633,6 +14633,1009 @@
         </is>
       </c>
     </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>Equip30002NameText</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>낡은 투구</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Worn Helm</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>Equip30003NameText</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>낡은 갑옷</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Worn Armor</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>Equip30004NameText</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>낡은 장갑</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Worn Gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>Equip30005NameText</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>낡은 각반</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Worn Greaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Equip30006NameText</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>낡은 부적</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Worn Amulet</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>Equip30007NameText</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>청동 검</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Bronze Sword</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Equip30008NameText</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>청동 투구</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Bronze Helm</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>Equip30009NameText</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>청동 갑옷</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Bronze Armor</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>Equip30010NameText</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>청동 장갑</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Bronze Gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>Equip30011NameText</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>청동 각반</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Bronze Greaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>Equip30012NameText</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>청동 부적</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Bronze Amulet</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>Equip30013NameText</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>강철 검</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Steel Sword</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>Equip30014NameText</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>강철 투구</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Steel Helm</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>Equip30015NameText</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>강철 갑옷</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Steel Armor</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>Equip30016NameText</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>강철 장갑</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Steel Gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>Equip30017NameText</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>강철 각반</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Steel Greaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>Equip30018NameText</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>강철 부적</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Steel Amulet</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>Equip30019NameText</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>은빛 검</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Silver Sword</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>Equip30020NameText</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>은빛 투구</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Silver Helm</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>Equip30021NameText</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>은빛 갑옷</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Silver Armor</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>Equip30022NameText</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>은빛 장갑</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Silver Gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>Equip30023NameText</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>은빛 각반</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Silver Greaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>Equip30024NameText</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>은빛 부적</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Silver Amulet</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>Equip30025NameText</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>미스릴 검</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Mithril Sword</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>Equip30026NameText</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>미스릴 투구</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Mithril Helm</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>Equip30027NameText</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>미스릴 갑옷</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Mithril Armor</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>Equip30028NameText</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>미스릴 장갑</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Mithril Gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>Equip30029NameText</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>미스릴 각반</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Mithril Greaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>Equip30030NameText</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>미스릴 부적</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Mithril Amulet</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>Equip30031NameText</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>용린 검</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Dragonscale Sword</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>Equip30032NameText</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>용린 투구</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Dragonscale Helm</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>Equip30033NameText</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>용린 갑옷</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Dragonscale Armor</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>Equip30034NameText</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>용린 장갑</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Dragonscale Gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>Equip30035NameText</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>용린 각반</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Dragonscale Greaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>Equip30036NameText</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>용린 부적</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Dragonscale Amulet</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>Equip30037NameText</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>성흔 검</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Sacred Sword</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>Equip30038NameText</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>성흔 투구</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Sacred Helm</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>Equip30039NameText</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>성흔 갑옷</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Sacred Armor</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>Equip30040NameText</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>성흔 장갑</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Sacred Gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>Equip30041NameText</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>성흔 각반</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Sacred Greaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>Equip30042NameText</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>성흔 부적</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Sacred Amulet</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>Equip30043NameText</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>심연 검</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Abyssal Sword</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>Equip30044NameText</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>심연 투구</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Abyssal Helm</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>Equip30045NameText</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>심연 갑옷</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Abyssal Armor</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>Equip30046NameText</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>심연 장갑</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Abyssal Gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>Equip30047NameText</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>심연 각반</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Abyssal Greaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>Equip30048NameText</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>심연 부적</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Abyssal Amulet</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>Equip30049NameText</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>여명 검</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Dawn Sword</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>Equip30050NameText</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>여명 투구</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Dawn Helm</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>Equip30051NameText</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>여명 갑옷</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Dawn Armor</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>Equip30052NameText</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>여명 장갑</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Dawn Gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>Equip30053NameText</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>여명 각반</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Dawn Greaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>Equip30054NameText</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>여명 부적</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Dawn Amulet</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>Equip30055NameText</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>신화 검</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Mythic Sword</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>Equip30056NameText</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>신화 투구</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Mythic Helm</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>Equip30057NameText</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>신화 갑옷</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Mythic Armor</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>Equip30058NameText</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>신화 장갑</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Mythic Gloves</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>Equip30059NameText</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>신화 각반</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Mythic Greaves</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>Equip30060NameText</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>신화 부적</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Mythic Amulet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C886"/>
+  <dimension ref="A1:C976"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15636,6 +15636,1536 @@
         </is>
       </c>
     </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>Skill5100NameText</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>선제의 감각</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>선제의 감각</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>Skill5100DescText</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>전투 시작 시 60% 확률로 공격력이 잠시 오른다</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>전투 시작 시 60% 확률로 공격력이 잠시 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>Skill5101NameText</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>연격의 습관</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>연격의 습관</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>Skill5101DescText</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>공격 시 25% 확률로 추가 피해를 준다</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>공격 시 25% 확률로 추가 피해를 준다</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>Skill5102NameText</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>잔심</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>잔심</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>Skill5102DescText</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>공격 후 30% 확률로 다음 일격이 날카로워진다</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>공격 후 30% 확률로 다음 일격이 날카로워진다</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>Skill5103NameText</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>타격 감각</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>타격 감각</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>Skill5103DescText</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>타격 시 20% 확률로 체력을 조금 회복한다</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>타격 시 20% 확률로 체력을 조금 회복한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>Skill5104NameText</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>치명의 흐름</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>치명의 흐름</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>Skill5104DescText</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>치명타 시 45% 확률로 공격속도가 오른다</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>치명타 시 45% 확률로 공격속도가 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>Skill5105NameText</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>연쇄 각성</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>연쇄 각성</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>Skill5105DescText</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>연속 3회 치명타 시 큰 피해를 추가한다</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>연속 3회 치명타 시 큰 피해를 추가한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>Skill5106NameText</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>빗나감의 교훈</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>빗나감의 교훈</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>Skill5106DescText</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>빗나갈 때 70% 확률로 명중이 오른다</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>빗나갈 때 70% 확률로 명중이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>Skill5107NameText</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>간파</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>간파</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>Skill5107DescText</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>상대가 회피하면 50% 확률로 치명타율이 오른다</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>상대가 회피하면 50% 확률로 치명타율이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>Skill5108NameText</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>흘리기</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>흘리기</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>Skill5108DescText</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>회피에 성공하면 55% 확률로 반격 피해를 준다</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>회피에 성공하면 55% 확률로 반격 피해를 준다</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>Skill5109NameText</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>그림자 걸음</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>그림자 걸음</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>Skill5109DescText</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>연속 3회 회피 시 회피율이 크게 오른다</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>연속 3회 회피 시 회피율이 크게 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>Skill5110NameText</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>굳은 살</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>굳은 살</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>Skill5110DescText</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>피격 시 35% 확률로 방어가 단단해진다</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>피격 시 35% 확률로 방어가 단단해진다</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>Skill5111NameText</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>벼랑 끝</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>벼랑 끝</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>Skill5111DescText</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>체력이 30% 이하가 되면 공격력이 크게 오른다</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>체력이 30% 이하가 되면 공격력이 크게 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>Skill5112NameText</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>숨통</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>숨통</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>Skill5112DescText</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>상대 체력이 30% 이하일 때 추가 피해를 준다</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>상대 체력이 30% 이하일 때 추가 피해를 준다</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>Skill5113NameText</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>불굴</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>불굴</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>Skill5113DescText</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>치명상을 입을 때 40% 확률로 체력을 회복하며 버틴다</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>치명상을 입을 때 40% 확률로 체력을 회복하며 버틴다</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>Skill5114NameText</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>회복의 여운</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>회복의 여운</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>Skill5114DescText</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>회복할 때 50% 확률로 방어가 오른다</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>회복할 때 50% 확률로 방어가 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>Skill5115NameText</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>전투 호흡</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>전투 호흡</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>Skill5115DescText</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>12초마다 체력을 회복한다</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>12초마다 체력을 회복한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>Skill5116NameText</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>각성</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>각성</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Skill5116DescText</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>18초마다 공격력이 잠시 오른다</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>18초마다 공격력이 잠시 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>Skill5117NameText</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>집중</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>집중</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>Skill5117DescText</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>16초마다 치명타율이 잠시 오른다</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>16초마다 치명타율이 잠시 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>Skill5118NameText</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>가속</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>가속</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>Skill5118DescText</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>15초마다 공격속도가 잠시 오른다</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>15초마다 공격속도가 잠시 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>Skill5119NameText</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>철벽</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>철벽</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Skill5119DescText</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>20초마다 방어가 잠시 오른다</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>20초마다 방어가 잠시 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>Skill5120NameText</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>예리함</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>예리함</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>Skill5120DescText</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>14초마다 명중이 잠시 오른다</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>14초마다 명중이 잠시 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>Skill5121NameText</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>잔상</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>잔상</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>Skill5121DescText</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>17초마다 회피율이 잠시 오른다</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>17초마다 회피율이 잠시 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Skill5122NameText</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>파쇄</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>파쇄</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>Skill5122DescText</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>22초마다 강한 추가 피해를 준다</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>22초마다 강한 추가 피해를 준다</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>Skill5123NameText</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>완력</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>완력</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Skill5123DescText</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>물리 공격력이 오른다</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>물리 공격력이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>Skill5124NameText</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>마력 회로</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>마력 회로</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>Skill5124DescText</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>마법 공격력이 오른다</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>마법 공격력이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>Skill5125NameText</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>강인함</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>강인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>Skill5125DescText</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>최대 체력이 오른다</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>최대 체력이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>Skill5126NameText</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>단련</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>단련</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>Skill5126DescText</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>방어력이 오른다</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>방어력이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>Skill5127NameText</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>급소 감각</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>급소 감각</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>Skill5127DescText</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>치명타 확률이 오른다</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>치명타 확률이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>Skill5128NameText</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>일격필살</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>일격필살</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>Skill5128DescText</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>치명타 피해가 오른다</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>치명타 피해가 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>Skill5129NameText</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>정확</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>정확</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>Skill5129DescText</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>명중률이 오른다</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>명중률이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>Skill5130NameText</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>속공</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>속공</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>Skill5130DescText</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>공격속도가 오른다</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>공격속도가 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>Skill5131NameText</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>민첩</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>민첩</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>Skill5131DescText</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>회피율이 오른다</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>회피율이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>Skill5132NameText</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>치유 친화</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>치유 친화</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>Skill5132DescText</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>회복량이 오른다</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>회복량이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>Skill5133NameText</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>기억의 그릇</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>기억의 그릇</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>Skill5133DescText</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>최대 기억력이 오른다</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>최대 기억력이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>Skill5134NameText</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>감내</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>감내</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>Skill5134DescText</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>물리 저항이 오른다</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>물리 저항이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>Skill5135NameText</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>탐구심</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>탐구심</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>Skill5135DescText</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>경험치 획득량이 늘어난다</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>경험치 획득량이 늘어난다</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>Skill5136NameText</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>장사 수완</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>장사 수완</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>Skill5136DescText</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>골드 획득량이 늘어난다</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>골드 획득량이 늘어난다</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Skill5137NameText</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>행운</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>행운</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>Skill5137DescText</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>아이템 드롭률이 오른다</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>아이템 드롭률이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>Skill5138NameText</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>교감</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>교감</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Skill5138DescText</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>미니몬 잡기 성공률이 오른다</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>미니몬 잡기 성공률이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>Skill5139NameText</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>각인</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>각인</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>Skill5139DescText</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>확정 포획에 필요한 횟수가 줄어든다</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>확정 포획에 필요한 횟수가 줄어든다</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>Skill5140NameText</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>친화의 향기</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>친화의 향기</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Skill5140DescText</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>관심 미니몬 보관 수가 늘어난다</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>관심 미니몬 보관 수가 늘어난다</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>Skill5141NameText</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>약초 지식</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>약초 지식</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>Skill5141DescText</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>물약 재사용 대기시간이 줄어든다</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>물약 재사용 대기시간이 줄어든다</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>Skill5142NameText</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>연계 감각</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>연계 감각</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>Skill5142DescText</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>콤보 게이지가 더 오래 유지된다</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>콤보 게이지가 더 오래 유지된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Skill5143NameText</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>대장장이의 눈</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>대장장이의 눈</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Skill5143DescText</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>장비 강화 성공률이 오른다</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>장비 강화 성공률이 오른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Skill5144NameText</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>발걸음</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>발걸음</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>Skill5144DescText</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>이동 속도가 오른다</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>이동 속도가 오른다</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C976"/>
+  <dimension ref="A1:C1188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17166,6 +17166,3610 @@
         </is>
       </c>
     </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>PlaceAsdalText</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>아스달 마을</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Asdal Village</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>PlaceWindportText</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>바람서린 항구</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Windrime Port</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>PlaceAshmineText</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>잿빛 광산촌</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Ashen Mining Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>PlaceFrostkeepText</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>서리안개 요새</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Frostmist Keep</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>PlaceDawnspireText</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>여명의 성도</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Dawnspire</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>SunkenGroveNameText</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>가라앉은 숲</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Sunken Grove</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>HollowBurrowNameText</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>텅 빈 굴</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Hollow Burrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>SaltMarshNameText</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>소금 늪지</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Salt Marsh</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>TidalCavernNameText</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>밀물 동굴</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Tidal Cavern</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>BrokenPierNameText</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>부서진 잔교</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Broken Pier</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>StormCliffNameText</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>폭풍 절벽</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Storm Cliff</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>DriftwoodWoodNameText</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>표류목 숲</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Driftwood Wood</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>CinderPitNameText</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>잿불 구덩이</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Cinder Pit</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>DeepShaftNameText</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>깊은 수직굴</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Deep Shaft</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>RustHallNameText</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>녹슨 회랑</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Rust Hall</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>EmberVeinNameText</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>불씨 광맥</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Ember Vein</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>CollapsedTunnelNameText</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>무너진 갱도</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Collapsed Tunnel</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>FrostWoodNameText</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>서리 수림</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Frost Wood</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>GlacierCaveNameText</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>빙하 동굴</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Glacier Cave</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>SilentChapelNameText</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>고요한 예배당</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Silent Chapel</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>WhiteWasteNameText</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>새하얀 황야</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>White Waste</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>FrozenVaultNameText</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>얼어붙은 금고</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Frozen Vault</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>DawnGardenNameText</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>여명의 정원</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Dawn Garden</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>VoidStairNameText</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>공허의 계단</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Void Stair</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>StarSanctumNameText</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>별의 성소</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Star Sanctum</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>LastRampartNameText</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>마지막 성벽</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Last Rampart</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>ThroneOfDawnNameText</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>여명의 왕좌</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Throne of Dawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>BreezingWindForestD1Text</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>신들바람 숲 입구</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Breezing Wind Forest Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>BreezingWindForestD2Text</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>신들바람 숲 2층</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Breezing Wind Forest F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>BreezingWindForestD3Text</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>신들바람 숲 3층</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>Breezing Wind Forest F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>BreezingWindForestD4Text</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>신들바람 숲 4층</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Breezing Wind Forest F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>BreezingWindForestD5Text</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>신들바람 숲 심층</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Breezing Wind Forest Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>WhisperingCaveD1Text</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>속삭이는 동굴 입구</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Whispering Cave Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>WhisperingCaveD2Text</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>속삭이는 동굴 2층</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Whispering Cave F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>WhisperingCaveD3Text</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>속삭이는 동굴 3층</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Whispering Cave F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>WhisperingCaveD4Text</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>속삭이는 동굴 4층</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Whispering Cave F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>WhisperingCaveD5Text</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>속삭이는 동굴 심층</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Whispering Cave Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>RuinedSanctumD1Text</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>폐허가 된 성소 입구</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Ruined Sanctum Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>RuinedSanctumD2Text</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>폐허가 된 성소 2층</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Ruined Sanctum F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>RuinedSanctumD3Text</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>폐허가 된 성소 3층</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Ruined Sanctum F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>RuinedSanctumD4Text</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>폐허가 된 성소 4층</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Ruined Sanctum F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>RuinedSanctumD5Text</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>폐허가 된 성소 심층</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Ruined Sanctum Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>SunkenGroveD1Text</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>가라앉은 숲 입구</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Sunken Grove Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>SunkenGroveD2Text</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>가라앉은 숲 2층</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Sunken Grove F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>SunkenGroveD3Text</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>가라앉은 숲 3층</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Sunken Grove F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>SunkenGroveD4Text</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>가라앉은 숲 4층</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Sunken Grove F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>SunkenGroveD5Text</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>가라앉은 숲 심층</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Sunken Grove Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>HollowBurrowD1Text</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>텅 빈 굴 입구</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Hollow Burrow Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>HollowBurrowD2Text</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>텅 빈 굴 2층</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Hollow Burrow F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>HollowBurrowD3Text</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>텅 빈 굴 3층</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Hollow Burrow F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>HollowBurrowD4Text</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>텅 빈 굴 4층</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Hollow Burrow F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>HollowBurrowD5Text</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>텅 빈 굴 심층</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Hollow Burrow Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>SaltMarshD1Text</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>소금 늪지 입구</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Salt Marsh Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>SaltMarshD2Text</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>소금 늪지 2층</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Salt Marsh F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>SaltMarshD3Text</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>소금 늪지 3층</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Salt Marsh F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>SaltMarshD4Text</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>소금 늪지 4층</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Salt Marsh F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>SaltMarshD5Text</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>소금 늪지 심층</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Salt Marsh Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>TidalCavernD1Text</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>밀물 동굴 입구</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Tidal Cavern Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>TidalCavernD2Text</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>밀물 동굴 2층</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Tidal Cavern F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>TidalCavernD3Text</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>밀물 동굴 3층</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Tidal Cavern F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>TidalCavernD4Text</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>밀물 동굴 4층</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Tidal Cavern F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>TidalCavernD5Text</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>밀물 동굴 심층</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Tidal Cavern Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>BrokenPierD1Text</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>부서진 잔교 입구</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Broken Pier Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>BrokenPierD2Text</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>부서진 잔교 2층</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Broken Pier F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>BrokenPierD3Text</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>부서진 잔교 3층</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Broken Pier F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>BrokenPierD4Text</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>부서진 잔교 4층</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Broken Pier F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>BrokenPierD5Text</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>부서진 잔교 심층</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Broken Pier Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>StormCliffD1Text</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>폭풍 절벽 입구</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Storm Cliff Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>StormCliffD2Text</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>폭풍 절벽 2층</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Storm Cliff F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>StormCliffD3Text</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>폭풍 절벽 3층</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Storm Cliff F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>StormCliffD4Text</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>폭풍 절벽 4층</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Storm Cliff F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>StormCliffD5Text</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>폭풍 절벽 심층</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Storm Cliff Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>DriftwoodWoodD1Text</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>표류목 숲 입구</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Driftwood Wood Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>DriftwoodWoodD2Text</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>표류목 숲 2층</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Driftwood Wood F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>DriftwoodWoodD3Text</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>표류목 숲 3층</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Driftwood Wood F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>DriftwoodWoodD4Text</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>표류목 숲 4층</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Driftwood Wood F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>DriftwoodWoodD5Text</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>표류목 숲 심층</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Driftwood Wood Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>CinderPitD1Text</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>잿불 구덩이 입구</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Cinder Pit Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>CinderPitD2Text</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>잿불 구덩이 2층</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Cinder Pit F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>CinderPitD3Text</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>잿불 구덩이 3층</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Cinder Pit F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>CinderPitD4Text</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>잿불 구덩이 4층</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Cinder Pit F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>CinderPitD5Text</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>잿불 구덩이 심층</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Cinder Pit Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>DeepShaftD1Text</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>깊은 수직굴 입구</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Deep Shaft Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>DeepShaftD2Text</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>깊은 수직굴 2층</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Deep Shaft F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>DeepShaftD3Text</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>깊은 수직굴 3층</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Deep Shaft F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>DeepShaftD4Text</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>깊은 수직굴 4층</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Deep Shaft F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>DeepShaftD5Text</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>깊은 수직굴 심층</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Deep Shaft Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>RustHallD1Text</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>녹슨 회랑 입구</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Rust Hall Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>RustHallD2Text</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>녹슨 회랑 2층</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Rust Hall F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>RustHallD3Text</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>녹슨 회랑 3층</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Rust Hall F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>RustHallD4Text</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>녹슨 회랑 4층</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Rust Hall F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>RustHallD5Text</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>녹슨 회랑 심층</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Rust Hall Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>EmberVeinD1Text</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>불씨 광맥 입구</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Ember Vein Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>EmberVeinD2Text</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>불씨 광맥 2층</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Ember Vein F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>EmberVeinD3Text</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>불씨 광맥 3층</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Ember Vein F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>EmberVeinD4Text</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>불씨 광맥 4층</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Ember Vein F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>EmberVeinD5Text</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>불씨 광맥 심층</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Ember Vein Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>CollapsedTunnelD1Text</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>무너진 갱도 입구</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Collapsed Tunnel Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>CollapsedTunnelD2Text</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>무너진 갱도 2층</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Collapsed Tunnel F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>CollapsedTunnelD3Text</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>무너진 갱도 3층</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Collapsed Tunnel F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>CollapsedTunnelD4Text</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>무너진 갱도 4층</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Collapsed Tunnel F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>CollapsedTunnelD5Text</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>무너진 갱도 심층</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Collapsed Tunnel Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>FrostWoodD1Text</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>서리 수림 입구</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Frost Wood Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>FrostWoodD2Text</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>서리 수림 2층</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Frost Wood F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>FrostWoodD3Text</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>서리 수림 3층</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Frost Wood F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>FrostWoodD4Text</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>서리 수림 4층</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Frost Wood F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>FrostWoodD5Text</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>서리 수림 심층</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Frost Wood Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>GlacierCaveD1Text</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>빙하 동굴 입구</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Glacier Cave Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>GlacierCaveD2Text</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>빙하 동굴 2층</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Glacier Cave F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>GlacierCaveD3Text</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>빙하 동굴 3층</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Glacier Cave F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>GlacierCaveD4Text</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>빙하 동굴 4층</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Glacier Cave F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>GlacierCaveD5Text</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>빙하 동굴 심층</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Glacier Cave Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>SilentChapelD1Text</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>고요한 예배당 입구</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Silent Chapel Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>SilentChapelD2Text</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>고요한 예배당 2층</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Silent Chapel F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>SilentChapelD3Text</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>고요한 예배당 3층</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Silent Chapel F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>SilentChapelD4Text</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>고요한 예배당 4층</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Silent Chapel F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>SilentChapelD5Text</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>고요한 예배당 심층</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Silent Chapel Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>WhiteWasteD1Text</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>새하얀 황야 입구</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>White Waste Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>WhiteWasteD2Text</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>새하얀 황야 2층</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>White Waste F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>WhiteWasteD3Text</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>새하얀 황야 3층</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>White Waste F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>WhiteWasteD4Text</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>새하얀 황야 4층</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>White Waste F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>WhiteWasteD5Text</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>새하얀 황야 심층</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>White Waste Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>FrozenVaultD1Text</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>얼어붙은 금고 입구</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Frozen Vault Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>FrozenVaultD2Text</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>얼어붙은 금고 2층</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Frozen Vault F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>FrozenVaultD3Text</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>얼어붙은 금고 3층</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Frozen Vault F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>FrozenVaultD4Text</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>얼어붙은 금고 4층</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Frozen Vault F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>FrozenVaultD5Text</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>얼어붙은 금고 심층</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Frozen Vault Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>DawnGardenD1Text</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>여명의 정원 입구</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Dawn Garden Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>DawnGardenD2Text</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>여명의 정원 2층</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Dawn Garden F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>DawnGardenD3Text</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>여명의 정원 3층</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Dawn Garden F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>DawnGardenD4Text</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>여명의 정원 4층</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Dawn Garden F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>DawnGardenD5Text</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>여명의 정원 심층</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Dawn Garden Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>VoidStairD1Text</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>공허의 계단 입구</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Void Stair Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>VoidStairD2Text</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>공허의 계단 2층</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Void Stair F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>VoidStairD3Text</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>공허의 계단 3층</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Void Stair F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>VoidStairD4Text</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>공허의 계단 4층</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Void Stair F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>VoidStairD5Text</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>공허의 계단 심층</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Void Stair Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>StarSanctumD1Text</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>별의 성소 입구</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Star Sanctum Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>StarSanctumD2Text</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>별의 성소 2층</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Star Sanctum F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>StarSanctumD3Text</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>별의 성소 3층</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Star Sanctum F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>StarSanctumD4Text</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>별의 성소 4층</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Star Sanctum F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>StarSanctumD5Text</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>별의 성소 심층</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Star Sanctum Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>LastRampartD1Text</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>마지막 성벽 입구</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Last Rampart Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>LastRampartD2Text</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>마지막 성벽 2층</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Last Rampart F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>LastRampartD3Text</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>마지막 성벽 3층</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Last Rampart F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>LastRampartD4Text</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>마지막 성벽 4층</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Last Rampart F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>LastRampartD5Text</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>마지막 성벽 심층</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>Last Rampart Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>ThroneOfDawnD1Text</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>여명의 왕좌 입구</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>Throne of Dawn Entrance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>ThroneOfDawnD2Text</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>여명의 왕좌 2층</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Throne of Dawn F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>ThroneOfDawnD3Text</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>여명의 왕좌 3층</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>Throne of Dawn F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>ThroneOfDawnD4Text</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>여명의 왕좌 4층</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>Throne of Dawn F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>ThroneOfDawnD5Text</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>여명의 왕좌 심층</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Throne of Dawn Depths</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>Mat11001NameText</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>슬라임 젤리</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Slime Jelly</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>Mat11001DescText</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>슬라임 젤리. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Slime Jelly. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>Mat11002NameText</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>거미 실크</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Spider Silk</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>Mat11002DescText</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>거미 실크. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Spider Silk. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>Mat11003NameText</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>늑대 송곳니</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>Wolf Fang</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>Mat11003DescText</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>늑대 송곳니. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Wolf Fang. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>Mat11004NameText</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>독버섯 갓</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Toadstool Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>Mat11004DescText</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>독버섯 갓. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Toadstool Cap. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>Mat11005NameText</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>바람 정수</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Wind Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>Mat11005DescText</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>바람 정수. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Wind Essence. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>Mat11006NameText</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>멧돼지 가죽</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Boar Hide</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>Mat11006DescText</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>멧돼지 가죽. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Boar Hide. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>Mat11007NameText</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>까마귀 깃털</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Crow Feather</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>Mat11007DescText</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>까마귀 깃털. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Crow Feather. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>Mat11008NameText</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>질긴 덩굴</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Tough Vine</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>Mat11008DescText</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>질긴 덩굴. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Tough Vine. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>Mat11009NameText</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>여우 꼬리털</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Fox Fur</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>Mat11009DescText</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>여우 꼬리털. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Fox Fur. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>Mat11010NameText</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>말벌 침</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Hornet Sting</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>Mat11010DescText</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>말벌 침. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Hornet Sting. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>Mat11011NameText</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>박쥐 날개막</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Bat Membrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>Mat11011DescText</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>박쥐 날개막. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Bat Membrane. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>Mat11012NameText</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>두더지 발톱</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Mole Claw</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>Mat11012DescText</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>두더지 발톱. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Mole Claw. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>Mat11013NameText</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>광부의 유품</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Miner's Relic</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>Mat11013DescText</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>광부의 유품. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Miner's Relic. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>Mat11014NameText</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>수정 파편</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Crystal Shard</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>Mat11014DescText</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>수정 파편. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Crystal Shard. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>Mat11015NameText</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>지네 외피</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Centipede Shell</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>Mat11015DescText</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>지네 외피. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Centipede Shell. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>Mat11016NameText</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>젖은 이끼</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Damp Moss</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>Mat11016DescText</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>젖은 이끼. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Damp Moss. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>Mat11017NameText</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>석상 조각</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Statue Fragment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>Mat11017DescText</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>석상 조각. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Statue Fragment. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>Mat11018NameText</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>그림자 응결물</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Shadow Clot</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>Mat11018DescText</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>그림자 응결물. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Shadow Clot. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>Mat11019NameText</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>도롱뇽 비늘</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Salamander Scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>Mat11019DescText</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>도롱뇽 비늘. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Salamander Scale. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>Mat11020NameText</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>발광 점액</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Glow Slime</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>Mat11020DescText</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>발광 점액. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Glow Slime. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>Mat11021NameText</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>망령의 재</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Revenant Ash</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>Mat11021DescText</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>망령의 재. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Revenant Ash. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>Mat11022NameText</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>기사의 문장</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Knight's Crest</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>Mat11022DescText</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>기사의 문장. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Knight's Crest. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>Mat11023NameText</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>타락한 성물</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Tainted Relic</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>Mat11023DescText</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>타락한 성물. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Tainted Relic. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>Mat11024NameText</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>키메라 갈기</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Chimera Mane</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>Mat11024DescText</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>키메라 갈기. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Chimera Mane. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>Mat11025NameText</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>가고일 돌조각</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Gargoyle Stone</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>Mat11025DescText</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>가고일 돌조각. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Gargoyle Stone. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>Mat11026NameText</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>수호자의 핵</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Warden Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>Mat11026DescText</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>수호자의 핵. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Warden Core. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>Mat11027NameText</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>환영의 조각</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Phantom Sliver</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>Mat11027DescText</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>환영의 조각. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Phantom Sliver. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>Mat11028NameText</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>오염된 정수</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Tainted Essence</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>Mat11028DescText</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>오염된 정수. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Tainted Essence. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>Mat11029NameText</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>제단의 파편</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Altar Fragment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>Mat11029DescText</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>제단의 파편. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Altar Fragment. A crafting material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>Mat11030NameText</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>공허 결정</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Void Crystal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>Mat11030DescText</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>공허 결정. 몬스터에게서 얻는 재료다.</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Void Crystal. A crafting material.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1188"/>
+  <dimension ref="A1:C1192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20770,6 +20770,74 @@
         </is>
       </c>
     </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>ForgeCantRecoverText</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>복구불가</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>CANT RECOV</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>ForgeCantEnhanceText</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>강화불가</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>CANT ENHANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>ForgeDurabilityText</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>내구도</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>DURABILITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>TestKey</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>테스트</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -14131,7 +14131,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>신들바람 숲 입구</t>
+          <t>산들바람 숲 입구</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>신들바람 숲 2층</t>
+          <t>산들바람 숲 2층</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>신들바람 숲 3층</t>
+          <t>산들바람 숲 3층</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>신들바람 숲 4층</t>
+          <t>산들바람 숲 4층</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>신들바람 숲 5층</t>
+          <t>산들바람 숲 5층</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>신들바람 숲 6층</t>
+          <t>산들바람 숲 6층</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>신들바람 숲 7층</t>
+          <t>산들바람 숲 7층</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -14250,7 +14250,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>신들바람 숲 8층</t>
+          <t>산들바람 숲 8층</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -14267,7 +14267,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>신들바람 숲 9층</t>
+          <t>산들바람 숲 9층</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>신들바람 숲 10층</t>
+          <t>산들바람 숲 10층</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>신들바람 숲 입구</t>
+          <t>산들바람 숲 입구</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
@@ -17650,7 +17650,7 @@
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>신들바람 숲 2층</t>
+          <t>산들바람 숲 2층</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -17667,7 +17667,7 @@
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>신들바람 숲 3층</t>
+          <t>산들바람 숲 3층</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
@@ -17684,7 +17684,7 @@
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>신들바람 숲 4층</t>
+          <t>산들바람 숲 4층</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
@@ -17701,7 +17701,7 @@
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>신들바람 숲 심층</t>
+          <t>산들바람 숲 심층</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1192"/>
+  <dimension ref="A1:C1204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20838,6 +20838,210 @@
         </is>
       </c>
     </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>Skill5200NameText</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>강타</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Smash</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>Skill5200DescText</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>적에게 즉시 추가 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Deals instant bonus damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>Skill5201NameText</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>회복술</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Mend</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>Skill5201DescText</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>체력을 회복한다.</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Restores health.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>Skill5202NameText</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>광폭화</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Frenzy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>Skill5202DescText</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>일정 시간 공격력이 크게 오른다.</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Greatly raises attack power for a time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>Skill5203NameText</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>질풍</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Gale</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>Skill5203DescText</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>일정 시간 공격 속도가 오른다.</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Raises attack speed for a time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>Skill5204NameText</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>철벽</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Bulwark</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>Skill5204DescText</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>일정 시간 방어력이 크게 오른다.</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Greatly raises defense for a time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>Skill5205NameText</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>필살</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>Skill5205DescText</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>온 힘을 모아 결정타를 날린다.</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Gathers all strength for a decisive blow.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1204"/>
+  <dimension ref="A1:C1207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21042,6 +21042,57 @@
         </is>
       </c>
     </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>ForgePotentialText</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>잠재력</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>POTENTIALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>ForgeOrText</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>또는</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>ForgeReqMaterialText</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>필요 재료</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>REQ. MATERIAL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1207"/>
+  <dimension ref="A1:C1215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21093,6 +21093,142 @@
         </is>
       </c>
     </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>ItemSOM1NameText</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>장인의 인장 I</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Sigil of Master I</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>ItemSOM1DescText</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>강화 돌파에 쓰이는 하급 인장.</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>A lesser sigil used to break enhancement limits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>ItemSOM2NameText</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>장인의 인장 II</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Sigil of Master II</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>ItemSOM2DescText</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>강화 돌파에 쓰이는 중급 인장.</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>A greater sigil used to break enhancement limits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>ItemSOM3NameText</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>장인의 인장 III</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Sigil of Master III</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>ItemSOM3DescText</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>강화 돌파에 쓰이는 상급 인장.</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>A supreme sigil used to break enhancement limits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>ItemBMORNameText</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>축복의 거울</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Blessed Mirror</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>ItemBMORDescText</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>내구도를 완전히 되돌리는 거울.</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>A mirror that fully restores durability.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1215"/>
+  <dimension ref="A1:C1219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21229,6 +21229,76 @@
         </is>
       </c>
     </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>MagicAttackText</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>마법공격력</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>M.ATK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>EnhanceLevelText</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>강화도</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>ENHANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>EnhanceSucceededText</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>강화 성공</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>ENHANCE
+SUCCEEDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>EnhanceFailedText</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>강화 실패</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>ENHANCE
+FAILED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1219"/>
+  <dimension ref="A1:C1220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21299,6 +21299,23 @@
         </is>
       </c>
     </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>EnhancePreviewText</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>강화 성공 시 능력치 변화</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>ON SUCCESS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1220"/>
+  <dimension ref="A1:C1243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,7 +866,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>단조</t>
+          <t>대장간</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -21316,6 +21316,403 @@
         </is>
       </c>
     </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>MonasteryUnlockText</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>수도원에 출입할 수 있게 되었습니다.
+[축성]으로 직업 능력을 받으세요.</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>The Monastery is now open to you.
+Receive your class blessings there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>MonasteryNothingText</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>준비 중</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>ForgeUnlockText</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>대장간이 문을 열었습니다.
+재료를 모아 장비를 만들 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>The Forge has opened.
+Gather materials to craft equipment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>ForgeCraftBtnText</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>제작</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>CRAFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>ForgeEnhanceBtnText</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>강화</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>ENHANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>ForgeCraftTitleText</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>장비 제작</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>CRAFT EQUIPMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>ForgeNoCraftableText</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>지금 만들 수 있는 장비가 없습니다.</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Nothing can be crafted right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>ForgeCraftedText</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>제작 완료</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>CRAFTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>ForgeOwnedText</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>보유 중</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>OWNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>ForgeNoEquipText</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>손질할 장비가 없습니다.</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>You have no equipment to work on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>ShopText</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>상점</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>ShopUnlockText</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>상점이 문을 열었습니다.
+물약과 재료를 사고팔 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>The Shop has opened.
+Buy and sell potions and materials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>ShopBuyBtnText</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>ShopSellBtnText</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>판매</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>ShopBuyTitleText</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>판매 목록</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>FOR SALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>ShopSellTitleText</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>되팔기</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>SELL BACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>ShopNotEnoughGoldText</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>골드가 부족합니다.</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Not enough gold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>ShopNothingToSellText</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>되팔 물건이 없습니다.</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Nothing to sell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>ShopLockedItemText</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Lv.{0} 부터</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>From Lv.{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>ShopPurchasedText</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>구매했습니다.</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Purchased.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>ShopSoldText</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>판매했습니다.</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Sold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>ShopSellPriceText</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>판매가</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>SELL PRICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>ShopOwnedCountText</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>보유</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>OWNED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1243"/>
+  <dimension ref="A1:C1247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21713,6 +21713,74 @@
         </is>
       </c>
     </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>ConfirmBtnText</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>CancelBtnText</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>취소</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>CANCEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>ShopConfirmBuyTitleText</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>구매하시겠습니까?</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>BUY?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>ShopConfirmSellTitleText</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>판매하시겠습니까?</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>SELL?</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1247"/>
+  <dimension ref="A1:C1309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>어린 슬라임</t>
+          <t>설익은 슬라임</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Young Slime</t>
+          <t>Callow Slime</t>
         </is>
       </c>
     </row>
@@ -5818,12 +5818,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>어린 숲거미</t>
+          <t>설익은 숲거미</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Young Forest Spider</t>
+          <t>Callow Forest Spider</t>
         </is>
       </c>
     </row>
@@ -5835,12 +5835,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>어린 들늑대</t>
+          <t>설익은 들늑대</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Young Wild Wolf</t>
+          <t>Callow Wild Wolf</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>어린 독버섯</t>
+          <t>설익은 독버섯</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Young Toadstool</t>
+          <t>Callow Toadstool</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>어린 바람정령</t>
+          <t>설익은 바람정령</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Young Wind Sprite</t>
+          <t>Callow Wind Sprite</t>
         </is>
       </c>
     </row>
@@ -5886,12 +5886,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>어린 멧돼지</t>
+          <t>설익은 멧돼지</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Young Boar</t>
+          <t>Callow Boar</t>
         </is>
       </c>
     </row>
@@ -5903,12 +5903,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>어린 까마귀</t>
+          <t>설익은 까마귀</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Young Crow</t>
+          <t>Callow Crow</t>
         </is>
       </c>
     </row>
@@ -6090,12 +6090,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>거친 슬라임</t>
+          <t>억센 슬라임</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Feral Slime</t>
+          <t>Sturdy Slime</t>
         </is>
       </c>
     </row>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>거친 숲거미</t>
+          <t>억센 숲거미</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Feral Forest Spider</t>
+          <t>Sturdy Forest Spider</t>
         </is>
       </c>
     </row>
@@ -6124,12 +6124,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>거친 들늑대</t>
+          <t>억센 들늑대</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Feral Wild Wolf</t>
+          <t>Sturdy Wild Wolf</t>
         </is>
       </c>
     </row>
@@ -6141,12 +6141,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>거친 독버섯</t>
+          <t>억센 독버섯</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Feral Toadstool</t>
+          <t>Sturdy Toadstool</t>
         </is>
       </c>
     </row>
@@ -6158,12 +6158,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>거친 바람정령</t>
+          <t>억센 바람정령</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Feral Wind Sprite</t>
+          <t>Sturdy Wind Sprite</t>
         </is>
       </c>
     </row>
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>거친 멧돼지</t>
+          <t>억센 멧돼지</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Feral Boar</t>
+          <t>Sturdy Boar</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>거친 까마귀</t>
+          <t>억센 까마귀</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Feral Crow</t>
+          <t>Sturdy Crow</t>
         </is>
       </c>
     </row>
@@ -6379,12 +6379,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>굶주린 슬라임</t>
+          <t>표독한 슬라임</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Starving Slime</t>
+          <t>Vicious Slime</t>
         </is>
       </c>
     </row>
@@ -6396,12 +6396,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>굶주린 숲거미</t>
+          <t>표독한 숲거미</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Starving Forest Spider</t>
+          <t>Vicious Forest Spider</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>굶주린 들늑대</t>
+          <t>표독한 들늑대</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Starving Wild Wolf</t>
+          <t>Vicious Wild Wolf</t>
         </is>
       </c>
     </row>
@@ -6430,12 +6430,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>굶주린 독버섯</t>
+          <t>표독한 독버섯</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Starving Toadstool</t>
+          <t>Vicious Toadstool</t>
         </is>
       </c>
     </row>
@@ -6447,12 +6447,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>굶주린 바람정령</t>
+          <t>표독한 바람정령</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Starving Wind Sprite</t>
+          <t>Vicious Wind Sprite</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>굶주린 멧돼지</t>
+          <t>표독한 멧돼지</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Starving Boar</t>
+          <t>Vicious Boar</t>
         </is>
       </c>
     </row>
@@ -6481,12 +6481,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>굶주린 까마귀</t>
+          <t>표독한 까마귀</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Starving Crow</t>
+          <t>Vicious Crow</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>성난 슬라임</t>
+          <t>흉포한 슬라임</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Enraged Slime</t>
+          <t>Ferocious Slime</t>
         </is>
       </c>
     </row>
@@ -6685,12 +6685,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>성난 숲거미</t>
+          <t>흉포한 숲거미</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Enraged Forest Spider</t>
+          <t>Ferocious Forest Spider</t>
         </is>
       </c>
     </row>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>성난 들늑대</t>
+          <t>흉포한 들늑대</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Enraged Wild Wolf</t>
+          <t>Ferocious Wild Wolf</t>
         </is>
       </c>
     </row>
@@ -6719,12 +6719,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>성난 독버섯</t>
+          <t>흉포한 독버섯</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Enraged Toadstool</t>
+          <t>Ferocious Toadstool</t>
         </is>
       </c>
     </row>
@@ -6736,12 +6736,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>성난 바람정령</t>
+          <t>흉포한 바람정령</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Enraged Wind Sprite</t>
+          <t>Ferocious Wind Sprite</t>
         </is>
       </c>
     </row>
@@ -6753,12 +6753,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>성난 멧돼지</t>
+          <t>흉포한 멧돼지</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Enraged Boar</t>
+          <t>Ferocious Boar</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>성난 까마귀</t>
+          <t>흉포한 까마귀</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Enraged Crow</t>
+          <t>Ferocious Crow</t>
         </is>
       </c>
     </row>
@@ -6957,12 +6957,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>사나운 슬라임</t>
+          <t>무자비한 슬라임</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Savage Slime</t>
+          <t>Merciless Slime</t>
         </is>
       </c>
     </row>
@@ -6974,12 +6974,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>사나운 숲거미</t>
+          <t>무자비한 숲거미</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Savage Forest Spider</t>
+          <t>Merciless Forest Spider</t>
         </is>
       </c>
     </row>
@@ -6991,12 +6991,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>사나운 들늑대</t>
+          <t>무자비한 들늑대</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Savage Wild Wolf</t>
+          <t>Merciless Wild Wolf</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>사나운 독버섯</t>
+          <t>무자비한 독버섯</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Savage Toadstool</t>
+          <t>Merciless Toadstool</t>
         </is>
       </c>
     </row>
@@ -7025,12 +7025,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>사나운 바람정령</t>
+          <t>무자비한 바람정령</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Savage Wind Sprite</t>
+          <t>Merciless Wind Sprite</t>
         </is>
       </c>
     </row>
@@ -7042,12 +7042,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>사나운 멧돼지</t>
+          <t>무자비한 멧돼지</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Savage Boar</t>
+          <t>Merciless Boar</t>
         </is>
       </c>
     </row>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>사나운 까마귀</t>
+          <t>무자비한 까마귀</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Savage Crow</t>
+          <t>Merciless Crow</t>
         </is>
       </c>
     </row>
@@ -7246,12 +7246,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>오래된 슬라임</t>
+          <t>풍화된 슬라임</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Ancient Slime</t>
+          <t>Weathered Slime</t>
         </is>
       </c>
     </row>
@@ -7263,12 +7263,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>오래된 숲거미</t>
+          <t>풍화된 숲거미</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Ancient Forest Spider</t>
+          <t>Weathered Forest Spider</t>
         </is>
       </c>
     </row>
@@ -7280,12 +7280,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>오래된 들늑대</t>
+          <t>풍화된 들늑대</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Ancient Wild Wolf</t>
+          <t>Weathered Wild Wolf</t>
         </is>
       </c>
     </row>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>오래된 독버섯</t>
+          <t>풍화된 독버섯</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Ancient Toadstool</t>
+          <t>Weathered Toadstool</t>
         </is>
       </c>
     </row>
@@ -7314,12 +7314,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>오래된 바람정령</t>
+          <t>풍화된 바람정령</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Ancient Wind Sprite</t>
+          <t>Weathered Wind Sprite</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>오래된 멧돼지</t>
+          <t>풍화된 멧돼지</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Ancient Boar</t>
+          <t>Weathered Boar</t>
         </is>
       </c>
     </row>
@@ -7348,12 +7348,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>오래된 까마귀</t>
+          <t>풍화된 까마귀</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Ancient Crow</t>
+          <t>Weathered Crow</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Corrupted Slime</t>
+          <t>Tainted Slime</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Corrupted Forest Spider</t>
+          <t>Tainted Forest Spider</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Corrupted Wild Wolf</t>
+          <t>Tainted Wild Wolf</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Corrupted Toadstool</t>
+          <t>Tainted Toadstool</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Corrupted Wind Sprite</t>
+          <t>Tainted Wind Sprite</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Corrupted Boar</t>
+          <t>Tainted Boar</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Corrupted Crow</t>
+          <t>Tainted Crow</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Corrupted Creeper</t>
+          <t>Tainted Creeper</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Corrupted Fox</t>
+          <t>Tainted Fox</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Corrupted Hornet</t>
+          <t>Tainted Hornet</t>
         </is>
       </c>
     </row>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>타락한 슬라임</t>
+          <t>저주받은 슬라임</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Corrupted Slime</t>
+          <t>Cursed Slime</t>
         </is>
       </c>
     </row>
@@ -7552,12 +7552,12 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>타락한 숲거미</t>
+          <t>저주받은 숲거미</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Corrupted Forest Spider</t>
+          <t>Cursed Forest Spider</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>타락한 들늑대</t>
+          <t>저주받은 들늑대</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Corrupted Wild Wolf</t>
+          <t>Cursed Wild Wolf</t>
         </is>
       </c>
     </row>
@@ -7586,12 +7586,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>타락한 독버섯</t>
+          <t>저주받은 독버섯</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Corrupted Toadstool</t>
+          <t>Cursed Toadstool</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>타락한 바람정령</t>
+          <t>저주받은 바람정령</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Corrupted Wind Sprite</t>
+          <t>Cursed Wind Sprite</t>
         </is>
       </c>
     </row>
@@ -7620,12 +7620,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>타락한 멧돼지</t>
+          <t>저주받은 멧돼지</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Corrupted Boar</t>
+          <t>Cursed Boar</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>타락한 까마귀</t>
+          <t>저주받은 까마귀</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Corrupted Crow</t>
+          <t>Cursed Crow</t>
         </is>
       </c>
     </row>
@@ -7824,12 +7824,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>심연의 슬라임</t>
+          <t>공허의 슬라임</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Abyssal Slime</t>
+          <t>Voidtouched Slime</t>
         </is>
       </c>
     </row>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>심연의 숲거미</t>
+          <t>공허의 숲거미</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Abyssal Forest Spider</t>
+          <t>Voidtouched Forest Spider</t>
         </is>
       </c>
     </row>
@@ -7858,12 +7858,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>심연의 들늑대</t>
+          <t>공허의 들늑대</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Abyssal Wild Wolf</t>
+          <t>Voidtouched Wild Wolf</t>
         </is>
       </c>
     </row>
@@ -7875,12 +7875,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>심연의 독버섯</t>
+          <t>공허의 독버섯</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Abyssal Toadstool</t>
+          <t>Voidtouched Toadstool</t>
         </is>
       </c>
     </row>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>심연의 바람정령</t>
+          <t>공허의 바람정령</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Abyssal Wind Sprite</t>
+          <t>Voidtouched Wind Sprite</t>
         </is>
       </c>
     </row>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>심연의 멧돼지</t>
+          <t>공허의 멧돼지</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Abyssal Boar</t>
+          <t>Voidtouched Boar</t>
         </is>
       </c>
     </row>
@@ -7926,12 +7926,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>심연의 까마귀</t>
+          <t>공허의 까마귀</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Abyssal Crow</t>
+          <t>Voidtouched Crow</t>
         </is>
       </c>
     </row>
@@ -8113,12 +8113,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>왕관을 쓴 슬라임</t>
+          <t>불멸의 슬라임</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Crowned Slime</t>
+          <t>Undying Slime</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>왕관을 쓴 숲거미</t>
+          <t>불멸의 숲거미</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Crowned Forest Spider</t>
+          <t>Undying Forest Spider</t>
         </is>
       </c>
     </row>
@@ -8147,12 +8147,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>왕관을 쓴 들늑대</t>
+          <t>불멸의 들늑대</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Crowned Wild Wolf</t>
+          <t>Undying Wild Wolf</t>
         </is>
       </c>
     </row>
@@ -8164,12 +8164,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>왕관을 쓴 독버섯</t>
+          <t>불멸의 독버섯</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Crowned Toadstool</t>
+          <t>Undying Toadstool</t>
         </is>
       </c>
     </row>
@@ -8181,12 +8181,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>왕관을 쓴 바람정령</t>
+          <t>불멸의 바람정령</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Crowned Wind Sprite</t>
+          <t>Undying Wind Sprite</t>
         </is>
       </c>
     </row>
@@ -8198,12 +8198,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>왕관을 쓴 멧돼지</t>
+          <t>불멸의 멧돼지</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Crowned Boar</t>
+          <t>Undying Boar</t>
         </is>
       </c>
     </row>
@@ -8215,12 +8215,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>왕관을 쓴 까마귀</t>
+          <t>불멸의 까마귀</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Crowned Crow</t>
+          <t>Undying Crow</t>
         </is>
       </c>
     </row>
@@ -8402,12 +8402,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>전설의 슬라임</t>
+          <t>태초의 슬라임</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Legendary Slime</t>
+          <t>Primordial Slime</t>
         </is>
       </c>
     </row>
@@ -8419,12 +8419,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>전설의 숲거미</t>
+          <t>태초의 숲거미</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Legendary Forest Spider</t>
+          <t>Primordial Forest Spider</t>
         </is>
       </c>
     </row>
@@ -8436,12 +8436,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>전설의 들늑대</t>
+          <t>태초의 들늑대</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Legendary Wild Wolf</t>
+          <t>Primordial Wild Wolf</t>
         </is>
       </c>
     </row>
@@ -8453,12 +8453,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>전설의 독버섯</t>
+          <t>태초의 독버섯</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Legendary Toadstool</t>
+          <t>Primordial Toadstool</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>전설의 바람정령</t>
+          <t>태초의 바람정령</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Legendary Wind Sprite</t>
+          <t>Primordial Wind Sprite</t>
         </is>
       </c>
     </row>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>전설의 멧돼지</t>
+          <t>태초의 멧돼지</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Legendary Boar</t>
+          <t>Primordial Boar</t>
         </is>
       </c>
     </row>
@@ -8504,12 +8504,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>전설의 까마귀</t>
+          <t>태초의 까마귀</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Legendary Crow</t>
+          <t>Primordial Crow</t>
         </is>
       </c>
     </row>
@@ -8691,12 +8691,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>어린 동굴박쥐</t>
+          <t>설익은 동굴박쥐</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Young Cave Bat</t>
+          <t>Callow Cave Bat</t>
         </is>
       </c>
     </row>
@@ -8708,12 +8708,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>어린 두더지</t>
+          <t>설익은 두더지</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Young Mole</t>
+          <t>Callow Mole</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>어린 광부망령</t>
+          <t>설익은 광부망령</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Young Miner Wraith</t>
+          <t>Callow Miner Wraith</t>
         </is>
       </c>
     </row>
@@ -8742,12 +8742,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>어린 수정골렘</t>
+          <t>설익은 수정골렘</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Young Crystal Golem</t>
+          <t>Callow Crystal Golem</t>
         </is>
       </c>
     </row>
@@ -8759,12 +8759,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>어린 지네</t>
+          <t>설익은 지네</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Young Centipede</t>
+          <t>Callow Centipede</t>
         </is>
       </c>
     </row>
@@ -8776,12 +8776,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>어린 이끼괴물</t>
+          <t>설익은 이끼괴물</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Young Moss Horror</t>
+          <t>Callow Moss Horror</t>
         </is>
       </c>
     </row>
@@ -8793,12 +8793,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>어린 석상병</t>
+          <t>설익은 석상병</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Young Stone Sentry</t>
+          <t>Callow Stone Sentry</t>
         </is>
       </c>
     </row>
@@ -8980,12 +8980,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>거친 동굴박쥐</t>
+          <t>억센 동굴박쥐</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Feral Cave Bat</t>
+          <t>Sturdy Cave Bat</t>
         </is>
       </c>
     </row>
@@ -8997,12 +8997,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>거친 두더지</t>
+          <t>억센 두더지</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Feral Mole</t>
+          <t>Sturdy Mole</t>
         </is>
       </c>
     </row>
@@ -9014,12 +9014,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>거친 광부망령</t>
+          <t>억센 광부망령</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Feral Miner Wraith</t>
+          <t>Sturdy Miner Wraith</t>
         </is>
       </c>
     </row>
@@ -9031,12 +9031,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>거친 수정골렘</t>
+          <t>억센 수정골렘</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Feral Crystal Golem</t>
+          <t>Sturdy Crystal Golem</t>
         </is>
       </c>
     </row>
@@ -9048,12 +9048,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>거친 지네</t>
+          <t>억센 지네</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Feral Centipede</t>
+          <t>Sturdy Centipede</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>거친 이끼괴물</t>
+          <t>억센 이끼괴물</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Feral Moss Horror</t>
+          <t>Sturdy Moss Horror</t>
         </is>
       </c>
     </row>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>거친 석상병</t>
+          <t>억센 석상병</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Feral Stone Sentry</t>
+          <t>Sturdy Stone Sentry</t>
         </is>
       </c>
     </row>
@@ -9269,12 +9269,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>굶주린 동굴박쥐</t>
+          <t>표독한 동굴박쥐</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Starving Cave Bat</t>
+          <t>Vicious Cave Bat</t>
         </is>
       </c>
     </row>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>굶주린 두더지</t>
+          <t>표독한 두더지</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Starving Mole</t>
+          <t>Vicious Mole</t>
         </is>
       </c>
     </row>
@@ -9303,12 +9303,12 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>굶주린 광부망령</t>
+          <t>표독한 광부망령</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Starving Miner Wraith</t>
+          <t>Vicious Miner Wraith</t>
         </is>
       </c>
     </row>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>굶주린 수정골렘</t>
+          <t>표독한 수정골렘</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Starving Crystal Golem</t>
+          <t>Vicious Crystal Golem</t>
         </is>
       </c>
     </row>
@@ -9337,12 +9337,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>굶주린 지네</t>
+          <t>표독한 지네</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Starving Centipede</t>
+          <t>Vicious Centipede</t>
         </is>
       </c>
     </row>
@@ -9354,12 +9354,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>굶주린 이끼괴물</t>
+          <t>표독한 이끼괴물</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Starving Moss Horror</t>
+          <t>Vicious Moss Horror</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>굶주린 석상병</t>
+          <t>표독한 석상병</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Starving Stone Sentry</t>
+          <t>Vicious Stone Sentry</t>
         </is>
       </c>
     </row>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>성난 동굴박쥐</t>
+          <t>흉포한 동굴박쥐</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Enraged Cave Bat</t>
+          <t>Ferocious Cave Bat</t>
         </is>
       </c>
     </row>
@@ -9575,12 +9575,12 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>성난 두더지</t>
+          <t>흉포한 두더지</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Enraged Mole</t>
+          <t>Ferocious Mole</t>
         </is>
       </c>
     </row>
@@ -9592,12 +9592,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>성난 광부망령</t>
+          <t>흉포한 광부망령</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Enraged Miner Wraith</t>
+          <t>Ferocious Miner Wraith</t>
         </is>
       </c>
     </row>
@@ -9609,12 +9609,12 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>성난 수정골렘</t>
+          <t>흉포한 수정골렘</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Enraged Crystal Golem</t>
+          <t>Ferocious Crystal Golem</t>
         </is>
       </c>
     </row>
@@ -9626,12 +9626,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>성난 지네</t>
+          <t>흉포한 지네</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Enraged Centipede</t>
+          <t>Ferocious Centipede</t>
         </is>
       </c>
     </row>
@@ -9643,12 +9643,12 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>성난 이끼괴물</t>
+          <t>흉포한 이끼괴물</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Enraged Moss Horror</t>
+          <t>Ferocious Moss Horror</t>
         </is>
       </c>
     </row>
@@ -9660,12 +9660,12 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>성난 석상병</t>
+          <t>흉포한 석상병</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Enraged Stone Sentry</t>
+          <t>Ferocious Stone Sentry</t>
         </is>
       </c>
     </row>
@@ -9847,12 +9847,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>사나운 동굴박쥐</t>
+          <t>무자비한 동굴박쥐</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Savage Cave Bat</t>
+          <t>Merciless Cave Bat</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>사나운 두더지</t>
+          <t>무자비한 두더지</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Savage Mole</t>
+          <t>Merciless Mole</t>
         </is>
       </c>
     </row>
@@ -9881,12 +9881,12 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>사나운 광부망령</t>
+          <t>무자비한 광부망령</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Savage Miner Wraith</t>
+          <t>Merciless Miner Wraith</t>
         </is>
       </c>
     </row>
@@ -9898,12 +9898,12 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>사나운 수정골렘</t>
+          <t>무자비한 수정골렘</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Savage Crystal Golem</t>
+          <t>Merciless Crystal Golem</t>
         </is>
       </c>
     </row>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>사나운 지네</t>
+          <t>무자비한 지네</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Savage Centipede</t>
+          <t>Merciless Centipede</t>
         </is>
       </c>
     </row>
@@ -9932,12 +9932,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>사나운 이끼괴물</t>
+          <t>무자비한 이끼괴물</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Savage Moss Horror</t>
+          <t>Merciless Moss Horror</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>사나운 석상병</t>
+          <t>무자비한 석상병</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Savage Stone Sentry</t>
+          <t>Merciless Stone Sentry</t>
         </is>
       </c>
     </row>
@@ -10136,12 +10136,12 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>오래된 동굴박쥐</t>
+          <t>풍화된 동굴박쥐</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Ancient Cave Bat</t>
+          <t>Weathered Cave Bat</t>
         </is>
       </c>
     </row>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>오래된 두더지</t>
+          <t>풍화된 두더지</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Ancient Mole</t>
+          <t>Weathered Mole</t>
         </is>
       </c>
     </row>
@@ -10170,12 +10170,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>오래된 광부망령</t>
+          <t>풍화된 광부망령</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Ancient Miner Wraith</t>
+          <t>Weathered Miner Wraith</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>오래된 수정골렘</t>
+          <t>풍화된 수정골렘</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Ancient Crystal Golem</t>
+          <t>Weathered Crystal Golem</t>
         </is>
       </c>
     </row>
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>오래된 지네</t>
+          <t>풍화된 지네</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Ancient Centipede</t>
+          <t>Weathered Centipede</t>
         </is>
       </c>
     </row>
@@ -10221,12 +10221,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>오래된 이끼괴물</t>
+          <t>풍화된 이끼괴물</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Ancient Moss Horror</t>
+          <t>Weathered Moss Horror</t>
         </is>
       </c>
     </row>
@@ -10238,12 +10238,12 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>오래된 석상병</t>
+          <t>풍화된 석상병</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Ancient Stone Sentry</t>
+          <t>Weathered Stone Sentry</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Corrupted Cave Bat</t>
+          <t>Tainted Cave Bat</t>
         </is>
       </c>
     </row>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Corrupted Mole</t>
+          <t>Tainted Mole</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Corrupted Miner Wraith</t>
+          <t>Tainted Miner Wraith</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Corrupted Crystal Golem</t>
+          <t>Tainted Crystal Golem</t>
         </is>
       </c>
     </row>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Corrupted Centipede</t>
+          <t>Tainted Centipede</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Corrupted Moss Horror</t>
+          <t>Tainted Moss Horror</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Corrupted Stone Sentry</t>
+          <t>Tainted Stone Sentry</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Corrupted Shade</t>
+          <t>Tainted Shade</t>
         </is>
       </c>
     </row>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Corrupted Salamander</t>
+          <t>Tainted Salamander</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Corrupted Glow Worm</t>
+          <t>Tainted Glow Worm</t>
         </is>
       </c>
     </row>
@@ -10425,12 +10425,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>타락한 동굴박쥐</t>
+          <t>저주받은 동굴박쥐</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Corrupted Cave Bat</t>
+          <t>Cursed Cave Bat</t>
         </is>
       </c>
     </row>
@@ -10442,12 +10442,12 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>타락한 두더지</t>
+          <t>저주받은 두더지</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Corrupted Mole</t>
+          <t>Cursed Mole</t>
         </is>
       </c>
     </row>
@@ -10459,12 +10459,12 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>타락한 광부망령</t>
+          <t>저주받은 광부망령</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Corrupted Miner Wraith</t>
+          <t>Cursed Miner Wraith</t>
         </is>
       </c>
     </row>
@@ -10476,12 +10476,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>타락한 수정골렘</t>
+          <t>저주받은 수정골렘</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Corrupted Crystal Golem</t>
+          <t>Cursed Crystal Golem</t>
         </is>
       </c>
     </row>
@@ -10493,12 +10493,12 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>타락한 지네</t>
+          <t>저주받은 지네</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Corrupted Centipede</t>
+          <t>Cursed Centipede</t>
         </is>
       </c>
     </row>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>타락한 이끼괴물</t>
+          <t>저주받은 이끼괴물</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Corrupted Moss Horror</t>
+          <t>Cursed Moss Horror</t>
         </is>
       </c>
     </row>
@@ -10527,12 +10527,12 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>타락한 석상병</t>
+          <t>저주받은 석상병</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Corrupted Stone Sentry</t>
+          <t>Cursed Stone Sentry</t>
         </is>
       </c>
     </row>
@@ -10714,12 +10714,12 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>심연의 동굴박쥐</t>
+          <t>공허의 동굴박쥐</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Abyssal Cave Bat</t>
+          <t>Voidtouched Cave Bat</t>
         </is>
       </c>
     </row>
@@ -10731,12 +10731,12 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>심연의 두더지</t>
+          <t>공허의 두더지</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Abyssal Mole</t>
+          <t>Voidtouched Mole</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>심연의 광부망령</t>
+          <t>공허의 광부망령</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Abyssal Miner Wraith</t>
+          <t>Voidtouched Miner Wraith</t>
         </is>
       </c>
     </row>
@@ -10765,12 +10765,12 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>심연의 수정골렘</t>
+          <t>공허의 수정골렘</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Abyssal Crystal Golem</t>
+          <t>Voidtouched Crystal Golem</t>
         </is>
       </c>
     </row>
@@ -10782,12 +10782,12 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>심연의 지네</t>
+          <t>공허의 지네</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Abyssal Centipede</t>
+          <t>Voidtouched Centipede</t>
         </is>
       </c>
     </row>
@@ -10799,12 +10799,12 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>심연의 이끼괴물</t>
+          <t>공허의 이끼괴물</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Abyssal Moss Horror</t>
+          <t>Voidtouched Moss Horror</t>
         </is>
       </c>
     </row>
@@ -10816,12 +10816,12 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>심연의 석상병</t>
+          <t>공허의 석상병</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Abyssal Stone Sentry</t>
+          <t>Voidtouched Stone Sentry</t>
         </is>
       </c>
     </row>
@@ -11003,12 +11003,12 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>왕관을 쓴 동굴박쥐</t>
+          <t>불멸의 동굴박쥐</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Crowned Cave Bat</t>
+          <t>Undying Cave Bat</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>왕관을 쓴 두더지</t>
+          <t>불멸의 두더지</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Crowned Mole</t>
+          <t>Undying Mole</t>
         </is>
       </c>
     </row>
@@ -11037,12 +11037,12 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>왕관을 쓴 광부망령</t>
+          <t>불멸의 광부망령</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Crowned Miner Wraith</t>
+          <t>Undying Miner Wraith</t>
         </is>
       </c>
     </row>
@@ -11054,12 +11054,12 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>왕관을 쓴 수정골렘</t>
+          <t>불멸의 수정골렘</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Crowned Crystal Golem</t>
+          <t>Undying Crystal Golem</t>
         </is>
       </c>
     </row>
@@ -11071,12 +11071,12 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>왕관을 쓴 지네</t>
+          <t>불멸의 지네</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Crowned Centipede</t>
+          <t>Undying Centipede</t>
         </is>
       </c>
     </row>
@@ -11088,12 +11088,12 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>왕관을 쓴 이끼괴물</t>
+          <t>불멸의 이끼괴물</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Crowned Moss Horror</t>
+          <t>Undying Moss Horror</t>
         </is>
       </c>
     </row>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>왕관을 쓴 석상병</t>
+          <t>불멸의 석상병</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Crowned Stone Sentry</t>
+          <t>Undying Stone Sentry</t>
         </is>
       </c>
     </row>
@@ -11292,12 +11292,12 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>전설의 동굴박쥐</t>
+          <t>태초의 동굴박쥐</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Legendary Cave Bat</t>
+          <t>Primordial Cave Bat</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>전설의 두더지</t>
+          <t>태초의 두더지</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Legendary Mole</t>
+          <t>Primordial Mole</t>
         </is>
       </c>
     </row>
@@ -11326,12 +11326,12 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>전설의 광부망령</t>
+          <t>태초의 광부망령</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Legendary Miner Wraith</t>
+          <t>Primordial Miner Wraith</t>
         </is>
       </c>
     </row>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>전설의 수정골렘</t>
+          <t>태초의 수정골렘</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Legendary Crystal Golem</t>
+          <t>Primordial Crystal Golem</t>
         </is>
       </c>
     </row>
@@ -11360,12 +11360,12 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>전설의 지네</t>
+          <t>태초의 지네</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Legendary Centipede</t>
+          <t>Primordial Centipede</t>
         </is>
       </c>
     </row>
@@ -11377,12 +11377,12 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>전설의 이끼괴물</t>
+          <t>태초의 이끼괴물</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Legendary Moss Horror</t>
+          <t>Primordial Moss Horror</t>
         </is>
       </c>
     </row>
@@ -11394,12 +11394,12 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>전설의 석상병</t>
+          <t>태초의 석상병</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Legendary Stone Sentry</t>
+          <t>Primordial Stone Sentry</t>
         </is>
       </c>
     </row>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>어린 망령</t>
+          <t>설익은 망령</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Young Revenant</t>
+          <t>Callow Revenant</t>
         </is>
       </c>
     </row>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>어린 석상기사</t>
+          <t>설익은 석상기사</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Young Stone Knight</t>
+          <t>Callow Stone Knight</t>
         </is>
       </c>
     </row>
@@ -11615,12 +11615,12 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>어린 타락사제</t>
+          <t>설익은 타락사제</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Young Fallen Priest</t>
+          <t>Callow Fallen Priest</t>
         </is>
       </c>
     </row>
@@ -11632,12 +11632,12 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>어린 키메라</t>
+          <t>설익은 키메라</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Young Chimera</t>
+          <t>Callow Chimera</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>어린 가고일</t>
+          <t>설익은 가고일</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Young Gargoyle</t>
+          <t>Callow Gargoyle</t>
         </is>
       </c>
     </row>
@@ -11666,12 +11666,12 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>어린 수호자</t>
+          <t>설익은 수호자</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Young Warden</t>
+          <t>Callow Warden</t>
         </is>
       </c>
     </row>
@@ -11853,12 +11853,12 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>거친 망령</t>
+          <t>억센 망령</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Feral Revenant</t>
+          <t>Sturdy Revenant</t>
         </is>
       </c>
     </row>
@@ -11870,12 +11870,12 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>거친 석상기사</t>
+          <t>억센 석상기사</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Feral Stone Knight</t>
+          <t>Sturdy Stone Knight</t>
         </is>
       </c>
     </row>
@@ -11887,12 +11887,12 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>거친 타락사제</t>
+          <t>억센 타락사제</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Feral Fallen Priest</t>
+          <t>Sturdy Fallen Priest</t>
         </is>
       </c>
     </row>
@@ -11904,12 +11904,12 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>거친 키메라</t>
+          <t>억센 키메라</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Feral Chimera</t>
+          <t>Sturdy Chimera</t>
         </is>
       </c>
     </row>
@@ -11921,12 +11921,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>거친 가고일</t>
+          <t>억센 가고일</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Feral Gargoyle</t>
+          <t>Sturdy Gargoyle</t>
         </is>
       </c>
     </row>
@@ -11938,12 +11938,12 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>거친 수호자</t>
+          <t>억센 수호자</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Feral Warden</t>
+          <t>Sturdy Warden</t>
         </is>
       </c>
     </row>
@@ -12125,12 +12125,12 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>굶주린 망령</t>
+          <t>표독한 망령</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Starving Revenant</t>
+          <t>Vicious Revenant</t>
         </is>
       </c>
     </row>
@@ -12142,12 +12142,12 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>굶주린 석상기사</t>
+          <t>표독한 석상기사</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Starving Stone Knight</t>
+          <t>Vicious Stone Knight</t>
         </is>
       </c>
     </row>
@@ -12159,12 +12159,12 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>굶주린 타락사제</t>
+          <t>표독한 타락사제</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Starving Fallen Priest</t>
+          <t>Vicious Fallen Priest</t>
         </is>
       </c>
     </row>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>굶주린 키메라</t>
+          <t>표독한 키메라</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Starving Chimera</t>
+          <t>Vicious Chimera</t>
         </is>
       </c>
     </row>
@@ -12193,12 +12193,12 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>굶주린 가고일</t>
+          <t>표독한 가고일</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Starving Gargoyle</t>
+          <t>Vicious Gargoyle</t>
         </is>
       </c>
     </row>
@@ -12210,12 +12210,12 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>굶주린 수호자</t>
+          <t>표독한 수호자</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Starving Warden</t>
+          <t>Vicious Warden</t>
         </is>
       </c>
     </row>
@@ -12397,12 +12397,12 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>성난 망령</t>
+          <t>흉포한 망령</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Enraged Revenant</t>
+          <t>Ferocious Revenant</t>
         </is>
       </c>
     </row>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>성난 석상기사</t>
+          <t>흉포한 석상기사</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Enraged Stone Knight</t>
+          <t>Ferocious Stone Knight</t>
         </is>
       </c>
     </row>
@@ -12431,12 +12431,12 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>성난 타락사제</t>
+          <t>흉포한 타락사제</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Enraged Fallen Priest</t>
+          <t>Ferocious Fallen Priest</t>
         </is>
       </c>
     </row>
@@ -12448,12 +12448,12 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>성난 키메라</t>
+          <t>흉포한 키메라</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Enraged Chimera</t>
+          <t>Ferocious Chimera</t>
         </is>
       </c>
     </row>
@@ -12465,12 +12465,12 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>성난 가고일</t>
+          <t>흉포한 가고일</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Enraged Gargoyle</t>
+          <t>Ferocious Gargoyle</t>
         </is>
       </c>
     </row>
@@ -12482,12 +12482,12 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>성난 수호자</t>
+          <t>흉포한 수호자</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Enraged Warden</t>
+          <t>Ferocious Warden</t>
         </is>
       </c>
     </row>
@@ -12669,12 +12669,12 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>사나운 망령</t>
+          <t>무자비한 망령</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Savage Revenant</t>
+          <t>Merciless Revenant</t>
         </is>
       </c>
     </row>
@@ -12686,12 +12686,12 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>사나운 석상기사</t>
+          <t>무자비한 석상기사</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Savage Stone Knight</t>
+          <t>Merciless Stone Knight</t>
         </is>
       </c>
     </row>
@@ -12703,12 +12703,12 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>사나운 타락사제</t>
+          <t>무자비한 타락사제</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Savage Fallen Priest</t>
+          <t>Merciless Fallen Priest</t>
         </is>
       </c>
     </row>
@@ -12720,12 +12720,12 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>사나운 키메라</t>
+          <t>무자비한 키메라</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Savage Chimera</t>
+          <t>Merciless Chimera</t>
         </is>
       </c>
     </row>
@@ -12737,12 +12737,12 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>사나운 가고일</t>
+          <t>무자비한 가고일</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>Savage Gargoyle</t>
+          <t>Merciless Gargoyle</t>
         </is>
       </c>
     </row>
@@ -12754,12 +12754,12 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>사나운 수호자</t>
+          <t>무자비한 수호자</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Savage Warden</t>
+          <t>Merciless Warden</t>
         </is>
       </c>
     </row>
@@ -12941,12 +12941,12 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>오래된 망령</t>
+          <t>풍화된 망령</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Ancient Revenant</t>
+          <t>Weathered Revenant</t>
         </is>
       </c>
     </row>
@@ -12958,12 +12958,12 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>오래된 석상기사</t>
+          <t>풍화된 석상기사</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Ancient Stone Knight</t>
+          <t>Weathered Stone Knight</t>
         </is>
       </c>
     </row>
@@ -12975,12 +12975,12 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>오래된 타락사제</t>
+          <t>풍화된 타락사제</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Ancient Fallen Priest</t>
+          <t>Weathered Fallen Priest</t>
         </is>
       </c>
     </row>
@@ -12992,12 +12992,12 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>오래된 키메라</t>
+          <t>풍화된 키메라</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Ancient Chimera</t>
+          <t>Weathered Chimera</t>
         </is>
       </c>
     </row>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>오래된 가고일</t>
+          <t>풍화된 가고일</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Ancient Gargoyle</t>
+          <t>Weathered Gargoyle</t>
         </is>
       </c>
     </row>
@@ -13026,12 +13026,12 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>오래된 수호자</t>
+          <t>풍화된 수호자</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Ancient Warden</t>
+          <t>Weathered Warden</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Corrupted Revenant</t>
+          <t>Tainted Revenant</t>
         </is>
       </c>
     </row>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>Corrupted Stone Knight</t>
+          <t>Tainted Stone Knight</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Corrupted Fallen Priest</t>
+          <t>Tainted Fallen Priest</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Corrupted Chimera</t>
+          <t>Tainted Chimera</t>
         </is>
       </c>
     </row>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Corrupted Gargoyle</t>
+          <t>Tainted Gargoyle</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>Corrupted Warden</t>
+          <t>Tainted Warden</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>Corrupted Phantasm</t>
+          <t>Tainted Phantasm</t>
         </is>
       </c>
     </row>
@@ -13167,7 +13167,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Corrupted Tainted Spirit</t>
+          <t>Tainted Tainted Spirit</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Corrupted Altar Ward</t>
+          <t>Tainted Altar Ward</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Corrupted Void Thing</t>
+          <t>Tainted Void Thing</t>
         </is>
       </c>
     </row>
@@ -13213,12 +13213,12 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>타락한 망령</t>
+          <t>저주받은 망령</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>Corrupted Revenant</t>
+          <t>Cursed Revenant</t>
         </is>
       </c>
     </row>
@@ -13230,12 +13230,12 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>타락한 석상기사</t>
+          <t>저주받은 석상기사</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Corrupted Stone Knight</t>
+          <t>Cursed Stone Knight</t>
         </is>
       </c>
     </row>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>타락한 타락사제</t>
+          <t>저주받은 타락사제</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Corrupted Fallen Priest</t>
+          <t>Cursed Fallen Priest</t>
         </is>
       </c>
     </row>
@@ -13264,12 +13264,12 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>타락한 키메라</t>
+          <t>저주받은 키메라</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Corrupted Chimera</t>
+          <t>Cursed Chimera</t>
         </is>
       </c>
     </row>
@@ -13281,12 +13281,12 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>타락한 가고일</t>
+          <t>저주받은 가고일</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Corrupted Gargoyle</t>
+          <t>Cursed Gargoyle</t>
         </is>
       </c>
     </row>
@@ -13298,12 +13298,12 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>타락한 수호자</t>
+          <t>저주받은 수호자</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>Corrupted Warden</t>
+          <t>Cursed Warden</t>
         </is>
       </c>
     </row>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>심연의 망령</t>
+          <t>공허의 망령</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Abyssal Revenant</t>
+          <t>Voidtouched Revenant</t>
         </is>
       </c>
     </row>
@@ -13502,12 +13502,12 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>심연의 석상기사</t>
+          <t>공허의 석상기사</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Abyssal Stone Knight</t>
+          <t>Voidtouched Stone Knight</t>
         </is>
       </c>
     </row>
@@ -13519,12 +13519,12 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>심연의 타락사제</t>
+          <t>공허의 타락사제</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Abyssal Fallen Priest</t>
+          <t>Voidtouched Fallen Priest</t>
         </is>
       </c>
     </row>
@@ -13536,12 +13536,12 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>심연의 키메라</t>
+          <t>공허의 키메라</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Abyssal Chimera</t>
+          <t>Voidtouched Chimera</t>
         </is>
       </c>
     </row>
@@ -13553,12 +13553,12 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>심연의 가고일</t>
+          <t>공허의 가고일</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Abyssal Gargoyle</t>
+          <t>Voidtouched Gargoyle</t>
         </is>
       </c>
     </row>
@@ -13570,12 +13570,12 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>심연의 수호자</t>
+          <t>공허의 수호자</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Abyssal Warden</t>
+          <t>Voidtouched Warden</t>
         </is>
       </c>
     </row>
@@ -13757,12 +13757,12 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>왕관을 쓴 망령</t>
+          <t>불멸의 망령</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Crowned Revenant</t>
+          <t>Undying Revenant</t>
         </is>
       </c>
     </row>
@@ -13774,12 +13774,12 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>왕관을 쓴 석상기사</t>
+          <t>불멸의 석상기사</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Crowned Stone Knight</t>
+          <t>Undying Stone Knight</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>왕관을 쓴 타락사제</t>
+          <t>불멸의 타락사제</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Crowned Fallen Priest</t>
+          <t>Undying Fallen Priest</t>
         </is>
       </c>
     </row>
@@ -13808,12 +13808,12 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>왕관을 쓴 키메라</t>
+          <t>불멸의 키메라</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Crowned Chimera</t>
+          <t>Undying Chimera</t>
         </is>
       </c>
     </row>
@@ -13825,12 +13825,12 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>왕관을 쓴 가고일</t>
+          <t>불멸의 가고일</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Crowned Gargoyle</t>
+          <t>Undying Gargoyle</t>
         </is>
       </c>
     </row>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>왕관을 쓴 수호자</t>
+          <t>불멸의 수호자</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Crowned Warden</t>
+          <t>Undying Warden</t>
         </is>
       </c>
     </row>
@@ -14029,12 +14029,12 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>전설의 망령</t>
+          <t>태초의 망령</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Legendary Revenant</t>
+          <t>Primordial Revenant</t>
         </is>
       </c>
     </row>
@@ -14046,12 +14046,12 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>전설의 석상기사</t>
+          <t>태초의 석상기사</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Legendary Stone Knight</t>
+          <t>Primordial Stone Knight</t>
         </is>
       </c>
     </row>
@@ -14063,12 +14063,12 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>전설의 타락사제</t>
+          <t>태초의 타락사제</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Legendary Fallen Priest</t>
+          <t>Primordial Fallen Priest</t>
         </is>
       </c>
     </row>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>전설의 키메라</t>
+          <t>태초의 키메라</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Legendary Chimera</t>
+          <t>Primordial Chimera</t>
         </is>
       </c>
     </row>
@@ -14097,12 +14097,12 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>전설의 가고일</t>
+          <t>태초의 가고일</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Legendary Gargoyle</t>
+          <t>Primordial Gargoyle</t>
         </is>
       </c>
     </row>
@@ -14114,12 +14114,12 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>전설의 수호자</t>
+          <t>태초의 수호자</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Legendary Warden</t>
+          <t>Primordial Warden</t>
         </is>
       </c>
     </row>
@@ -21778,6 +21778,1060 @@
       <c r="C1247" t="inlineStr">
         <is>
           <t>SELL?</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>MonSkillSlimeName</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>점액 분출</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Ooze Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>MonSkillSlimeDesc</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>끈적한 점액을 뿜어 발을 묶는다.</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Spews clinging ooze that fouls your footing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>MonSkillGoblinName</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>잽싼 찌르기</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Quick Jab</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>MonSkillGoblinDesc</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>짧고 빠르게 찔러 넣는다.</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Jabs short and fast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>MonSkillForestSpiderName</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>거미줄 결박</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Web Snare</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>MonSkillForestSpiderDesc</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>거미줄을 쏘아 움직임을 옭아맨다.</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Fires webbing that binds movement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>MonSkillWildWolfName</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>무리 사냥</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Pack Hunt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>MonSkillWildWolfDesc</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>동료가 가까울수록 사납게 문다.</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Bites harder while its pack is near.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>MonSkillToadstoolName</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>포자 살포</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Spore Cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>MonSkillToadstoolDesc</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>독 포자를 흩뿌려 서서히 갉아먹는다.</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Scatters toxic spores that gnaw slowly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>MonSkillWindSpriteName</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>질풍 베기</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Galecut</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>MonSkillWindSpriteDesc</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>바람에 날을 세워 먼 곳까지 벤다.</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>Hones the wind to a blade and cuts at range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>MonSkillBoarName</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>저돌 돌진</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Reckless Charge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>MonSkillBoarDesc</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>머리를 숙이고 곧장 들이받는다.</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Lowers its head and barrels straight in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>MonSkillCrowName</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>눈 쪼기</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Eye Peck</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>MonSkillCrowDesc</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>눈을 노려 쪼아 조준을 흐린다.</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Pecks at the eyes to spoil your aim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>MonSkillCreeperName</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>덩굴 옭아매기</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Vine Grasp</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>MonSkillCreeperDesc</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>땅에서 덩굴을 뻗어 발목을 감는다.</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>Sends vines up to coil around your ankles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>MonSkillFoxName</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>홀리는 걸음</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Beguiling Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>MonSkillFoxDesc</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>종잡을 수 없는 걸음으로 공격을 흘린다.</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Slips attacks with an unreadable gait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>MonSkillHornetName</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>연속 침</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Stinger Flurry</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>MonSkillHornetDesc</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>짧은 간격으로 거듭 찌른다.</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Stabs again and again in quick succession.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>MonSkillCaveBatName</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>초음파 교란</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Sonic Jolt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>MonSkillCaveBatDesc</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>음파를 쏘아 감각을 어지럽힌다.</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Looses a shriek that scrambles the senses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>MonSkillMoleName</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>굴파기 기습</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Burrow Ambush</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>MonSkillMoleDesc</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>땅을 파고들어 발밑에서 솟는다.</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Tunnels under and erupts beneath you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>MonSkillMinerWraithName</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>곡괭이 원한</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Grudge Pick</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>MonSkillMinerWraithDesc</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>생전의 곡괭이를 원한 실어 내리친다.</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Swings its old pick, heavy with grudge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>MonSkillCrystalGolemName</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>수정 갑피</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Crystal Carapace</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>MonSkillCrystalGolemDesc</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>수정 껍질이 충격을 흩어 버린다.</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>A crystal shell scatters the impact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>MonSkillCentipedeName</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>다발 물기</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Manyfold Bite</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>MonSkillCentipedeDesc</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>수많은 다리로 붙어 연달아 문다.</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Clings with many legs and bites in series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>MonSkillMossHorrorName</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>습지 포옹</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Bog Embrace</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>MonSkillMossHorrorDesc</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>축축한 몸으로 감싸 움직임을 늦춘다.</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Wraps you in sodden bulk and slows you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>MonSkillStoneSentryName</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>석화 응시</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Petrifying Gaze</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>MonSkillStoneSentryDesc</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>돌처럼 굳은 시선으로 노려본다.</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Fixes you with a gaze gone to stone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>MonSkillShadeName</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>그림자 잠행</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Shadowslip</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>MonSkillShadeDesc</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>그림자에 스며 공격을 비껴간다.</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Melts into shadow and lets blows pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>MonSkillSalamanderName</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>불꽃 숨</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Ember Breath</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>MonSkillSalamanderDesc</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>달아오른 숨을 내뿜는다.</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Exhales a breath gone red with heat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>MonSkillGlowWormName</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>현혹의 빛</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Dazzling Glow</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>MonSkillGlowWormDesc</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>눈부신 빛으로 조준을 흐트러뜨린다.</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Blooms with light that ruins your aim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>MonSkillRevenantName</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>원혼의 손길</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Wraithtouch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>MonSkillRevenantDesc</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>차가운 손이 방어를 지나 스민다.</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>A cold hand seeps past your guard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>MonSkillStoneKnightName</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>방패 밀치기</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Shield Bash</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>MonSkillStoneKnightDesc</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>거대한 방패로 밀어붙인다.</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Drives forward behind a vast shield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>MonSkillFallenPriestName</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>뒤틀린 기도</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Twisted Prayer</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>MonSkillFallenPriestDesc</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>일그러진 기도가 상처를 벌린다.</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>A warped prayer pries your wounds open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>MonSkillChimeraName</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>세 갈래 이빨</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Trifang</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>MonSkillChimeraDesc</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>세 머리가 번갈아 물어뜯는다.</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Three heads tear at you in turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>MonSkillGargoyleName</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>석익 강하</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Stonewing Dive</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>MonSkillGargoyleDesc</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>돌 날개로 급강하해 내리찍는다.</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Folds its stone wings and dives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>MonSkillWardenName</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>봉인의 일격</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Sealing Blow</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>MonSkillWardenDesc</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>봉인의 힘을 실어 내리친다.</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Brings down a blow weighted with wards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>MonSkillPhantasmName</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>허상 분열</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Mirage Split</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>MonSkillPhantasmDesc</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>허상을 만들어 공격을 흘린다.</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Splits into mirages and sheds your blows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>MonSkillTaintedSpiritName</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>오염된 바람</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Blighted Gale</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>MonSkillTaintedSpiritDesc</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>썩은 바람이 살갗을 태운다.</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>A rotten wind sears the skin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>MonSkillAltarWardName</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>제단의 진노</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Altar's Wrath</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>MonSkillAltarWardDesc</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>제단을 건드린 자에게 진노를 내린다.</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Visits wrath on those who touch the altar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>MonSkillVoidThingName</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>공허 삼킴</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Void Swallow</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>MonSkillVoidThingDesc</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>닿는 것을 공허로 빨아들인다.</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Draws whatever it touches into the void.</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>당신는(은) 매력발산!를(을) 사용했다!</t>
+          <t>매력을 발산해 미니몬의 관심을 끌었다!</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4920,12 +4920,18 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>젤리 퐁의 고유기술. 최대 체력을 늘린다.</t>
+          <t>기본 효과: 단계당 최대 체력 +30.
+수동 사용: 최대 체력의 18% × 능력 단계만큼 회복한다.
+재사용 18초(미니몬 능력끼리 공유).
+동행 중 임시 사용 가능. 공명도 100%에서 영구 습득.</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Jelly Pong's unique skill. Increases max HP.</t>
+          <t>Passive: +30 maximum HP per ability level.
+Manual use: Restore 18% of maximum HP per ability level.
+Cooldown: 18s, shared by minion abilities.
+Available temporarily while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
     </row>
@@ -4973,12 +4979,18 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>라비 슬라임의 고유기술. 공격속도를 높인다.</t>
+          <t>기본 효과: 단계당 공격속도 +10%p.
+수동 사용: 8초 동안 공격속도가 30%p × 능력 단계만큼 오른다.
+재사용 18초(미니몬 능력끼리 공유).
+동행 중 임시 사용 가능. 공명도 100%에서 영구 습득.</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Rabi Slime's unique skill. Increases attack speed.</t>
+          <t>Passive: +10 percentage points of attack speed per ability level.
+Manual use: Gain 30 percentage points of attack speed per ability level for 8 seconds.
+Cooldown: 18s, shared by minion abilities.
+Available temporarily while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1840"/>
+  <dimension ref="A1:C1845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33797,6 +33797,91 @@
         </is>
       </c>
     </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>CombatAbilityReadyText</t>
+        </is>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>눌러서 사용</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>Tap to use</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>CombatAbilityCooldownText</t>
+        </is>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>재사용 대기</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>Cooling down</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>CombatAbilityFullHpText</t>
+        </is>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>체력이 가득합니다</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>Health is full</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>CombatAbilityNoTargetText</t>
+        </is>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>적을 기다리는 중</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>Waiting for a target</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>CombatAbilityUnavailableText</t>
+        </is>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>지금은 사용할 수 없습니다</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>Unavailable</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1845"/>
+  <dimension ref="A1:C1851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33882,6 +33882,110 @@
         </is>
       </c>
     </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>Equip30061NameText</t>
+        </is>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>견습생의 장검</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>Apprentice Longsword</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>Equip30062NameText</t>
+        </is>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>견습생의 세검</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>Apprentice Rapier</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>GrowthClassGuideText</t>
+        </is>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>처치마다 숙련도 +1
+100이면 축성 가능</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>Kills: +1 proficiency
+Anoint at 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>GrowthMaterialHintText</t>
+        </is>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>재료 이름을 누르면 획득 장소를 확인합니다.</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>Tap a material to see where to find it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>GrowthItemRarityLabelText</t>
+        </is>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>등급:</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>Rarity:</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>GrowthItemFoundLabelText</t>
+        </is>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>발견장소:</t>
+        </is>
+      </c>
+      <c r="C1851" t="inlineStr">
+        <is>
+          <t>Found:</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1851"/>
+  <dimension ref="A1:C1878"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>최대 체력을 증가시킨다.</t>
+          <t>최대 체력과 방어력이 오른다.</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Increases max HP.</t>
+          <t>Increases max HP and defense.</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Physical attack rises for a while at battle start.</t>
+          <t>Increases physical attack briefly when entering a battle area.</t>
         </is>
       </c>
     </row>
@@ -15576,7 +15576,7 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>선제의 감각</t>
+          <t>First Strike Instinct</t>
         </is>
       </c>
     </row>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>전투 시작 시 60% 확률로 공격력이 잠시 오른다</t>
+          <t>A 60% chance to briefly increase physical attack when entering a battle area.</t>
         </is>
       </c>
     </row>
@@ -15746,7 +15746,7 @@
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>연쇄 각성</t>
+          <t>Chain Awakening</t>
         </is>
       </c>
     </row>
@@ -15763,7 +15763,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>연속 3회 치명타 시 큰 피해를 추가한다</t>
+          <t>Deals bonus damage after three consecutive critical hits.</t>
         </is>
       </c>
     </row>
@@ -15882,7 +15882,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>그림자 걸음</t>
+          <t>Shadow Step</t>
         </is>
       </c>
     </row>
@@ -15899,7 +15899,7 @@
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>연속 3회 회피 시 회피율이 크게 오른다</t>
+          <t>Briefly increases evasion after three consecutive dodges.</t>
         </is>
       </c>
     </row>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>불굴</t>
+          <t>Indomitable</t>
         </is>
       </c>
     </row>
@@ -16030,12 +16030,12 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>치명상을 입을 때 40% 확률로 체력을 회복하며 버틴다</t>
+          <t>치명 피해를 받기 직전 40% 확률로 체력을 회복한다.</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>치명상을 입을 때 40% 확률로 체력을 회복하며 버틴다</t>
+          <t>A 40% chance to restore HP just before taking an otherwise fatal hit.</t>
         </is>
       </c>
     </row>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>각성</t>
+          <t>Awakening</t>
         </is>
       </c>
     </row>
@@ -16137,7 +16137,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>18초마다 공격력이 잠시 오른다</t>
+          <t>Briefly increases physical attack every 18 seconds while in battle.</t>
         </is>
       </c>
     </row>
@@ -16290,7 +16290,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>잔상</t>
+          <t>Afterimage</t>
         </is>
       </c>
     </row>
@@ -16307,7 +16307,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>17초마다 회피율이 잠시 오른다</t>
+          <t>Briefly increases evasion every 17 seconds while in battle.</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>강인함</t>
+          <t>Fortitude</t>
         </is>
       </c>
     </row>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>최대 체력이 오른다</t>
+          <t>Increases max HP.</t>
         </is>
       </c>
     </row>
@@ -16630,7 +16630,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>민첩</t>
+          <t>Agility</t>
         </is>
       </c>
     </row>
@@ -16647,7 +16647,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>회피율이 오른다</t>
+          <t>Increases evasion.</t>
         </is>
       </c>
     </row>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>각인</t>
+          <t>Imprint</t>
         </is>
       </c>
     </row>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>확정 포획에 필요한 횟수가 줄어든다</t>
+          <t>Reduces the number of attempts needed for a guaranteed capture.</t>
         </is>
       </c>
     </row>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>연계 감각</t>
+          <t>Combo Instinct</t>
         </is>
       </c>
     </row>
@@ -17016,12 +17016,12 @@
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>콤보 게이지가 더 오래 유지된다</t>
+          <t>콤보 유지 시간이 늘어난다.</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>콤보 게이지가 더 오래 유지된다</t>
+          <t>Extends the time before a combo expires.</t>
         </is>
       </c>
     </row>
@@ -33983,6 +33983,465 @@
       <c r="C1851" t="inlineStr">
         <is>
           <t>Found:</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>ClassAbilityCurrentFormat</t>
+        </is>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>현재 {0}단계</t>
+        </is>
+      </c>
+      <c r="C1852" t="inlineStr">
+        <is>
+          <t>Current level {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>ClassAbilityAcquisitionFormat</t>
+        </is>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>습득 시 {0}단계</t>
+        </is>
+      </c>
+      <c r="C1853" t="inlineStr">
+        <is>
+          <t>Upon learning: level {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>ClassAbilityNextFormat</t>
+        </is>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>다음 {0}단계</t>
+        </is>
+      </c>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>Next level {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>ClassAbilityFlatStatFormat</t>
+        </is>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>{0} +{1}</t>
+        </is>
+      </c>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>{0} +{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>ClassAbilityPercentPointFormat</t>
+        </is>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>{0} +{1}%p</t>
+        </is>
+      </c>
+      <c r="C1856" t="inlineStr">
+        <is>
+          <t>{0} +{1} percentage points</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>ClassAbilityComboFormat</t>
+        </is>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>콤보 유지 시간 +{0}%</t>
+        </is>
+      </c>
+      <c r="C1857" t="inlineStr">
+        <is>
+          <t>Combo duration +{0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>ClassAbilityCaptureFormat</t>
+        </is>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>확정 포획에 필요한 실패 횟수 -{0}</t>
+        </is>
+      </c>
+      <c r="C1858" t="inlineStr">
+        <is>
+          <t>Failures needed for a guaranteed catch -{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>ClassAbilityChanceFormat</t>
+        </is>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>{0}% 확률로 발동</t>
+        </is>
+      </c>
+      <c r="C1859" t="inlineStr">
+        <is>
+          <t>{0}% chance to activate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>ClassAbilityIntervalFormat</t>
+        </is>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>{0}, 재사용 대기 {1}초</t>
+        </is>
+      </c>
+      <c r="C1860" t="inlineStr">
+        <is>
+          <t>{0}, cooldown {1}s</t>
+        </is>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>ClassAbilityHealFormat</t>
+        </is>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>HP {0} 회복</t>
+        </is>
+      </c>
+      <c r="C1861" t="inlineStr">
+        <is>
+          <t>Restore {0} HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>ClassAbilityDamageFormat</t>
+        </is>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>추가 피해 {0}</t>
+        </is>
+      </c>
+      <c r="C1862" t="inlineStr">
+        <is>
+          <t>Deal {0} bonus damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>ClassAbilityHealRatioFormat</t>
+        </is>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>{0}의 {1}%만큼 HP 회복</t>
+        </is>
+      </c>
+      <c r="C1863" t="inlineStr">
+        <is>
+          <t>Restore HP equal to {1}% of {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>ClassAbilityDamageRatioFormat</t>
+        </is>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>{0}의 {1}%만큼 추가 피해</t>
+        </is>
+      </c>
+      <c r="C1864" t="inlineStr">
+        <is>
+          <t>Deal bonus damage equal to {1}% of {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>ClassAbilityDurationFormat</t>
+        </is>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>{0} ({1}초)</t>
+        </is>
+      </c>
+      <c r="C1865" t="inlineStr">
+        <is>
+          <t>{0} ({1}s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>ClassAbilityUntilBattleEndFormat</t>
+        </is>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>{0} (전투 종료까지)</t>
+        </is>
+      </c>
+      <c r="C1866" t="inlineStr">
+        <is>
+          <t>{0} (until battle ends)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>ClassAbilityBattleStartText</t>
+        </is>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>지역 전투 시작 시</t>
+        </is>
+      </c>
+      <c r="C1867" t="inlineStr">
+        <is>
+          <t>At the start of an area's battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>ClassAbilityConsecutiveCritFormat</t>
+        </is>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>{0}회 연속 치명타 시</t>
+        </is>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>After {0} consecutive critical hits</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>ClassAbilityConsecutiveEvadeFormat</t>
+        </is>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>{0}회 연속 회피 시</t>
+        </is>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t>After {0} consecutive evades</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>ClassAbilityFatalDamageText</t>
+        </is>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>치명적인 피해를 받기 직전</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>Before taking lethal damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>ClassAbilityInBattleText</t>
+        </is>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>전투 중 자동 발동</t>
+        </is>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t>Activates automatically in battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>ClassAbilityOutOfBattleText</t>
+        </is>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>비전투 중 자동 발동</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>Activates automatically outside battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>ClassAbilityAlwaysText</t>
+        </is>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>항상 자동 발동</t>
+        </is>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>Activates automatically at any time</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>ClassAbilityOrText</t>
+        </is>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 또는 </t>
+        </is>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> or </t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>ClassAbilityMaxHpText</t>
+        </is>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>최대 HP</t>
+        </is>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>Max HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>ClassAbilityDefText</t>
+        </is>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>방어력</t>
+        </is>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>Defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>ClassAbilityEvasionText</t>
+        </is>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>회피율</t>
+        </is>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t>Evasion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>ClassAbilityPhysicalAtkText</t>
+        </is>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>물리 공격력</t>
+        </is>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>Physical attack</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1878"/>
+  <dimension ref="A1:C1946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>[아직 내용이 없습니다.]</t>
+          <t>[No description yet.]</t>
         </is>
       </c>
     </row>
@@ -5178,8 +5178,8 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>발자국의 깊이, 숨결의 결.
- 사냥꾼은 직감으로 안다.</t>
+          <t>The depth of a footprint, the grain of a breath.
+ A hunter knows by instinct.</t>
         </is>
       </c>
     </row>
@@ -5231,8 +5231,8 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>급할수록 돌아가라.
- 허나 길은 점점 짧아진다.</t>
+          <t>When in haste, take the long way around.
+ Yet the road keeps growing shorter.</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>걸어온 길은 모두 양분이 된다.</t>
+          <t>Every road you have walked becomes nourishment.</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>한 길만 걷지 않은 자의 흔적.</t>
+          <t>The mark of one who walked more than one path.</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>두 갈래의 길을 함께 걷는다.</t>
+          <t>Walking two diverging paths side by side.</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>모든 길의 끝에서 만나는 자.</t>
+          <t>The one you meet at the end of every road.</t>
         </is>
       </c>
     </row>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>연격의 습관</t>
+          <t>Flurry Habit</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>공격 시 25% 확률로 추가 피해를 준다</t>
+          <t>A 25% chance to deal bonus damage when attacking.</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>잔심</t>
+          <t>Lingering Focus</t>
         </is>
       </c>
     </row>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>공격 후 30% 확률로 다음 일격이 날카로워진다</t>
+          <t>A 30% chance for your next strike to become sharper after attacking.</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>타격 감각</t>
+          <t>Impact Sense</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>타격 시 20% 확률로 체력을 조금 회복한다</t>
+          <t>A 20% chance to restore a little HP when landing a hit.</t>
         </is>
       </c>
     </row>
@@ -15712,7 +15712,7 @@
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>치명의 흐름</t>
+          <t>Critical Flow</t>
         </is>
       </c>
     </row>
@@ -15729,7 +15729,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>치명타 시 45% 확률로 공격속도가 오른다</t>
+          <t>A 45% chance to increase attack speed on a critical hit.</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15780,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>빗나감의 교훈</t>
+          <t>Lesson of a Miss</t>
         </is>
       </c>
     </row>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>빗나갈 때 70% 확률로 명중이 오른다</t>
+          <t>A 70% chance to increase accuracy when an attack misses.</t>
         </is>
       </c>
     </row>
@@ -15814,7 +15814,7 @@
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>간파</t>
+          <t>Insight</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>상대가 회피하면 50% 확률로 치명타율이 오른다</t>
+          <t>A 50% chance to increase critical rate when the enemy dodges.</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>흘리기</t>
+          <t>Deflection</t>
         </is>
       </c>
     </row>
@@ -15865,7 +15865,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>회피에 성공하면 55% 확률로 반격 피해를 준다</t>
+          <t>A 55% chance to deal counter damage after a successful dodge.</t>
         </is>
       </c>
     </row>
@@ -15916,7 +15916,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>굳은 살</t>
+          <t>Toughened Skin</t>
         </is>
       </c>
     </row>
@@ -15933,7 +15933,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>피격 시 35% 확률로 방어가 단단해진다</t>
+          <t>A 35% chance to harden your defense when hit.</t>
         </is>
       </c>
     </row>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>벼랑 끝</t>
+          <t>On the Brink</t>
         </is>
       </c>
     </row>
@@ -15967,7 +15967,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>체력이 30% 이하가 되면 공격력이 크게 오른다</t>
+          <t>Greatly increases physical attack when HP falls to 30% or below.</t>
         </is>
       </c>
     </row>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>숨통</t>
+          <t>Coup de Grace</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16001,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>상대 체력이 30% 이하일 때 추가 피해를 준다</t>
+          <t>Deals bonus damage when the enemy's HP is 30% or below.</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>회복의 여운</t>
+          <t>Healing Afterglow</t>
         </is>
       </c>
     </row>
@@ -16069,7 +16069,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>회복할 때 50% 확률로 방어가 오른다</t>
+          <t>A 50% chance to increase defense when you recover HP.</t>
         </is>
       </c>
     </row>
@@ -16086,7 +16086,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>전투 호흡</t>
+          <t>Combat Breathing</t>
         </is>
       </c>
     </row>
@@ -16103,7 +16103,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>12초마다 체력을 회복한다</t>
+          <t>Restores HP every 12 seconds while in battle.</t>
         </is>
       </c>
     </row>
@@ -16154,7 +16154,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>집중</t>
+          <t>Focus</t>
         </is>
       </c>
     </row>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>16초마다 치명타율이 잠시 오른다</t>
+          <t>Briefly increases critical rate every 16 seconds while in battle.</t>
         </is>
       </c>
     </row>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>가속</t>
+          <t>Acceleration</t>
         </is>
       </c>
     </row>
@@ -16205,7 +16205,7 @@
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>15초마다 공격속도가 잠시 오른다</t>
+          <t>Briefly increases attack speed every 15 seconds while in battle.</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>철벽</t>
+          <t>Iron Wall</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>20초마다 방어가 잠시 오른다</t>
+          <t>Briefly increases defense every 20 seconds while in battle.</t>
         </is>
       </c>
     </row>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>예리함</t>
+          <t>Keenness</t>
         </is>
       </c>
     </row>
@@ -16273,7 +16273,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>14초마다 명중이 잠시 오른다</t>
+          <t>Briefly increases accuracy every 14 seconds while in battle.</t>
         </is>
       </c>
     </row>
@@ -16324,7 +16324,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>파쇄</t>
+          <t>Shatter</t>
         </is>
       </c>
     </row>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>22초마다 강한 추가 피해를 준다</t>
+          <t>Deals heavy bonus damage every 22 seconds while in battle.</t>
         </is>
       </c>
     </row>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>완력</t>
+          <t>Brawn</t>
         </is>
       </c>
     </row>
@@ -16375,7 +16375,7 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>물리 공격력이 오른다</t>
+          <t>Increases physical attack.</t>
         </is>
       </c>
     </row>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>마력 회로</t>
+          <t>Mana Circuit</t>
         </is>
       </c>
     </row>
@@ -16409,7 +16409,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>마법 공격력이 오른다</t>
+          <t>Increases magic attack.</t>
         </is>
       </c>
     </row>
@@ -16460,7 +16460,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>단련</t>
+          <t>Tempering</t>
         </is>
       </c>
     </row>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>방어력이 오른다</t>
+          <t>Increases defense.</t>
         </is>
       </c>
     </row>
@@ -16494,7 +16494,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>급소 감각</t>
+          <t>Weak Point Sense</t>
         </is>
       </c>
     </row>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>치명타 확률이 오른다</t>
+          <t>Increases critical rate.</t>
         </is>
       </c>
     </row>
@@ -16528,7 +16528,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>일격필살</t>
+          <t>Killing Blow</t>
         </is>
       </c>
     </row>
@@ -16545,7 +16545,7 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>치명타 피해가 오른다</t>
+          <t>Increases critical damage.</t>
         </is>
       </c>
     </row>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>정확</t>
+          <t>Precision</t>
         </is>
       </c>
     </row>
@@ -16579,7 +16579,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>명중률이 오른다</t>
+          <t>Increases accuracy.</t>
         </is>
       </c>
     </row>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>속공</t>
+          <t>Swift Assault</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16613,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>공격속도가 오른다</t>
+          <t>Increases attack speed.</t>
         </is>
       </c>
     </row>
@@ -16664,7 +16664,7 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>치유 친화</t>
+          <t>Healing Affinity</t>
         </is>
       </c>
     </row>
@@ -16681,7 +16681,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>회복량이 오른다</t>
+          <t>Increases the amount of HP restored.</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>기억의 그릇</t>
+          <t>Vessel of Memory</t>
         </is>
       </c>
     </row>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>최대 기억력이 오른다</t>
+          <t>Increases max memory.</t>
         </is>
       </c>
     </row>
@@ -16732,7 +16732,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>감내</t>
+          <t>Endurance</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>물리 저항이 오른다</t>
+          <t>Increases physical resistance.</t>
         </is>
       </c>
     </row>
@@ -16766,7 +16766,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>탐구심</t>
+          <t>Curiosity</t>
         </is>
       </c>
     </row>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>경험치 획득량이 늘어난다</t>
+          <t>Increases experience gained.</t>
         </is>
       </c>
     </row>
@@ -16800,7 +16800,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>장사 수완</t>
+          <t>Merchant's Knack</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>골드 획득량이 늘어난다</t>
+          <t>Increases gold gained.</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>행운</t>
+          <t>Luck</t>
         </is>
       </c>
     </row>
@@ -16851,7 +16851,7 @@
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>아이템 드롭률이 오른다</t>
+          <t>Increases item drop rate.</t>
         </is>
       </c>
     </row>
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>교감</t>
+          <t>Rapport</t>
         </is>
       </c>
     </row>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>미니몬 잡기 성공률이 오른다</t>
+          <t>Increases minion catch success rate.</t>
         </is>
       </c>
     </row>
@@ -16936,7 +16936,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>친화의 향기</t>
+          <t>Scent of Affinity</t>
         </is>
       </c>
     </row>
@@ -16953,7 +16953,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>관심 미니몬 보관 수가 늘어난다</t>
+          <t>Increases the number of attracted minions you can hold.</t>
         </is>
       </c>
     </row>
@@ -16970,7 +16970,7 @@
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>약초 지식</t>
+          <t>Herbal Lore</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>물약 재사용 대기시간이 줄어든다</t>
+          <t>Reduces potion cooldown.</t>
         </is>
       </c>
     </row>
@@ -17038,7 +17038,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>대장장이의 눈</t>
+          <t>Blacksmith's Eye</t>
         </is>
       </c>
     </row>
@@ -17055,7 +17055,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>장비 강화 성공률이 오른다</t>
+          <t>Increases equipment enhancement success rate.</t>
         </is>
       </c>
     </row>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>발걸음</t>
+          <t>Quick Steps</t>
         </is>
       </c>
     </row>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>이동 속도가 오른다</t>
+          <t>Increases movement speed.</t>
         </is>
       </c>
     </row>
@@ -34442,6 +34442,1168 @@
       <c r="C1878" t="inlineStr">
         <is>
           <t>Physical attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>AbilityTriggerChanceFormat</t>
+        </is>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>{0:0}% 확률로 {1}</t>
+        </is>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>{0:0}% chance to {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>AbilityTriggerIntervalFormat</t>
+        </is>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>{0:0.#}초마다 {1}</t>
+        </is>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>Every {0:0.#}s, {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>AbilityCondBattleStartText</t>
+        </is>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>전투 시작 시</t>
+        </is>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>At battle start</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>AbilityCondOnAttackText</t>
+        </is>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>공격 시</t>
+        </is>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>On attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>AbilityCondAfterAttackText</t>
+        </is>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>공격 후</t>
+        </is>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>After attacking</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>AbilityCondOnHitText</t>
+        </is>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>타격 시</t>
+        </is>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>On landing a hit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>AbilityCondOnCritText</t>
+        </is>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>치명타 시</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>On critical hit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>AbilityCondOnMissText</t>
+        </is>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>공격이 빗나갈 시</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>When an attack misses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>AbilityCondSelfEvadeText</t>
+        </is>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>회피 시</t>
+        </is>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>When you dodge</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>AbilityCondOnDamagedText</t>
+        </is>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>피격 시</t>
+        </is>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>When you are hit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>AbilityCondOnHealText</t>
+        </is>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>체력 회복 시</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>When you recover HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>AbilityCondLowHpFormat</t>
+        </is>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>HP {0:0}% 이하 시</t>
+        </is>
+      </c>
+      <c r="C1890" t="inlineStr">
+        <is>
+          <t>When HP is {0:0}% or below</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>AbilityCondEnemyEvadeText</t>
+        </is>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>상대 회피 시</t>
+        </is>
+      </c>
+      <c r="C1891" t="inlineStr">
+        <is>
+          <t>When the enemy dodges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>AbilityCondEnemyLowHpFormat</t>
+        </is>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>상대 HP {0:0}% 이하 시</t>
+        </is>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>When enemy HP is {0:0}% or below</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>AbilityContextInBattleText</t>
+        </is>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>전투 중</t>
+        </is>
+      </c>
+      <c r="C1893" t="inlineStr">
+        <is>
+          <t>In battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>AbilityContextOutOfBattleText</t>
+        </is>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>비전투 중</t>
+        </is>
+      </c>
+      <c r="C1894" t="inlineStr">
+        <is>
+          <t>Out of battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>AbilityContextAlwaysText</t>
+        </is>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>항시</t>
+        </is>
+      </c>
+      <c r="C1895" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>AbilityEffectHealFormat</t>
+        </is>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>체력 {0:0} 회복</t>
+        </is>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>restore {0:0} HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>AbilityEffectBonusDamageFormat</t>
+        </is>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>{0:0} 추가 피해</t>
+        </is>
+      </c>
+      <c r="C1897" t="inlineStr">
+        <is>
+          <t>deal {0:0} bonus damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>AbilityEffectBuffFormat</t>
+        </is>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>{0} +{1:0}</t>
+        </is>
+      </c>
+      <c r="C1898" t="inlineStr">
+        <is>
+          <t>gain {0} +{1:0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>AbilityEffectDurationFormat</t>
+        </is>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>({0:0.#}초)</t>
+        </is>
+      </c>
+      <c r="C1899" t="inlineStr">
+        <is>
+          <t>({0:0.#}s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>AbilityStatPhysicalAtkText</t>
+        </is>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>물리공격력</t>
+        </is>
+      </c>
+      <c r="C1900" t="inlineStr">
+        <is>
+          <t>physical attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>AbilityStatMagicAtkText</t>
+        </is>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>마법공격력</t>
+        </is>
+      </c>
+      <c r="C1901" t="inlineStr">
+        <is>
+          <t>magic attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>AbilityStatCritRateText</t>
+        </is>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>치명타 확률</t>
+        </is>
+      </c>
+      <c r="C1902" t="inlineStr">
+        <is>
+          <t>critical rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>AbilityStatCritDamageText</t>
+        </is>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>치명타 피해</t>
+        </is>
+      </c>
+      <c r="C1903" t="inlineStr">
+        <is>
+          <t>critical damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>AbilityStatAtkSpeedText</t>
+        </is>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>공격속도</t>
+        </is>
+      </c>
+      <c r="C1904" t="inlineStr">
+        <is>
+          <t>attack speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>AbilityStatAccuracyText</t>
+        </is>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>명중률</t>
+        </is>
+      </c>
+      <c r="C1905" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>AbilityStatDefText</t>
+        </is>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>방어력</t>
+        </is>
+      </c>
+      <c r="C1906" t="inlineStr">
+        <is>
+          <t>defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>AbilityStatMaxHpText</t>
+        </is>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>최대 체력</t>
+        </is>
+      </c>
+      <c r="C1907" t="inlineStr">
+        <is>
+          <t>max HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>AbilityStatEvasionText</t>
+        </is>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>회피율</t>
+        </is>
+      </c>
+      <c r="C1908" t="inlineStr">
+        <is>
+          <t>evasion</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>AbilityStatPhysicalResistText</t>
+        </is>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>물리 저항</t>
+        </is>
+      </c>
+      <c r="C1909" t="inlineStr">
+        <is>
+          <t>physical resistance</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>AbilityStatMaxMemoryText</t>
+        </is>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>최대 기억력</t>
+        </is>
+      </c>
+      <c r="C1910" t="inlineStr">
+        <is>
+          <t>max memory</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>AbilityStatCatchRateText</t>
+        </is>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>잡기 성공률</t>
+        </is>
+      </c>
+      <c r="C1911" t="inlineStr">
+        <is>
+          <t>catch success rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>AbilityStatGuaranteedCatchReduceText</t>
+        </is>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>확정 포획 필요 횟수</t>
+        </is>
+      </c>
+      <c r="C1912" t="inlineStr">
+        <is>
+          <t>attempts for guaranteed catch</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>AbilityStatExpGainText</t>
+        </is>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>경험치 획득량</t>
+        </is>
+      </c>
+      <c r="C1913" t="inlineStr">
+        <is>
+          <t>EXP gain</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>AbilityStatGoldGainText</t>
+        </is>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>골드 획득량</t>
+        </is>
+      </c>
+      <c r="C1914" t="inlineStr">
+        <is>
+          <t>gold gain</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>AbilityStatDropRateText</t>
+        </is>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>아이템 드롭률</t>
+        </is>
+      </c>
+      <c r="C1915" t="inlineStr">
+        <is>
+          <t>item drop rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>AbilityStatInterestMaxText</t>
+        </is>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>관심 미니몬 보관 수</t>
+        </is>
+      </c>
+      <c r="C1916" t="inlineStr">
+        <is>
+          <t>attracted minion capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>AbilityStatPotionCooldownText</t>
+        </is>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>물약 재사용 대기시간</t>
+        </is>
+      </c>
+      <c r="C1917" t="inlineStr">
+        <is>
+          <t>potion cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>AbilityStatEnhanceLuckText</t>
+        </is>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>강화 성공률</t>
+        </is>
+      </c>
+      <c r="C1918" t="inlineStr">
+        <is>
+          <t>enhancement success rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>AbilityStatMoveSpeedText</t>
+        </is>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>이동 속도</t>
+        </is>
+      </c>
+      <c r="C1919" t="inlineStr">
+        <is>
+          <t>movement speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>AbilityStatRecoveryRateText</t>
+        </is>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>회복량</t>
+        </is>
+      </c>
+      <c r="C1920" t="inlineStr">
+        <is>
+          <t>HP recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>AbilityNeedLearnText</t>
+        </is>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>습득 필요</t>
+        </is>
+      </c>
+      <c r="C1921" t="inlineStr">
+        <is>
+          <t>LEARN FIRST</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>AbilityAlwaysActiveText</t>
+        </is>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>항시 적용</t>
+        </is>
+      </c>
+      <c r="C1922" t="inlineStr">
+        <is>
+          <t>ALWAYS ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>NpcReceptionistNameText</t>
+        </is>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>접수원 아가씨</t>
+        </is>
+      </c>
+      <c r="C1923" t="inlineStr">
+        <is>
+          <t>Receptionist</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>NpcAlchemistNameText</t>
+        </is>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>연금공방 아가씨</t>
+        </is>
+      </c>
+      <c r="C1924" t="inlineStr">
+        <is>
+          <t>Alchemist</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>NpcBlacksmithNameText</t>
+        </is>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>대장장이</t>
+        </is>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>Blacksmith</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>NpcMonasteryPriestNameText</t>
+        </is>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>수도원 사제</t>
+        </is>
+      </c>
+      <c r="C1926" t="inlineStr">
+        <is>
+          <t>Monastery Priest</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>NpcShopkeeperNameText</t>
+        </is>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>상점 주인</t>
+        </is>
+      </c>
+      <c r="C1927" t="inlineStr">
+        <is>
+          <t>Shopkeeper</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>MinimonDefaultNameText</t>
+        </is>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>미니몬</t>
+        </is>
+      </c>
+      <c r="C1928" t="inlineStr">
+        <is>
+          <t>Minimon</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>AbilityUnknownFormat</t>
+        </is>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>능력 #{0}</t>
+        </is>
+      </c>
+      <c r="C1929" t="inlineStr">
+        <is>
+          <t>Ability #{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>IdleHuntAreaFormat</t>
+        </is>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>방치 사냥 중 — {0}에서 {1}마리
+경험치 {2:N0} · 골드 {3:N0}</t>
+        </is>
+      </c>
+      <c r="C1930" t="inlineStr">
+        <is>
+          <t>Idle hunting — {1} defeated in {0}
+EXP {2:N0} · Gold {3:N0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>IdleHuntFormat</t>
+        </is>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>방치 사냥 중 — {0}마리
+경험치 {1:N0} · 골드 {2:N0}</t>
+        </is>
+      </c>
+      <c r="C1931" t="inlineStr">
+        <is>
+          <t>Idle hunting — {0} defeated
+EXP {1:N0} · Gold {2:N0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>OfflineRewardFormat</t>
+        </is>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>자리를 비운 {0} 동안 {1}마리를 처치했습니다
+경험치 {2:N0} · 골드 {3:N0}</t>
+        </is>
+      </c>
+      <c r="C1932" t="inlineStr">
+        <is>
+          <t>You defeated {1} monsters while away for {0}.
+EXP {2:N0} · Gold {3:N0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>OfflineRewardCapFormat</t>
+        </is>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>(최대 {0:F0}시간까지 정산됩니다)</t>
+        </is>
+      </c>
+      <c r="C1933" t="inlineStr">
+        <is>
+          <t>(Rewards are capped at {0:F0} hours.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>OfflineTimeHoursFormat</t>
+        </is>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>{0:F1}시간</t>
+        </is>
+      </c>
+      <c r="C1934" t="inlineStr">
+        <is>
+          <t>{0:F1} hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>OfflineTimeMinutesFormat</t>
+        </is>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>{0:F0}분</t>
+        </is>
+      </c>
+      <c r="C1935" t="inlineStr">
+        <is>
+          <t>{0:F0} min</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>ShopNotForSaleText</t>
+        </is>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>판매하지 않는 물건</t>
+        </is>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>Not for sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>TravelLockedText</t>
+        </is>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>잠김</t>
+        </is>
+      </c>
+      <c r="C1937" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>DefaultPlayerNameText</t>
+        </is>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>여행자</t>
+        </is>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>Traveler</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>BackAgainToQuitText</t>
+        </is>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>한 번 더 누르면 게임을 종료합니다.</t>
+        </is>
+      </c>
+      <c r="C1939" t="inlineStr">
+        <is>
+          <t>Press back again to quit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>QuitGameText</t>
+        </is>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>게임 종료</t>
+        </is>
+      </c>
+      <c r="C1940" t="inlineStr">
+        <is>
+          <t>QUIT GAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>SettingText</t>
+        </is>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="C1941" t="inlineStr">
+        <is>
+          <t>SETTINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>CreditsText</t>
+        </is>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>크레딧</t>
+        </is>
+      </c>
+      <c r="C1942" t="inlineStr">
+        <is>
+          <t>CREDITS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>SystemText</t>
+        </is>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="C1943" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>FullscreenText</t>
+        </is>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>전체 화면</t>
+        </is>
+      </c>
+      <c r="C1944" t="inlineStr">
+        <is>
+          <t>FULLSCREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>ThanksForPlayingText</t>
+        </is>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>플레이해 주셔서 감사합니다!</t>
+        </is>
+      </c>
+      <c r="C1945" t="inlineStr">
+        <is>
+          <t>Thank you for playing!</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>EquipmentTitleText</t>
+        </is>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+      <c r="C1946" t="inlineStr">
+        <is>
+          <t>EQUIPMENT</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -20744,7 +20744,7 @@
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>DURABILITY</t>
+          <t>DUR.</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -4930,7 +4930,7 @@
         <is>
           <t>Passive: +30 maximum HP per ability level.
 Manual use: Restore 18% of maximum HP per ability level.
-Cooldown: 18s, shared by minion abilities.
+Cooldown: 18s, shared by Minimon abilities.
 Available temporarily while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -4989,7 +4989,7 @@
         <is>
           <t>Passive: +10 percentage points of attack speed per ability level.
 Manual use: Gain 30 percentage points of attack speed per ability level for 8 seconds.
-Cooldown: 18s, shared by minion abilities.
+Cooldown: 18s, shared by Minimon abilities.
 Available temporarily while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Increases minion catch success rate.</t>
+          <t>Increases Minimon catch success rate.</t>
         </is>
       </c>
     </row>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Increases minion catch success rate.</t>
+          <t>Increases Minimon catch success rate.</t>
         </is>
       </c>
     </row>
@@ -16953,7 +16953,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>Increases the number of attracted minions you can hold.</t>
+          <t>Increases the number of attracted Minimon you can hold.</t>
         </is>
       </c>
     </row>
@@ -23292,7 +23292,7 @@
       <c r="C1340" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23313,7 +23313,7 @@
       <c r="C1341" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23334,7 +23334,7 @@
       <c r="C1342" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23355,7 +23355,7 @@
       <c r="C1343" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23376,7 +23376,7 @@
       <c r="C1344" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23397,7 +23397,7 @@
       <c r="C1345" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23418,7 +23418,7 @@
       <c r="C1346" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23439,7 +23439,7 @@
       <c r="C1347" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23460,7 +23460,7 @@
       <c r="C1348" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23481,7 +23481,7 @@
       <c r="C1349" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23502,7 +23502,7 @@
       <c r="C1350" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23523,7 +23523,7 @@
       <c r="C1351" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23544,7 +23544,7 @@
       <c r="C1352" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23565,7 +23565,7 @@
       <c r="C1353" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23586,7 +23586,7 @@
       <c r="C1354" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23607,7 +23607,7 @@
       <c r="C1355" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23628,7 +23628,7 @@
       <c r="C1356" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23649,7 +23649,7 @@
       <c r="C1357" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23670,7 +23670,7 @@
       <c r="C1358" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23691,7 +23691,7 @@
       <c r="C1359" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23712,7 +23712,7 @@
       <c r="C1360" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23733,7 +23733,7 @@
       <c r="C1361" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23754,7 +23754,7 @@
       <c r="C1362" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23775,7 +23775,7 @@
       <c r="C1363" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23796,7 +23796,7 @@
       <c r="C1364" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23817,7 +23817,7 @@
       <c r="C1365" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23838,7 +23838,7 @@
       <c r="C1366" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23859,7 +23859,7 @@
       <c r="C1367" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23880,7 +23880,7 @@
       <c r="C1368" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23901,7 +23901,7 @@
       <c r="C1369" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23922,7 +23922,7 @@
       <c r="C1370" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23943,7 +23943,7 @@
       <c r="C1371" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23964,7 +23964,7 @@
       <c r="C1372" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -23985,7 +23985,7 @@
       <c r="C1373" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24006,7 +24006,7 @@
       <c r="C1374" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24027,7 +24027,7 @@
       <c r="C1375" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24048,7 +24048,7 @@
       <c r="C1376" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24069,7 +24069,7 @@
       <c r="C1377" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24090,7 +24090,7 @@
       <c r="C1378" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24111,7 +24111,7 @@
       <c r="C1379" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24132,7 +24132,7 @@
       <c r="C1380" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24153,7 +24153,7 @@
       <c r="C1381" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24174,7 +24174,7 @@
       <c r="C1382" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24195,7 +24195,7 @@
       <c r="C1383" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24216,7 +24216,7 @@
       <c r="C1384" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24237,7 +24237,7 @@
       <c r="C1385" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24258,7 +24258,7 @@
       <c r="C1386" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24279,7 +24279,7 @@
       <c r="C1387" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24300,7 +24300,7 @@
       <c r="C1388" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24321,7 +24321,7 @@
       <c r="C1389" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24342,7 +24342,7 @@
       <c r="C1390" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24363,7 +24363,7 @@
       <c r="C1391" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24384,7 +24384,7 @@
       <c r="C1392" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24405,7 +24405,7 @@
       <c r="C1393" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24426,7 +24426,7 @@
       <c r="C1394" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24447,7 +24447,7 @@
       <c r="C1395" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24468,7 +24468,7 @@
       <c r="C1396" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24489,7 +24489,7 @@
       <c r="C1397" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24510,7 +24510,7 @@
       <c r="C1398" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24531,7 +24531,7 @@
       <c r="C1399" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24552,7 +24552,7 @@
       <c r="C1400" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24573,7 +24573,7 @@
       <c r="C1401" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24594,7 +24594,7 @@
       <c r="C1402" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24615,7 +24615,7 @@
       <c r="C1403" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24636,7 +24636,7 @@
       <c r="C1404" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24657,7 +24657,7 @@
       <c r="C1405" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24678,7 +24678,7 @@
       <c r="C1406" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24699,7 +24699,7 @@
       <c r="C1407" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24720,7 +24720,7 @@
       <c r="C1408" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24741,7 +24741,7 @@
       <c r="C1409" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24762,7 +24762,7 @@
       <c r="C1410" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24783,7 +24783,7 @@
       <c r="C1411" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24804,7 +24804,7 @@
       <c r="C1412" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24825,7 +24825,7 @@
       <c r="C1413" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24846,7 +24846,7 @@
       <c r="C1414" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24867,7 +24867,7 @@
       <c r="C1415" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24888,7 +24888,7 @@
       <c r="C1416" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24909,7 +24909,7 @@
       <c r="C1417" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24930,7 +24930,7 @@
       <c r="C1418" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24951,7 +24951,7 @@
       <c r="C1419" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24972,7 +24972,7 @@
       <c r="C1420" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -24993,7 +24993,7 @@
       <c r="C1421" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25014,7 +25014,7 @@
       <c r="C1422" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25035,7 +25035,7 @@
       <c r="C1423" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25056,7 +25056,7 @@
       <c r="C1424" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25077,7 +25077,7 @@
       <c r="C1425" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25098,7 +25098,7 @@
       <c r="C1426" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25119,7 +25119,7 @@
       <c r="C1427" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25140,7 +25140,7 @@
       <c r="C1428" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25161,7 +25161,7 @@
       <c r="C1429" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25182,7 +25182,7 @@
       <c r="C1430" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25203,7 +25203,7 @@
       <c r="C1431" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25224,7 +25224,7 @@
       <c r="C1432" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25245,7 +25245,7 @@
       <c r="C1433" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25266,7 +25266,7 @@
       <c r="C1434" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25287,7 +25287,7 @@
       <c r="C1435" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25308,7 +25308,7 @@
       <c r="C1436" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25329,7 +25329,7 @@
       <c r="C1437" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25350,7 +25350,7 @@
       <c r="C1438" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25371,7 +25371,7 @@
       <c r="C1439" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25392,7 +25392,7 @@
       <c r="C1440" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25413,7 +25413,7 @@
       <c r="C1441" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25434,7 +25434,7 @@
       <c r="C1442" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25455,7 +25455,7 @@
       <c r="C1443" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25476,7 +25476,7 @@
       <c r="C1444" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25497,7 +25497,7 @@
       <c r="C1445" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25518,7 +25518,7 @@
       <c r="C1446" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25539,7 +25539,7 @@
       <c r="C1447" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25560,7 +25560,7 @@
       <c r="C1448" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25581,7 +25581,7 @@
       <c r="C1449" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25602,7 +25602,7 @@
       <c r="C1450" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25623,7 +25623,7 @@
       <c r="C1451" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25644,7 +25644,7 @@
       <c r="C1452" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25665,7 +25665,7 @@
       <c r="C1453" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25686,7 +25686,7 @@
       <c r="C1454" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25707,7 +25707,7 @@
       <c r="C1455" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25728,7 +25728,7 @@
       <c r="C1456" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25749,7 +25749,7 @@
       <c r="C1457" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25770,7 +25770,7 @@
       <c r="C1458" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25791,7 +25791,7 @@
       <c r="C1459" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25812,7 +25812,7 @@
       <c r="C1460" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25833,7 +25833,7 @@
       <c r="C1461" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25854,7 +25854,7 @@
       <c r="C1462" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25875,7 +25875,7 @@
       <c r="C1463" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25896,7 +25896,7 @@
       <c r="C1464" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25917,7 +25917,7 @@
       <c r="C1465" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25938,7 +25938,7 @@
       <c r="C1466" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25959,7 +25959,7 @@
       <c r="C1467" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -25980,7 +25980,7 @@
       <c r="C1468" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26001,7 +26001,7 @@
       <c r="C1469" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26022,7 +26022,7 @@
       <c r="C1470" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26043,7 +26043,7 @@
       <c r="C1471" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26064,7 +26064,7 @@
       <c r="C1472" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26085,7 +26085,7 @@
       <c r="C1473" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26106,7 +26106,7 @@
       <c r="C1474" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26127,7 +26127,7 @@
       <c r="C1475" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26148,7 +26148,7 @@
       <c r="C1476" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26169,7 +26169,7 @@
       <c r="C1477" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26190,7 +26190,7 @@
       <c r="C1478" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26211,7 +26211,7 @@
       <c r="C1479" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26232,7 +26232,7 @@
       <c r="C1480" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26253,7 +26253,7 @@
       <c r="C1481" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26274,7 +26274,7 @@
       <c r="C1482" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26295,7 +26295,7 @@
       <c r="C1483" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26316,7 +26316,7 @@
       <c r="C1484" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26337,7 +26337,7 @@
       <c r="C1485" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26358,7 +26358,7 @@
       <c r="C1486" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26379,7 +26379,7 @@
       <c r="C1487" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26400,7 +26400,7 @@
       <c r="C1488" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26421,7 +26421,7 @@
       <c r="C1489" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26442,7 +26442,7 @@
       <c r="C1490" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26463,7 +26463,7 @@
       <c r="C1491" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26484,7 +26484,7 @@
       <c r="C1492" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26505,7 +26505,7 @@
       <c r="C1493" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26526,7 +26526,7 @@
       <c r="C1494" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26547,7 +26547,7 @@
       <c r="C1495" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26568,7 +26568,7 @@
       <c r="C1496" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26589,7 +26589,7 @@
       <c r="C1497" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26610,7 +26610,7 @@
       <c r="C1498" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26631,7 +26631,7 @@
       <c r="C1499" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26652,7 +26652,7 @@
       <c r="C1500" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26673,7 +26673,7 @@
       <c r="C1501" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26694,7 +26694,7 @@
       <c r="C1502" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26715,7 +26715,7 @@
       <c r="C1503" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26736,7 +26736,7 @@
       <c r="C1504" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26757,7 +26757,7 @@
       <c r="C1505" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26778,7 +26778,7 @@
       <c r="C1506" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26799,7 +26799,7 @@
       <c r="C1507" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26820,7 +26820,7 @@
       <c r="C1508" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26841,7 +26841,7 @@
       <c r="C1509" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26862,7 +26862,7 @@
       <c r="C1510" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26883,7 +26883,7 @@
       <c r="C1511" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26904,7 +26904,7 @@
       <c r="C1512" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26925,7 +26925,7 @@
       <c r="C1513" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26946,7 +26946,7 @@
       <c r="C1514" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26967,7 +26967,7 @@
       <c r="C1515" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -26988,7 +26988,7 @@
       <c r="C1516" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27009,7 +27009,7 @@
       <c r="C1517" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27030,7 +27030,7 @@
       <c r="C1518" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27051,7 +27051,7 @@
       <c r="C1519" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27072,7 +27072,7 @@
       <c r="C1520" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27093,7 +27093,7 @@
       <c r="C1521" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27114,7 +27114,7 @@
       <c r="C1522" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27135,7 +27135,7 @@
       <c r="C1523" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27156,7 +27156,7 @@
       <c r="C1524" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27177,7 +27177,7 @@
       <c r="C1525" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27198,7 +27198,7 @@
       <c r="C1526" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27219,7 +27219,7 @@
       <c r="C1527" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27240,7 +27240,7 @@
       <c r="C1528" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27261,7 +27261,7 @@
       <c r="C1529" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27282,7 +27282,7 @@
       <c r="C1530" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27303,7 +27303,7 @@
       <c r="C1531" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27324,7 +27324,7 @@
       <c r="C1532" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27345,7 +27345,7 @@
       <c r="C1533" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27366,7 +27366,7 @@
       <c r="C1534" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27387,7 +27387,7 @@
       <c r="C1535" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27408,7 +27408,7 @@
       <c r="C1536" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27429,7 +27429,7 @@
       <c r="C1537" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27450,7 +27450,7 @@
       <c r="C1538" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27471,7 +27471,7 @@
       <c r="C1539" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27492,7 +27492,7 @@
       <c r="C1540" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27513,7 +27513,7 @@
       <c r="C1541" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27534,7 +27534,7 @@
       <c r="C1542" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27555,7 +27555,7 @@
       <c r="C1543" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27576,7 +27576,7 @@
       <c r="C1544" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27597,7 +27597,7 @@
       <c r="C1545" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27618,7 +27618,7 @@
       <c r="C1546" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27639,7 +27639,7 @@
       <c r="C1547" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27660,7 +27660,7 @@
       <c r="C1548" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27681,7 +27681,7 @@
       <c r="C1549" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27702,7 +27702,7 @@
       <c r="C1550" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27723,7 +27723,7 @@
       <c r="C1551" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27744,7 +27744,7 @@
       <c r="C1552" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27765,7 +27765,7 @@
       <c r="C1553" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27786,7 +27786,7 @@
       <c r="C1554" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27807,7 +27807,7 @@
       <c r="C1555" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27828,7 +27828,7 @@
       <c r="C1556" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27849,7 +27849,7 @@
       <c r="C1557" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27870,7 +27870,7 @@
       <c r="C1558" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27891,7 +27891,7 @@
       <c r="C1559" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27912,7 +27912,7 @@
       <c r="C1560" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27933,7 +27933,7 @@
       <c r="C1561" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27954,7 +27954,7 @@
       <c r="C1562" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27975,7 +27975,7 @@
       <c r="C1563" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -27996,7 +27996,7 @@
       <c r="C1564" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28017,7 +28017,7 @@
       <c r="C1565" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28038,7 +28038,7 @@
       <c r="C1566" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28059,7 +28059,7 @@
       <c r="C1567" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28080,7 +28080,7 @@
       <c r="C1568" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28101,7 +28101,7 @@
       <c r="C1569" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28122,7 +28122,7 @@
       <c r="C1570" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28143,7 +28143,7 @@
       <c r="C1571" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28164,7 +28164,7 @@
       <c r="C1572" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28185,7 +28185,7 @@
       <c r="C1573" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28206,7 +28206,7 @@
       <c r="C1574" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28227,7 +28227,7 @@
       <c r="C1575" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28248,7 +28248,7 @@
       <c r="C1576" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28269,7 +28269,7 @@
       <c r="C1577" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28290,7 +28290,7 @@
       <c r="C1578" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28311,7 +28311,7 @@
       <c r="C1579" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28332,7 +28332,7 @@
       <c r="C1580" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28353,7 +28353,7 @@
       <c r="C1581" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28374,7 +28374,7 @@
       <c r="C1582" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28395,7 +28395,7 @@
       <c r="C1583" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28416,7 +28416,7 @@
       <c r="C1584" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28437,7 +28437,7 @@
       <c r="C1585" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28458,7 +28458,7 @@
       <c r="C1586" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28479,7 +28479,7 @@
       <c r="C1587" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28500,7 +28500,7 @@
       <c r="C1588" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28521,7 +28521,7 @@
       <c r="C1589" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28542,7 +28542,7 @@
       <c r="C1590" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28563,7 +28563,7 @@
       <c r="C1591" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28584,7 +28584,7 @@
       <c r="C1592" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28605,7 +28605,7 @@
       <c r="C1593" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28626,7 +28626,7 @@
       <c r="C1594" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28647,7 +28647,7 @@
       <c r="C1595" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28668,7 +28668,7 @@
       <c r="C1596" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28689,7 +28689,7 @@
       <c r="C1597" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28710,7 +28710,7 @@
       <c r="C1598" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28731,7 +28731,7 @@
       <c r="C1599" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28752,7 +28752,7 @@
       <c r="C1600" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28773,7 +28773,7 @@
       <c r="C1601" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28794,7 +28794,7 @@
       <c r="C1602" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28815,7 +28815,7 @@
       <c r="C1603" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28836,7 +28836,7 @@
       <c r="C1604" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28857,7 +28857,7 @@
       <c r="C1605" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28878,7 +28878,7 @@
       <c r="C1606" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28899,7 +28899,7 @@
       <c r="C1607" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28920,7 +28920,7 @@
       <c r="C1608" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28941,7 +28941,7 @@
       <c r="C1609" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28962,7 +28962,7 @@
       <c r="C1610" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -28983,7 +28983,7 @@
       <c r="C1611" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29004,7 +29004,7 @@
       <c r="C1612" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29025,7 +29025,7 @@
       <c r="C1613" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29046,7 +29046,7 @@
       <c r="C1614" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29067,7 +29067,7 @@
       <c r="C1615" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29088,7 +29088,7 @@
       <c r="C1616" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29109,7 +29109,7 @@
       <c r="C1617" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29130,7 +29130,7 @@
       <c r="C1618" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29151,7 +29151,7 @@
       <c r="C1619" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29172,7 +29172,7 @@
       <c r="C1620" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29193,7 +29193,7 @@
       <c r="C1621" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29214,7 +29214,7 @@
       <c r="C1622" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29235,7 +29235,7 @@
       <c r="C1623" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29256,7 +29256,7 @@
       <c r="C1624" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29277,7 +29277,7 @@
       <c r="C1625" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29298,7 +29298,7 @@
       <c r="C1626" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29319,7 +29319,7 @@
       <c r="C1627" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29340,7 +29340,7 @@
       <c r="C1628" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29361,7 +29361,7 @@
       <c r="C1629" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29382,7 +29382,7 @@
       <c r="C1630" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29403,7 +29403,7 @@
       <c r="C1631" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29424,7 +29424,7 @@
       <c r="C1632" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29445,7 +29445,7 @@
       <c r="C1633" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29466,7 +29466,7 @@
       <c r="C1634" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29487,7 +29487,7 @@
       <c r="C1635" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29508,7 +29508,7 @@
       <c r="C1636" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29529,7 +29529,7 @@
       <c r="C1637" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29550,7 +29550,7 @@
       <c r="C1638" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29571,7 +29571,7 @@
       <c r="C1639" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29592,7 +29592,7 @@
       <c r="C1640" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29613,7 +29613,7 @@
       <c r="C1641" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29634,7 +29634,7 @@
       <c r="C1642" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29655,7 +29655,7 @@
       <c r="C1643" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29676,7 +29676,7 @@
       <c r="C1644" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29697,7 +29697,7 @@
       <c r="C1645" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29718,7 +29718,7 @@
       <c r="C1646" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29739,7 +29739,7 @@
       <c r="C1647" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29760,7 +29760,7 @@
       <c r="C1648" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29781,7 +29781,7 @@
       <c r="C1649" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29802,7 +29802,7 @@
       <c r="C1650" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29823,7 +29823,7 @@
       <c r="C1651" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29844,7 +29844,7 @@
       <c r="C1652" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29865,7 +29865,7 @@
       <c r="C1653" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29886,7 +29886,7 @@
       <c r="C1654" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29907,7 +29907,7 @@
       <c r="C1655" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29928,7 +29928,7 @@
       <c r="C1656" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29949,7 +29949,7 @@
       <c r="C1657" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29970,7 +29970,7 @@
       <c r="C1658" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -29991,7 +29991,7 @@
       <c r="C1659" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30012,7 +30012,7 @@
       <c r="C1660" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30033,7 +30033,7 @@
       <c r="C1661" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30054,7 +30054,7 @@
       <c r="C1662" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30075,7 +30075,7 @@
       <c r="C1663" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30096,7 +30096,7 @@
       <c r="C1664" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30117,7 +30117,7 @@
       <c r="C1665" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30138,7 +30138,7 @@
       <c r="C1666" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30159,7 +30159,7 @@
       <c r="C1667" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30180,7 +30180,7 @@
       <c r="C1668" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30201,7 +30201,7 @@
       <c r="C1669" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30222,7 +30222,7 @@
       <c r="C1670" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30243,7 +30243,7 @@
       <c r="C1671" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30264,7 +30264,7 @@
       <c r="C1672" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30285,7 +30285,7 @@
       <c r="C1673" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30306,7 +30306,7 @@
       <c r="C1674" t="inlineStr">
         <is>
           <t>Gain 20 percentage points of accuracy for 8 seconds.
-Cooldown: 14s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 14s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30327,7 +30327,7 @@
       <c r="C1675" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30348,7 +30348,7 @@
       <c r="C1676" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30369,7 +30369,7 @@
       <c r="C1677" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30390,7 +30390,7 @@
       <c r="C1678" t="inlineStr">
         <is>
           <t>Gain 30 percentage points of attack speed for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30411,7 +30411,7 @@
       <c r="C1679" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30432,7 +30432,7 @@
       <c r="C1680" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30453,7 +30453,7 @@
       <c r="C1681" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30474,7 +30474,7 @@
       <c r="C1682" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30495,7 +30495,7 @@
       <c r="C1683" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30516,7 +30516,7 @@
       <c r="C1684" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30537,7 +30537,7 @@
       <c r="C1685" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30558,7 +30558,7 @@
       <c r="C1686" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30579,7 +30579,7 @@
       <c r="C1687" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30600,7 +30600,7 @@
       <c r="C1688" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30621,7 +30621,7 @@
       <c r="C1689" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30642,7 +30642,7 @@
       <c r="C1690" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30663,7 +30663,7 @@
       <c r="C1691" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30684,7 +30684,7 @@
       <c r="C1692" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30705,7 +30705,7 @@
       <c r="C1693" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30726,7 +30726,7 @@
       <c r="C1694" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30747,7 +30747,7 @@
       <c r="C1695" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30768,7 +30768,7 @@
       <c r="C1696" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30789,7 +30789,7 @@
       <c r="C1697" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30810,7 +30810,7 @@
       <c r="C1698" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30831,7 +30831,7 @@
       <c r="C1699" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30852,7 +30852,7 @@
       <c r="C1700" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30873,7 +30873,7 @@
       <c r="C1701" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30894,7 +30894,7 @@
       <c r="C1702" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30915,7 +30915,7 @@
       <c r="C1703" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30936,7 +30936,7 @@
       <c r="C1704" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30957,7 +30957,7 @@
       <c r="C1705" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30978,7 +30978,7 @@
       <c r="C1706" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -30999,7 +30999,7 @@
       <c r="C1707" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31020,7 +31020,7 @@
       <c r="C1708" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31041,7 +31041,7 @@
       <c r="C1709" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31062,7 +31062,7 @@
       <c r="C1710" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31083,7 +31083,7 @@
       <c r="C1711" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31104,7 +31104,7 @@
       <c r="C1712" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31125,7 +31125,7 @@
       <c r="C1713" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31146,7 +31146,7 @@
       <c r="C1714" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31167,7 +31167,7 @@
       <c r="C1715" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31188,7 +31188,7 @@
       <c r="C1716" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31209,7 +31209,7 @@
       <c r="C1717" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31230,7 +31230,7 @@
       <c r="C1718" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31251,7 +31251,7 @@
       <c r="C1719" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31272,7 +31272,7 @@
       <c r="C1720" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31293,7 +31293,7 @@
       <c r="C1721" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31314,7 +31314,7 @@
       <c r="C1722" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31335,7 +31335,7 @@
       <c r="C1723" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31356,7 +31356,7 @@
       <c r="C1724" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31377,7 +31377,7 @@
       <c r="C1725" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31398,7 +31398,7 @@
       <c r="C1726" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31419,7 +31419,7 @@
       <c r="C1727" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31440,7 +31440,7 @@
       <c r="C1728" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31461,7 +31461,7 @@
       <c r="C1729" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31482,7 +31482,7 @@
       <c r="C1730" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31503,7 +31503,7 @@
       <c r="C1731" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31524,7 +31524,7 @@
       <c r="C1732" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31545,7 +31545,7 @@
       <c r="C1733" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31566,7 +31566,7 @@
       <c r="C1734" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31587,7 +31587,7 @@
       <c r="C1735" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31608,7 +31608,7 @@
       <c r="C1736" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31629,7 +31629,7 @@
       <c r="C1737" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31650,7 +31650,7 @@
       <c r="C1738" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31671,7 +31671,7 @@
       <c r="C1739" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31692,7 +31692,7 @@
       <c r="C1740" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31713,7 +31713,7 @@
       <c r="C1741" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31734,7 +31734,7 @@
       <c r="C1742" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31755,7 +31755,7 @@
       <c r="C1743" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31776,7 +31776,7 @@
       <c r="C1744" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31797,7 +31797,7 @@
       <c r="C1745" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31818,7 +31818,7 @@
       <c r="C1746" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31839,7 +31839,7 @@
       <c r="C1747" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31860,7 +31860,7 @@
       <c r="C1748" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31881,7 +31881,7 @@
       <c r="C1749" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31902,7 +31902,7 @@
       <c r="C1750" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31923,7 +31923,7 @@
       <c r="C1751" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31944,7 +31944,7 @@
       <c r="C1752" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31965,7 +31965,7 @@
       <c r="C1753" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -31986,7 +31986,7 @@
       <c r="C1754" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32007,7 +32007,7 @@
       <c r="C1755" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32028,7 +32028,7 @@
       <c r="C1756" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32049,7 +32049,7 @@
       <c r="C1757" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32070,7 +32070,7 @@
       <c r="C1758" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32091,7 +32091,7 @@
       <c r="C1759" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32112,7 +32112,7 @@
       <c r="C1760" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32133,7 +32133,7 @@
       <c r="C1761" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32154,7 +32154,7 @@
       <c r="C1762" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32175,7 +32175,7 @@
       <c r="C1763" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32196,7 +32196,7 @@
       <c r="C1764" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32217,7 +32217,7 @@
       <c r="C1765" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32238,7 +32238,7 @@
       <c r="C1766" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32259,7 +32259,7 @@
       <c r="C1767" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32280,7 +32280,7 @@
       <c r="C1768" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32301,7 +32301,7 @@
       <c r="C1769" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32322,7 +32322,7 @@
       <c r="C1770" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32343,7 +32343,7 @@
       <c r="C1771" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32364,7 +32364,7 @@
       <c r="C1772" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32385,7 +32385,7 @@
       <c r="C1773" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32406,7 +32406,7 @@
       <c r="C1774" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32427,7 +32427,7 @@
       <c r="C1775" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32448,7 +32448,7 @@
       <c r="C1776" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32469,7 +32469,7 @@
       <c r="C1777" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32490,7 +32490,7 @@
       <c r="C1778" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32511,7 +32511,7 @@
       <c r="C1779" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32532,7 +32532,7 @@
       <c r="C1780" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32553,7 +32553,7 @@
       <c r="C1781" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32574,7 +32574,7 @@
       <c r="C1782" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32595,7 +32595,7 @@
       <c r="C1783" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32616,7 +32616,7 @@
       <c r="C1784" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32637,7 +32637,7 @@
       <c r="C1785" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32658,7 +32658,7 @@
       <c r="C1786" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32679,7 +32679,7 @@
       <c r="C1787" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32700,7 +32700,7 @@
       <c r="C1788" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32721,7 +32721,7 @@
       <c r="C1789" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32742,7 +32742,7 @@
       <c r="C1790" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32763,7 +32763,7 @@
       <c r="C1791" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32784,7 +32784,7 @@
       <c r="C1792" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32805,7 +32805,7 @@
       <c r="C1793" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32826,7 +32826,7 @@
       <c r="C1794" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32847,7 +32847,7 @@
       <c r="C1795" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32868,7 +32868,7 @@
       <c r="C1796" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32889,7 +32889,7 @@
       <c r="C1797" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32910,7 +32910,7 @@
       <c r="C1798" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32931,7 +32931,7 @@
       <c r="C1799" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32952,7 +32952,7 @@
       <c r="C1800" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32973,7 +32973,7 @@
       <c r="C1801" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -32994,7 +32994,7 @@
       <c r="C1802" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33015,7 +33015,7 @@
       <c r="C1803" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33036,7 +33036,7 @@
       <c r="C1804" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33057,7 +33057,7 @@
       <c r="C1805" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33078,7 +33078,7 @@
       <c r="C1806" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33099,7 +33099,7 @@
       <c r="C1807" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33120,7 +33120,7 @@
       <c r="C1808" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33141,7 +33141,7 @@
       <c r="C1809" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33162,7 +33162,7 @@
       <c r="C1810" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33183,7 +33183,7 @@
       <c r="C1811" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33204,7 +33204,7 @@
       <c r="C1812" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33225,7 +33225,7 @@
       <c r="C1813" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33246,7 +33246,7 @@
       <c r="C1814" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33267,7 +33267,7 @@
       <c r="C1815" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33288,7 +33288,7 @@
       <c r="C1816" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33309,7 +33309,7 @@
       <c r="C1817" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33330,7 +33330,7 @@
       <c r="C1818" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33351,7 +33351,7 @@
       <c r="C1819" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33372,7 +33372,7 @@
       <c r="C1820" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33393,7 +33393,7 @@
       <c r="C1821" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33414,7 +33414,7 @@
       <c r="C1822" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33435,7 +33435,7 @@
       <c r="C1823" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33456,7 +33456,7 @@
       <c r="C1824" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33477,7 +33477,7 @@
       <c r="C1825" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33498,7 +33498,7 @@
       <c r="C1826" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33519,7 +33519,7 @@
       <c r="C1827" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33540,7 +33540,7 @@
       <c r="C1828" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33561,7 +33561,7 @@
       <c r="C1829" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33582,7 +33582,7 @@
       <c r="C1830" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33603,7 +33603,7 @@
       <c r="C1831" t="inlineStr">
         <is>
           <t>Gain 18 percentage points of evasion for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33624,7 +33624,7 @@
       <c r="C1832" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33645,7 +33645,7 @@
       <c r="C1833" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33666,7 +33666,7 @@
       <c r="C1834" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33687,7 +33687,7 @@
       <c r="C1835" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 180% of physical attack.
-Cooldown: 12s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 12s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33708,7 +33708,7 @@
       <c r="C1836" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33729,7 +33729,7 @@
       <c r="C1837" t="inlineStr">
         <is>
           <t>Restore 18% of maximum HP.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33750,7 +33750,7 @@
       <c r="C1838" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33771,7 +33771,7 @@
       <c r="C1839" t="inlineStr">
         <is>
           <t>Deal guaranteed bonus damage equal to 300% of physical attack.
-Cooldown: 20s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 20s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -33792,7 +33792,7 @@
       <c r="C1840" t="inlineStr">
         <is>
           <t>Gain 25 percentage points of physical resistance for 8 seconds.
-Cooldown: 18s, shared by minion abilities. Effect scales with ability level.
+Cooldown: 18s, shared by Minimon abilities. Effect scales with ability level.
 Available while accompanying. Permanently learned at 100% resonance.</t>
         </is>
       </c>
@@ -35087,7 +35087,7 @@
       </c>
       <c r="C1916" t="inlineStr">
         <is>
-          <t>attracted minion capacity</t>
+          <t>attracted Minimon capacity</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1946"/>
+  <dimension ref="A1:C1952"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35607,6 +35607,108 @@
         </is>
       </c>
     </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>InventoryTitleText</t>
+        </is>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>소지품</t>
+        </is>
+      </c>
+      <c r="C1947" t="inlineStr">
+        <is>
+          <t>INVENTORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>InventorySortText</t>
+        </is>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>정리</t>
+        </is>
+      </c>
+      <c r="C1948" t="inlineStr">
+        <is>
+          <t>SORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>MonsterSkillNeedLinkText</t>
+        </is>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>100% 동기화 필요</t>
+        </is>
+      </c>
+      <c r="C1949" t="inlineStr">
+        <is>
+          <t>REQUIRES 100% LINK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>MonsterSkillFullLockText</t>
+        </is>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>하수인 또는 완벽분석 필요</t>
+        </is>
+      </c>
+      <c r="C1950" t="inlineStr">
+        <is>
+          <t>REQUIRES MINIMON OR FULL LOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>NotOwnedText</t>
+        </is>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>미보유</t>
+        </is>
+      </c>
+      <c r="C1951" t="inlineStr">
+        <is>
+          <t>NOT OWNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>InfoBtnText</t>
+        </is>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="C1952" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1952"/>
+  <dimension ref="A1:C1954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35709,6 +35709,40 @@
         </is>
       </c>
     </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>PotionUpgradeText</t>
+        </is>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>물약개선</t>
+        </is>
+      </c>
+      <c r="C1953" t="inlineStr">
+        <is>
+          <t>UPGRADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>CustomOrderGreetingText</t>
+        </is>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>"무엇을 만들어드릴까요?"</t>
+        </is>
+      </c>
+      <c r="C1954" t="inlineStr">
+        <is>
+          <t>"What shall I brew for you?"</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -14063,7 +14063,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest Entrance</t>
+          <t>Breezewood Forest Entrance</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14080,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest F2</t>
+          <t>Breezewood Forest F2</t>
         </is>
       </c>
     </row>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest F3</t>
+          <t>Breezewood Forest F3</t>
         </is>
       </c>
     </row>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest F4</t>
+          <t>Breezewood Forest F4</t>
         </is>
       </c>
     </row>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest F5</t>
+          <t>Breezewood Forest F5</t>
         </is>
       </c>
     </row>
@@ -14148,7 +14148,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest F6</t>
+          <t>Breezewood Forest F6</t>
         </is>
       </c>
     </row>
@@ -14165,7 +14165,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest F7</t>
+          <t>Breezewood Forest F7</t>
         </is>
       </c>
     </row>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest F8</t>
+          <t>Breezewood Forest F8</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14199,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest F9</t>
+          <t>Breezewood Forest F9</t>
         </is>
       </c>
     </row>
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest F10</t>
+          <t>Breezewood Forest F10</t>
         </is>
       </c>
     </row>
@@ -17565,7 +17565,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest Entrance</t>
+          <t>Breezewood Forest Entrance</t>
         </is>
       </c>
     </row>
@@ -17582,7 +17582,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest F2</t>
+          <t>Breezewood Forest F2</t>
         </is>
       </c>
     </row>
@@ -17599,7 +17599,7 @@
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest F3</t>
+          <t>Breezewood Forest F3</t>
         </is>
       </c>
     </row>
@@ -17616,7 +17616,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest F4</t>
+          <t>Breezewood Forest F4</t>
         </is>
       </c>
     </row>
@@ -17633,7 +17633,7 @@
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>Breezing Wind Forest Depths</t>
+          <t>Breezewood Forest Depths</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ABILITY DETAILS</t>
+          <t>ABILITY INFO</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1954"/>
+  <dimension ref="A1:C1956"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DESCRIP</t>
+          <t>DESC.</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
           <t>A pass issued by the guild.
 An official certification seal 
 is added to the temporary pass.
-One wrong move, and it ooks
+One wrong move, and it looks
 like it will fall apart.
 Can this really be used as a pass?</t>
         </is>
@@ -3874,12 +3874,20 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>[아직 내용이 없습니다.]</t>
+          <t>보급형보다 한층 진해진 신속 물약.
+마시면 발걸음이 가볍고
+심장이 조금 빨리 뛴다.
+색은 여전히 수상한 노란색이다.
+이번엔 굳이 물어보지 않았다.</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>[No description yet.]</t>
+          <t>A stronger brew than the budget one.
+Your steps feel lighter
+and your heart beats a little faster.
+Still that suspicious yellow.
+This time, I didn't ask.</t>
         </is>
       </c>
     </row>
@@ -35743,6 +35751,40 @@
         </is>
       </c>
     </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>RankFormat</t>
+        </is>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>{0}단계</t>
+        </is>
+      </c>
+      <c r="C1955" t="inlineStr">
+        <is>
+          <t>RANK {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>SwitchToItemsText</t>
+        </is>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>필요 재료</t>
+        </is>
+      </c>
+      <c r="C1956" t="inlineStr">
+        <is>
+          <t>ITEMS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1956"/>
+  <dimension ref="A1:C1965"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35785,6 +35785,159 @@
         </is>
       </c>
     </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>TrainingTitleText</t>
+        </is>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>훈련</t>
+        </is>
+      </c>
+      <c r="C1957" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>TrainingCapFormat</t>
+        </is>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>상한 Lv.{0}</t>
+        </is>
+      </c>
+      <c r="C1958" t="inlineStr">
+        <is>
+          <t>CAP Lv.{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>TrainAtkText</t>
+        </is>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>공격력</t>
+        </is>
+      </c>
+      <c r="C1959" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>TrainHpText</t>
+        </is>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>체력</t>
+        </is>
+      </c>
+      <c r="C1960" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>TrainDefText</t>
+        </is>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>방어력</t>
+        </is>
+      </c>
+      <c r="C1961" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>TrainCritDmgText</t>
+        </is>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>치명 피해</t>
+        </is>
+      </c>
+      <c r="C1962" t="inlineStr">
+        <is>
+          <t>CRIT DMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>TrainingRowFormat</t>
+        </is>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>{0}  Lv.{1}  +{2}%</t>
+        </is>
+      </c>
+      <c r="C1963" t="inlineStr">
+        <is>
+          <t>{0}  Lv.{1}  +{2}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>TrainingCostFormat</t>
+        </is>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>{0:N0} 골드</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr">
+        <is>
+          <t>{0:N0} G</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>TrainingMaxText</t>
+        </is>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>상한</t>
+        </is>
+      </c>
+      <c r="C1965" t="inlineStr">
+        <is>
+          <t>MAX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1965"/>
+  <dimension ref="A1:C1975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35938,6 +35938,176 @@
         </is>
       </c>
     </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>StageLabelFormat</t>
+        </is>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>{0}-{1}  {2}</t>
+        </is>
+      </c>
+      <c r="C1966" t="inlineStr">
+        <is>
+          <t>{0}-{1}  {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>StageKillFormat</t>
+        </is>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>처치 {0}/{1}</t>
+        </is>
+      </c>
+      <c r="C1967" t="inlineStr">
+        <is>
+          <t>KILLS {0}/{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
+        <is>
+          <t>StageBossNextText</t>
+        </is>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>다음은 보스!</t>
+        </is>
+      </c>
+      <c r="C1968" t="inlineStr">
+        <is>
+          <t>BOSS NEXT!</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
+        <is>
+          <t>StageBossChallengeText</t>
+        </is>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>눌러서 보스 도전</t>
+        </is>
+      </c>
+      <c r="C1969" t="inlineStr">
+        <is>
+          <t>TAP TO FIGHT THE BOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
+        <is>
+          <t>StageBossTimerFormat</t>
+        </is>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>보스 {0:0.0}초</t>
+        </is>
+      </c>
+      <c r="C1970" t="inlineStr">
+        <is>
+          <t>BOSS {0:0.0}s</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>BossAppearText</t>
+        </is>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>보스 출현!</t>
+        </is>
+      </c>
+      <c r="C1971" t="inlineStr">
+        <is>
+          <t>BOSS INCOMING!</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
+        <is>
+          <t>StageClearFormat</t>
+        </is>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>스테이지 돌파! 크리스탈 +{0}</t>
+        </is>
+      </c>
+      <c r="C1972" t="inlineStr">
+        <is>
+          <t>STAGE CLEAR! +{0} CRYSTALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>BossDefeatText</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>보스 처치!</t>
+        </is>
+      </c>
+      <c r="C1973" t="inlineStr">
+        <is>
+          <t>BOSS DEFEATED!</t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
+        <is>
+          <t>BossFailText</t>
+        </is>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>보스를 놓쳤다! 훈련 후 재도전</t>
+        </is>
+      </c>
+      <c r="C1974" t="inlineStr">
+        <is>
+          <t>BOSS ESCAPED! TRAIN UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>StageNextLockedFormat</t>
+        </is>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>다음 스테이지: {0}</t>
+        </is>
+      </c>
+      <c r="C1975" t="inlineStr">
+        <is>
+          <t>NEXT STAGE: {0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1975"/>
+  <dimension ref="A1:C1978"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36108,6 +36108,59 @@
         </is>
       </c>
     </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>ParryText</t>
+        </is>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>패링!</t>
+        </is>
+      </c>
+      <c r="C1976" t="inlineStr">
+        <is>
+          <t>PARRY!</t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>BlockText</t>
+        </is>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>막기</t>
+        </is>
+      </c>
+      <c r="C1977" t="inlineStr">
+        <is>
+          <t>BLOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>GuardHintText</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>'!'가 뜨면 화면을 눌러 막기
+딱 맞추면 패링!</t>
+        </is>
+      </c>
+      <c r="C1978" t="inlineStr">
+        <is>
+          <t>TAP WHEN "!" SHOWS TO BLOCK
+PERFECT TIMING = PARRY!</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1978"/>
+  <dimension ref="A1:C2005"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36161,6 +36161,465 @@
         </is>
       </c>
     </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>MissionTitleText</t>
+        </is>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>미션</t>
+        </is>
+      </c>
+      <c r="C1979" t="inlineStr">
+        <is>
+          <t>MISSIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>MissionDailyTabText</t>
+        </is>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>일일</t>
+        </is>
+      </c>
+      <c r="C1980" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>MissionWeeklyTabText</t>
+        </is>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>주간</t>
+        </is>
+      </c>
+      <c r="C1981" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>MissionGuideTabText</t>
+        </is>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>가이드</t>
+        </is>
+      </c>
+      <c r="C1982" t="inlineStr">
+        <is>
+          <t>GUIDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>MissionAttendanceTabText</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>출석</t>
+        </is>
+      </c>
+      <c r="C1983" t="inlineStr">
+        <is>
+          <t>LOGIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>MissionKillFormat</t>
+        </is>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>몬스터 {0}마리 처치</t>
+        </is>
+      </c>
+      <c r="C1984" t="inlineStr">
+        <is>
+          <t>Defeat monsters x{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>MissionBossFormat</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>보스 {0}회 처치</t>
+        </is>
+      </c>
+      <c r="C1985" t="inlineStr">
+        <is>
+          <t>Defeat bosses x{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>MissionStageFormat</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>스테이지 {0}곳 돌파</t>
+        </is>
+      </c>
+      <c r="C1986" t="inlineStr">
+        <is>
+          <t>Clear stages x{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>MissionTrainFormat</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>훈련 {0}회</t>
+        </is>
+      </c>
+      <c r="C1987" t="inlineStr">
+        <is>
+          <t>Train x{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>MissionCaptureFormat</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>포획 {0}회 시도</t>
+        </is>
+      </c>
+      <c r="C1988" t="inlineStr">
+        <is>
+          <t>Capture attempts x{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>MissionEnhanceFormat</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>장비 강화 {0}회</t>
+        </is>
+      </c>
+      <c r="C1989" t="inlineStr">
+        <is>
+          <t>Enhance gear x{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>MissionParryFormat</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>패링 {0}회</t>
+        </is>
+      </c>
+      <c r="C1990" t="inlineStr">
+        <is>
+          <t>Parry x{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>MissionDailyAllFormat</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>일일 미션 완료 {0}일</t>
+        </is>
+      </c>
+      <c r="C1991" t="inlineStr">
+        <is>
+          <t>Finish all dailies x{0} days</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>MissionDailyChestText</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>일일 미션 모두 완료</t>
+        </is>
+      </c>
+      <c r="C1992" t="inlineStr">
+        <is>
+          <t>Finish all daily missions</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>MissionLevelFormat</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>레벨 {0} 달성</t>
+        </is>
+      </c>
+      <c r="C1993" t="inlineStr">
+        <is>
+          <t>Reach Lv.{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>MissionDiscoverFormat</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>도감 {0}종 발견</t>
+        </is>
+      </c>
+      <c r="C1994" t="inlineStr">
+        <is>
+          <t>Discover {0} species</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>AttendanceDayFormat</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>{0}일째</t>
+        </is>
+      </c>
+      <c r="C1995" t="inlineStr">
+        <is>
+          <t>Day {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>MissionClaimText</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>받기</t>
+        </is>
+      </c>
+      <c r="C1996" t="inlineStr">
+        <is>
+          <t>CLAIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>MissionDoneText</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="C1997" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>MissionNextText</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>다음</t>
+        </is>
+      </c>
+      <c r="C1998" t="inlineStr">
+        <is>
+          <t>NEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>MissionGuideDoneText</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>가이드를 모두 마쳤다!</t>
+        </is>
+      </c>
+      <c r="C1999" t="inlineStr">
+        <is>
+          <t>All guide steps done!</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>AttendanceClaimedText</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>받음</t>
+        </is>
+      </c>
+      <c r="C2000" t="inlineStr">
+        <is>
+          <t>GOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>AttendanceTomorrowText</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>내일</t>
+        </is>
+      </c>
+      <c r="C2001" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>RewardCrystalFormat</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>크리스탈 {0}</t>
+        </is>
+      </c>
+      <c r="C2002" t="inlineStr">
+        <is>
+          <t>{0} CRYSTALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>RewardMandrakeFormat</t>
+        </is>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>만드라고라 {0}</t>
+        </is>
+      </c>
+      <c r="C2003" t="inlineStr">
+        <is>
+          <t>{0} MANDRAKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>RewardGoldFormat</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>골드 {0:N0}</t>
+        </is>
+      </c>
+      <c r="C2004" t="inlineStr">
+        <is>
+          <t>{0:N0} GOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>MissionClaimAllText</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>모두 받기</t>
+        </is>
+      </c>
+      <c r="C2005" t="inlineStr">
+        <is>
+          <t>CLAIM ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2005"/>
+  <dimension ref="A1:C2032"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36620,6 +36620,465 @@
         </is>
       </c>
     </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>MissionShopTabText</t>
+        </is>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>상점</t>
+        </is>
+      </c>
+      <c r="C2006" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>HotGoldText</t>
+        </is>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>골드 2배</t>
+        </is>
+      </c>
+      <c r="C2007" t="inlineStr">
+        <is>
+          <t>GOLD x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>HotExpText</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>경험치 2배</t>
+        </is>
+      </c>
+      <c r="C2008" t="inlineStr">
+        <is>
+          <t>EXP x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>HotAtkText</t>
+        </is>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>공격력 +20%</t>
+        </is>
+      </c>
+      <c r="C2009" t="inlineStr">
+        <is>
+          <t>ATK +20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>HotLeftFormat</t>
+        </is>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>(남은 {0})</t>
+        </is>
+      </c>
+      <c r="C2010" t="inlineStr">
+        <is>
+          <t>({0} LEFT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>AdWatchFormat</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>광고 보기 {0}</t>
+        </is>
+      </c>
+      <c r="C2011" t="inlineStr">
+        <is>
+          <t>WATCH AD {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>FreeCrystalFormat</t>
+        </is>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>무료 크리스탈 {0}</t>
+        </is>
+      </c>
+      <c r="C2012" t="inlineStr">
+        <is>
+          <t>FREE {0} CRYSTALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>OfflineDoubleText</t>
+        </is>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>오프라인 보상 한 번 더</t>
+        </is>
+      </c>
+      <c r="C2013" t="inlineStr">
+        <is>
+          <t>DOUBLE OFFLINE REWARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>MonthlyDailyFormat</t>
+        </is>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>월정액 오늘 크리스탈 {0} ({1}일 남음)</t>
+        </is>
+      </c>
+      <c r="C2014" t="inlineStr">
+        <is>
+          <t>MONTHLY: {0} CRYSTALS TODAY ({1}D LEFT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>MonthlyLeftFormat</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>{0}일 남음</t>
+        </is>
+      </c>
+      <c r="C2015" t="inlineStr">
+        <is>
+          <t>{0}D LEFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>MandrakeBuyFormat</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>만드라고라 1개 (보유 {0})</t>
+        </is>
+      </c>
+      <c r="C2016" t="inlineStr">
+        <is>
+          <t>1 MANDRAKE (HAVE {0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>FirstBuyBonusText</t>
+        </is>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>첫 구매 2배</t>
+        </is>
+      </c>
+      <c r="C2017" t="inlineStr">
+        <is>
+          <t>FIRST x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>PriceFormat</t>
+        </is>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>{0:N0}원</t>
+        </is>
+      </c>
+      <c r="C2018" t="inlineStr">
+        <is>
+          <t>KRW {0:N0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>OwnedText</t>
+        </is>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>구매함</t>
+        </is>
+      </c>
+      <c r="C2019" t="inlineStr">
+        <is>
+          <t>OWNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>ShopBoughtFormat</t>
+        </is>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>{0} 구매 완료(테스트)</t>
+        </is>
+      </c>
+      <c r="C2020" t="inlineStr">
+        <is>
+          <t>{0} PURCHASED (TEST)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>ShopNotReadyText</t>
+        </is>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>결제는 곧 열립니다</t>
+        </is>
+      </c>
+      <c r="C2021" t="inlineStr">
+        <is>
+          <t>STORE COMING SOON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>NotEnoughCrystalText</t>
+        </is>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t>크리스탈이 부족합니다</t>
+        </is>
+      </c>
+      <c r="C2022" t="inlineStr">
+        <is>
+          <t>NOT ENOUGH CRYSTALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>ProductStarterText</t>
+        </is>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>시작 패키지</t>
+        </is>
+      </c>
+      <c r="C2023" t="inlineStr">
+        <is>
+          <t>STARTER PACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>ProductStepUp1Text</t>
+        </is>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>스텝업 I</t>
+        </is>
+      </c>
+      <c r="C2024" t="inlineStr">
+        <is>
+          <t>STEP-UP I</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>ProductStepUp2Text</t>
+        </is>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>스텝업 II</t>
+        </is>
+      </c>
+      <c r="C2025" t="inlineStr">
+        <is>
+          <t>STEP-UP II</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>ProductStepUp3Text</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>스텝업 III</t>
+        </is>
+      </c>
+      <c r="C2026" t="inlineStr">
+        <is>
+          <t>STEP-UP III</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>ProductMonthlyText</t>
+        </is>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>월정액 (30일)</t>
+        </is>
+      </c>
+      <c r="C2027" t="inlineStr">
+        <is>
+          <t>MONTHLY PASS (30D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>ProductAdFreeText</t>
+        </is>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>광고 제거</t>
+        </is>
+      </c>
+      <c r="C2028" t="inlineStr">
+        <is>
+          <t>REMOVE ADS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>ProductCrystalFormat</t>
+        </is>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>크리스탈 {0}</t>
+        </is>
+      </c>
+      <c r="C2029" t="inlineStr">
+        <is>
+          <t>{0} CRYSTALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>StepLockedText</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>앞 단계 먼저</t>
+        </is>
+      </c>
+      <c r="C2030" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>HotDurationFormat</t>
+        </is>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>{0}분</t>
+        </is>
+      </c>
+      <c r="C2031" t="inlineStr">
+        <is>
+          <t>{0} MIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>ShopTitleText</t>
+        </is>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>상점</t>
+        </is>
+      </c>
+      <c r="C2032" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2032"/>
+  <dimension ref="A1:C2036"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36150,13 +36150,13 @@
       </c>
       <c r="B1978" t="inlineStr">
         <is>
-          <t>'!'가 뜨면 화면을 눌러 막기
+          <t>'!'가 뜨면 방패 버튼으로 막기
 딱 맞추면 패링!</t>
         </is>
       </c>
       <c r="C1978" t="inlineStr">
         <is>
-          <t>TAP WHEN "!" SHOWS TO BLOCK
+          <t>SHIELD WHEN "!" SHOWS
 PERFECT TIMING = PARRY!</t>
         </is>
       </c>
@@ -37076,6 +37076,74 @@
       <c r="C2032" t="inlineStr">
         <is>
           <t>SHOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>TapHintText</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>화면을 누르면 공격! 연타로 몰아치자</t>
+        </is>
+      </c>
+      <c r="C2033" t="inlineStr">
+        <is>
+          <t>TAP TO ATTACK! KEEP TAPPING!</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>AutoBattleText</t>
+        </is>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="C2034" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>AutoBattleOnText</t>
+        </is>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>자동 전투 켬 - 누르면 더 빨리 벤다</t>
+        </is>
+      </c>
+      <c r="C2035" t="inlineStr">
+        <is>
+          <t>AUTO ON - TAP TO STRIKE FASTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>AutoBattleOffText</t>
+        </is>
+      </c>
+      <c r="B2036" t="inlineStr">
+        <is>
+          <t>자동 전투 끔 - 눌러서 공격</t>
+        </is>
+      </c>
+      <c r="C2036" t="inlineStr">
+        <is>
+          <t>AUTO OFF - TAP TO ATTACK</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2036"/>
+  <dimension ref="A1:C2052"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37147,6 +37147,278 @@
         </is>
       </c>
     </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>MissionDungeonTabText</t>
+        </is>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>던전</t>
+        </is>
+      </c>
+      <c r="C2037" t="inlineStr">
+        <is>
+          <t>DUNGEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>DungeonTitleText</t>
+        </is>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>요일 던전</t>
+        </is>
+      </c>
+      <c r="C2038" t="inlineStr">
+        <is>
+          <t>DAILY DUNGEONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>DungeonGoldText</t>
+        </is>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>골드 던전</t>
+        </is>
+      </c>
+      <c r="C2039" t="inlineStr">
+        <is>
+          <t>GOLD DUNGEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>DungeonExpText</t>
+        </is>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>경험치 던전</t>
+        </is>
+      </c>
+      <c r="C2040" t="inlineStr">
+        <is>
+          <t>EXP DUNGEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>DungeonMatText</t>
+        </is>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>재료 던전</t>
+        </is>
+      </c>
+      <c r="C2041" t="inlineStr">
+        <is>
+          <t>MATERIAL DUNGEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
+        <is>
+          <t>DungeonTodayFormat</t>
+        </is>
+      </c>
+      <c r="B2042" t="inlineStr">
+        <is>
+          <t>오늘 {0}배</t>
+        </is>
+      </c>
+      <c r="C2042" t="inlineStr">
+        <is>
+          <t>TODAY x{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>DungeonBestFormat</t>
+        </is>
+      </c>
+      <c r="B2043" t="inlineStr">
+        <is>
+          <t>최고 {0}</t>
+        </is>
+      </c>
+      <c r="C2043" t="inlineStr">
+        <is>
+          <t>BEST {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>DungeonFreeFormat</t>
+        </is>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>입장 {0}/{1}</t>
+        </is>
+      </c>
+      <c r="C2044" t="inlineStr">
+        <is>
+          <t>ENTER {0}/{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>DungeonHelpFormat</t>
+        </is>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>{0}초 동안 잡은 만큼 보상 · 빨리 누를수록 많이 잡는다</t>
+        </is>
+      </c>
+      <c r="C2045" t="inlineStr">
+        <is>
+          <t>REWARDS FOR EVERY KILL IN {0}s - TAP FAST</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>DungeonHudFormat</t>
+        </is>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>남은 {0:0.0}초 · {1}마리</t>
+        </is>
+      </c>
+      <c r="C2046" t="inlineStr">
+        <is>
+          <t>{0:0.0}s · {1} KILLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>DungeonStartFormat</t>
+        </is>
+      </c>
+      <c r="B2047" t="inlineStr">
+        <is>
+          <t>{0} 시작! {1}초</t>
+        </is>
+      </c>
+      <c r="C2047" t="inlineStr">
+        <is>
+          <t>{0} - {1}s!</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>DungeonResultFormat</t>
+        </is>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>{0} 끝! {1}마리 · {2}</t>
+        </is>
+      </c>
+      <c r="C2048" t="inlineStr">
+        <is>
+          <t>{0} DONE! {1} KILLS · {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>DungeonMatRewardFormat</t>
+        </is>
+      </c>
+      <c r="B2049" t="inlineStr">
+        <is>
+          <t>재료 {0}개 · 만드라고라 {1}</t>
+        </is>
+      </c>
+      <c r="C2049" t="inlineStr">
+        <is>
+          <t>{0} MATERIALS · {1} MANDRAKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
+        <is>
+          <t>DungeonBusyText</t>
+        </is>
+      </c>
+      <c r="B2050" t="inlineStr">
+        <is>
+          <t>지금은 들어갈 수 없다</t>
+        </is>
+      </c>
+      <c r="C2050" t="inlineStr">
+        <is>
+          <t>CANNOT ENTER RIGHT NOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>RewardExpFormat</t>
+        </is>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>경험치 {0:N0}</t>
+        </is>
+      </c>
+      <c r="C2051" t="inlineStr">
+        <is>
+          <t>{0:N0} EXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
+        <is>
+          <t>MissionDungeonFormat</t>
+        </is>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>요일 던전 {0}회</t>
+        </is>
+      </c>
+      <c r="C2052" t="inlineStr">
+        <is>
+          <t>Dungeon runs x{0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2052"/>
+  <dimension ref="A1:C2109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37419,6 +37419,975 @@
         </is>
       </c>
     </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>MissionRelicTabText</t>
+        </is>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>유물</t>
+        </is>
+      </c>
+      <c r="C2053" t="inlineStr">
+        <is>
+          <t>RELICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
+        <is>
+          <t>RelicTitleText</t>
+        </is>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>유물</t>
+        </is>
+      </c>
+      <c r="C2054" t="inlineStr">
+        <is>
+          <t>RELICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>RelicSummonOneText</t>
+        </is>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>유물 소환 1회</t>
+        </is>
+      </c>
+      <c r="C2055" t="inlineStr">
+        <is>
+          <t>SUMMON x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
+        <is>
+          <t>RelicSummonTenText</t>
+        </is>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>유물 소환 10회</t>
+        </is>
+      </c>
+      <c r="C2056" t="inlineStr">
+        <is>
+          <t>SUMMON x10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>RelicSummonAdText</t>
+        </is>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>광고 보고 1회 소환</t>
+        </is>
+      </c>
+      <c r="C2057" t="inlineStr">
+        <is>
+          <t>SUMMON x1 (AD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
+        <is>
+          <t>RelicRatesRowFormat</t>
+        </is>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>확률 보기 · 전설 천장 {0}/{1}</t>
+        </is>
+      </c>
+      <c r="C2058" t="inlineStr">
+        <is>
+          <t>RATES · LEGEND PITY {0}/{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>RelicViewText</t>
+        </is>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>보기</t>
+        </is>
+      </c>
+      <c r="C2059" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
+        <is>
+          <t>RelicBackText</t>
+        </is>
+      </c>
+      <c r="B2060" t="inlineStr">
+        <is>
+          <t>← 목록으로</t>
+        </is>
+      </c>
+      <c r="C2060" t="inlineStr">
+        <is>
+          <t>← BACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>RelicGradeCommonText</t>
+        </is>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C2061" t="inlineStr">
+        <is>
+          <t>COMMON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
+        <is>
+          <t>RelicGradeRareText</t>
+        </is>
+      </c>
+      <c r="B2062" t="inlineStr">
+        <is>
+          <t>희귀</t>
+        </is>
+      </c>
+      <c r="C2062" t="inlineStr">
+        <is>
+          <t>RARE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>RelicGradeEpicText</t>
+        </is>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>영웅</t>
+        </is>
+      </c>
+      <c r="C2063" t="inlineStr">
+        <is>
+          <t>EPIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>RelicGradeLegendaryText</t>
+        </is>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>전설</t>
+        </is>
+      </c>
+      <c r="C2064" t="inlineStr">
+        <is>
+          <t>LEGEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>RelicRowFormat</t>
+        </is>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>[{0}] {1} Lv.{2}</t>
+        </is>
+      </c>
+      <c r="C2065" t="inlineStr">
+        <is>
+          <t>[{0}] {1} Lv.{2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>RelicNotOwnedText</t>
+        </is>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>미획득</t>
+        </is>
+      </c>
+      <c r="C2066" t="inlineStr">
+        <is>
+          <t>NOT OWNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>RelicAtkFormat</t>
+        </is>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>공격력 +{0}%</t>
+        </is>
+      </c>
+      <c r="C2067" t="inlineStr">
+        <is>
+          <t>ATK +{0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>RelicHpFormat</t>
+        </is>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>체력 +{0}%</t>
+        </is>
+      </c>
+      <c r="C2068" t="inlineStr">
+        <is>
+          <t>HP +{0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>RelicDefFormat</t>
+        </is>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>방어력 +{0}%</t>
+        </is>
+      </c>
+      <c r="C2069" t="inlineStr">
+        <is>
+          <t>DEF +{0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
+        <is>
+          <t>RelicCritDmgFormat</t>
+        </is>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>치명 피해 +{0}%p</t>
+        </is>
+      </c>
+      <c r="C2070" t="inlineStr">
+        <is>
+          <t>CRIT DMG +{0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>RelicGoldFormat</t>
+        </is>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>골드 +{0}%</t>
+        </is>
+      </c>
+      <c r="C2071" t="inlineStr">
+        <is>
+          <t>GOLD +{0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
+        <is>
+          <t>RelicExpFormat</t>
+        </is>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>경험치 +{0}%</t>
+        </is>
+      </c>
+      <c r="C2072" t="inlineStr">
+        <is>
+          <t>EXP +{0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
+        <is>
+          <t>RelicDropFormat</t>
+        </is>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>획득률 +{0}%p</t>
+        </is>
+      </c>
+      <c r="C2073" t="inlineStr">
+        <is>
+          <t>DROP +{0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
+        <is>
+          <t>RelicInterestFormat</t>
+        </is>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>관심 확률 +{0}%</t>
+        </is>
+      </c>
+      <c r="C2074" t="inlineStr">
+        <is>
+          <t>INTEREST +{0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>RelicGradeRateFormat</t>
+        </is>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>{0} {1}% · {2}종 · 각 {3:0.###}%</t>
+        </is>
+      </c>
+      <c r="C2075" t="inlineStr">
+        <is>
+          <t>{0} {1}% · {2} KINDS · {3:0.###}% EACH</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
+        <is>
+          <t>RelicPityInfoFormat</t>
+        </is>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>전설 천장: {0}회 안에 전설 1개 확정 (지금 {1}회째)</t>
+        </is>
+      </c>
+      <c r="C2076" t="inlineStr">
+        <is>
+          <t>LEGEND PITY: ONE WITHIN {0} SUMMONS (NOW {1})</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>RelicResultFormat</t>
+        </is>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>유물 {0}회: 전설 {1} · 영웅 {2} · 희귀 {3} · 일반 {4}</t>
+        </is>
+      </c>
+      <c r="C2077" t="inlineStr">
+        <is>
+          <t>{0} SUMMONS: LEGEND {1} · EPIC {2} · RARE {3} · COMMON {4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
+        <is>
+          <t>RelicRefundFormat</t>
+        </is>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · 최대 레벨 환급 크리스탈 {0}</t>
+        </is>
+      </c>
+      <c r="C2078" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · MAX LV REFUND {0} CRYSTALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
+        <is>
+          <t>RelicLegendText</t>
+        </is>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>전설 유물!</t>
+        </is>
+      </c>
+      <c r="C2079" t="inlineStr">
+        <is>
+          <t>LEGENDARY!</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
+        <is>
+          <t>Relic8001NameText</t>
+        </is>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>녹슨 칼자루</t>
+        </is>
+      </c>
+      <c r="C2080" t="inlineStr">
+        <is>
+          <t>Rusty Hilt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
+        <is>
+          <t>Relic8002NameText</t>
+        </is>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>늑대 송곳니 부적</t>
+        </is>
+      </c>
+      <c r="C2081" t="inlineStr">
+        <is>
+          <t>Wolf Fang Charm</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
+        <is>
+          <t>Relic8003NameText</t>
+        </is>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>전사의 문장</t>
+        </is>
+      </c>
+      <c r="C2082" t="inlineStr">
+        <is>
+          <t>Warrior's Crest</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
+        <is>
+          <t>Relic8004NameText</t>
+        </is>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>불꽃 룬석</t>
+        </is>
+      </c>
+      <c r="C2083" t="inlineStr">
+        <is>
+          <t>Flame Runestone</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
+        <is>
+          <t>Relic8005NameText</t>
+        </is>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>용사의 건틀릿</t>
+        </is>
+      </c>
+      <c r="C2084" t="inlineStr">
+        <is>
+          <t>Hero's Gauntlet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
+        <is>
+          <t>Relic8006NameText</t>
+        </is>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>태양의 왕관</t>
+        </is>
+      </c>
+      <c r="C2085" t="inlineStr">
+        <is>
+          <t>Crown of the Sun</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
+        <is>
+          <t>Relic8007NameText</t>
+        </is>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>이끼 낀 조약돌</t>
+        </is>
+      </c>
+      <c r="C2086" t="inlineStr">
+        <is>
+          <t>Mossy Pebble</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
+        <is>
+          <t>Relic8008NameText</t>
+        </is>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>산딸기 병</t>
+        </is>
+      </c>
+      <c r="C2087" t="inlineStr">
+        <is>
+          <t>Berry Jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
+        <is>
+          <t>Relic8009NameText</t>
+        </is>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>생명의 도토리</t>
+        </is>
+      </c>
+      <c r="C2088" t="inlineStr">
+        <is>
+          <t>Acorn of Life</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
+        <is>
+          <t>Relic8010NameText</t>
+        </is>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>거인의 심장</t>
+        </is>
+      </c>
+      <c r="C2089" t="inlineStr">
+        <is>
+          <t>Giant's Heart</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
+        <is>
+          <t>Relic8011NameText</t>
+        </is>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>세계수의 잎</t>
+        </is>
+      </c>
+      <c r="C2090" t="inlineStr">
+        <is>
+          <t>World Tree Leaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
+        <is>
+          <t>Relic8012NameText</t>
+        </is>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>방패 조각</t>
+        </is>
+      </c>
+      <c r="C2091" t="inlineStr">
+        <is>
+          <t>Shield Shard</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
+        <is>
+          <t>Relic8013NameText</t>
+        </is>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>거북 등딱지</t>
+        </is>
+      </c>
+      <c r="C2092" t="inlineStr">
+        <is>
+          <t>Turtle Shell</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>Relic8014NameText</t>
+        </is>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>철갑 견장</t>
+        </is>
+      </c>
+      <c r="C2093" t="inlineStr">
+        <is>
+          <t>Iron Pauldron</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
+        <is>
+          <t>Relic8015NameText</t>
+        </is>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>수호자의 성배</t>
+        </is>
+      </c>
+      <c r="C2094" t="inlineStr">
+        <is>
+          <t>Guardian's Chalice</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
+        <is>
+          <t>Relic8016NameText</t>
+        </is>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>날 선 부싯돌</t>
+        </is>
+      </c>
+      <c r="C2095" t="inlineStr">
+        <is>
+          <t>Sharp Flint</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
+        <is>
+          <t>Relic8017NameText</t>
+        </is>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>매의 눈</t>
+        </is>
+      </c>
+      <c r="C2096" t="inlineStr">
+        <is>
+          <t>Hawk's Eye</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>Relic8018NameText</t>
+        </is>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>흡혈 송곳니</t>
+        </is>
+      </c>
+      <c r="C2097" t="inlineStr">
+        <is>
+          <t>Vampire Fang</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
+        <is>
+          <t>Relic8019NameText</t>
+        </is>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>파멸의 단검</t>
+        </is>
+      </c>
+      <c r="C2098" t="inlineStr">
+        <is>
+          <t>Dagger of Ruin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
+        <is>
+          <t>Relic8020NameText</t>
+        </is>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>구리 동전</t>
+        </is>
+      </c>
+      <c r="C2099" t="inlineStr">
+        <is>
+          <t>Copper Coin</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
+        <is>
+          <t>Relic8021NameText</t>
+        </is>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>가죽 지갑</t>
+        </is>
+      </c>
+      <c r="C2100" t="inlineStr">
+        <is>
+          <t>Leather Purse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>Relic8022NameText</t>
+        </is>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>행운의 편자</t>
+        </is>
+      </c>
+      <c r="C2101" t="inlineStr">
+        <is>
+          <t>Lucky Horseshoe</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
+        <is>
+          <t>Relic8023NameText</t>
+        </is>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>황금 두꺼비</t>
+        </is>
+      </c>
+      <c r="C2102" t="inlineStr">
+        <is>
+          <t>Golden Toad</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>Relic8024NameText</t>
+        </is>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>낡은 일지</t>
+        </is>
+      </c>
+      <c r="C2103" t="inlineStr">
+        <is>
+          <t>Old Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
+        <is>
+          <t>Relic8025NameText</t>
+        </is>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>현자의 안경</t>
+        </is>
+      </c>
+      <c r="C2104" t="inlineStr">
+        <is>
+          <t>Sage's Spectacles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>Relic8026NameText</t>
+        </is>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>푸른 모래시계</t>
+        </is>
+      </c>
+      <c r="C2105" t="inlineStr">
+        <is>
+          <t>Blue Hourglass</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
+        <is>
+          <t>Relic8027NameText</t>
+        </is>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>별의 두루마리</t>
+        </is>
+      </c>
+      <c r="C2106" t="inlineStr">
+        <is>
+          <t>Star Scroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
+        <is>
+          <t>Relic8028NameText</t>
+        </is>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>찢어진 자루</t>
+        </is>
+      </c>
+      <c r="C2107" t="inlineStr">
+        <is>
+          <t>Torn Sack</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
+        <is>
+          <t>Relic8029NameText</t>
+        </is>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>수집가의 갈고리</t>
+        </is>
+      </c>
+      <c r="C2108" t="inlineStr">
+        <is>
+          <t>Collector's Hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>Relic8030NameText</t>
+        </is>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>달콤한 꿀단지</t>
+        </is>
+      </c>
+      <c r="C2109" t="inlineStr">
+        <is>
+          <t>Honey Pot</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2109"/>
+  <dimension ref="A1:C2127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38388,6 +38388,312 @@
         </is>
       </c>
     </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>MissionTownTabText</t>
+        </is>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>마을</t>
+        </is>
+      </c>
+      <c r="C2110" t="inlineStr">
+        <is>
+          <t>TOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>BondTitleText</t>
+        </is>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>마을 사람들</t>
+        </is>
+      </c>
+      <c r="C2111" t="inlineStr">
+        <is>
+          <t>VILLAGERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>BondRequestHeaderText</t>
+        </is>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>오늘의 배달 의뢰 · 매일 00시에 새로</t>
+        </is>
+      </c>
+      <c r="C2112" t="inlineStr">
+        <is>
+          <t>ERRANDS OF THE DAY · NEW EVERY DAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>BondDeliverFormat</t>
+        </is>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>{0}: {1} {2}개 배달</t>
+        </is>
+      </c>
+      <c r="C2113" t="inlineStr">
+        <is>
+          <t>{0}: DELIVER {2} {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>BondHuntFormat</t>
+        </is>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>{0}: {1}에서 {2}마리</t>
+        </is>
+      </c>
+      <c r="C2114" t="inlineStr">
+        <is>
+          <t>{0}: DEFEAT {2} IN {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>BondDeliverText</t>
+        </is>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>배달</t>
+        </is>
+      </c>
+      <c r="C2115" t="inlineStr">
+        <is>
+          <t>DELIVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>BondPeopleHeaderFormat</t>
+        </is>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>마을 사람들 · 선물 = 가장 많은 재료 {0}개</t>
+        </is>
+      </c>
+      <c r="C2116" t="inlineStr">
+        <is>
+          <t>VILLAGERS · GIFT = {0} OF YOUR MOST COMMON MATERIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>BondNpcFormat</t>
+        </is>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>{0} Lv.{1} ({2})</t>
+        </is>
+      </c>
+      <c r="C2117" t="inlineStr">
+        <is>
+          <t>{0} Lv.{1} ({2})</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>BondGiftFormat</t>
+        </is>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>선물 {0}</t>
+        </is>
+      </c>
+      <c r="C2118" t="inlineStr">
+        <is>
+          <t>GIFT {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>BondPerkReceptionistFormat</t>
+        </is>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>의뢰 보상 +{0}%</t>
+        </is>
+      </c>
+      <c r="C2119" t="inlineStr">
+        <is>
+          <t>ERRAND REWARD +{0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>BondPerkAlchemistFormat</t>
+        </is>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>회복력 +{0}%</t>
+        </is>
+      </c>
+      <c r="C2120" t="inlineStr">
+        <is>
+          <t>RECOVERY +{0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>BondPerkBlacksmithFormat</t>
+        </is>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>강화 비용 -{0}%</t>
+        </is>
+      </c>
+      <c r="C2121" t="inlineStr">
+        <is>
+          <t>ENHANCE COST -{0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>BondPerkPriestFormat</t>
+        </is>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>숙련도 +1 확률 {0}%</t>
+        </is>
+      </c>
+      <c r="C2122" t="inlineStr">
+        <is>
+          <t>EXTRA PROFICIENCY {0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>BondPerkShopkeeperFormat</t>
+        </is>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>상점 가격 -{0}%</t>
+        </is>
+      </c>
+      <c r="C2123" t="inlineStr">
+        <is>
+          <t>SHOP PRICE -{0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>BondDoneFormat</t>
+        </is>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>{0}의 의뢰 완료! {1}</t>
+        </is>
+      </c>
+      <c r="C2124" t="inlineStr">
+        <is>
+          <t>ERRAND DONE FOR {0}! {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>BondNoGiftText</t>
+        </is>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>선물할 재료가 모자라다</t>
+        </is>
+      </c>
+      <c r="C2125" t="inlineStr">
+        <is>
+          <t>NOT ENOUGH MATERIALS TO GIFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>BondLevelUpFormat</t>
+        </is>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>{0} 호감도 Lv.{1}!</t>
+        </is>
+      </c>
+      <c r="C2126" t="inlineStr">
+        <is>
+          <t>{0} BOND Lv.{1}!</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>MissionBondFormat</t>
+        </is>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>배달 의뢰 {0}건</t>
+        </is>
+      </c>
+      <c r="C2127" t="inlineStr">
+        <is>
+          <t>Errands x{0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2127"/>
+  <dimension ref="A1:C2141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37172,12 +37172,12 @@
       </c>
       <c r="B2038" t="inlineStr">
         <is>
-          <t>요일 던전</t>
+          <t>던전</t>
         </is>
       </c>
       <c r="C2038" t="inlineStr">
         <is>
-          <t>DAILY DUNGEONS</t>
+          <t>DUNGEONS</t>
         </is>
       </c>
     </row>
@@ -38691,6 +38691,244 @@
       <c r="C2127" t="inlineStr">
         <is>
           <t>Errands x{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>PromotionRowFormat</t>
+        </is>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>시련 {0}단계 · 공격·체력 ×{1:0.##}</t>
+        </is>
+      </c>
+      <c r="C2128" t="inlineStr">
+        <is>
+          <t>TRIAL RANK {0} · ATK/HP x{1:0.##}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>PromotionReqFormat</t>
+        </is>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>Lv.{0} 필요</t>
+        </is>
+      </c>
+      <c r="C2129" t="inlineStr">
+        <is>
+          <t>NEEDS Lv.{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>PromotionChallengeText</t>
+        </is>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>도전</t>
+        </is>
+      </c>
+      <c r="C2130" t="inlineStr">
+        <is>
+          <t>CHALLENGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>PromotionMaxText</t>
+        </is>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>최고 단계</t>
+        </is>
+      </c>
+      <c r="C2131" t="inlineStr">
+        <is>
+          <t>MAX RANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>PromotionHudFormat</t>
+        </is>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>시련 {0}단계</t>
+        </is>
+      </c>
+      <c r="C2132" t="inlineStr">
+        <is>
+          <t>TRIAL {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>PromotionStartFormat</t>
+        </is>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>시련 {0}단계! {1}초 안에 시험관을 쓰러뜨려라</t>
+        </is>
+      </c>
+      <c r="C2133" t="inlineStr">
+        <is>
+          <t>TRIAL {0}! DEFEAT THE EXAMINER IN {1}s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>PromotionPassFormat</t>
+        </is>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>시련 {0}단계 통과! 공격·체력 ×{1:0.##}</t>
+        </is>
+      </c>
+      <c r="C2134" t="inlineStr">
+        <is>
+          <t>TRIAL {0} PASSED! ATK/HP x{1:0.##}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>PromotionFailText</t>
+        </is>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>시련 실패 — 더 강해져서 다시 도전</t>
+        </is>
+      </c>
+      <c r="C2135" t="inlineStr">
+        <is>
+          <t>TRIAL FAILED - GET STRONGER AND RETRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>AbyssRowFormat</t>
+        </is>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>심연 · 최고 {0}층</t>
+        </is>
+      </c>
+      <c r="C2136" t="inlineStr">
+        <is>
+          <t>ABYSS · BEST F{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>AbyssLockedText</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>전 스테이지 돌파</t>
+        </is>
+      </c>
+      <c r="C2137" t="inlineStr">
+        <is>
+          <t>CLEAR ALL STAGES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>AbyssHudFormat</t>
+        </is>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>심연 {0}층</t>
+        </is>
+      </c>
+      <c r="C2138" t="inlineStr">
+        <is>
+          <t>ABYSS F{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>AbyssStartFormat</t>
+        </is>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>심연으로 (최고 {0}층)</t>
+        </is>
+      </c>
+      <c r="C2139" t="inlineStr">
+        <is>
+          <t>INTO THE ABYSS (BEST F{0})</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>AbyssBossFormat</t>
+        </is>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>심연 {0}층 수문장!</t>
+        </is>
+      </c>
+      <c r="C2140" t="inlineStr">
+        <is>
+          <t>ABYSS F{0} GUARDIAN!</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>AbyssResultFormat</t>
+        </is>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>심연 {0}층에서 멈췄다 · 최고 {1}층 · 크리스탈 +{2}</t>
+        </is>
+      </c>
+      <c r="C2141" t="inlineStr">
+        <is>
+          <t>STOPPED AT F{0} · BEST F{1} · +{2} CRYSTALS</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2141"/>
+  <dimension ref="A1:C2142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38932,6 +38932,23 @@
         </is>
       </c>
     </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>AutoUnlockText</t>
+        </is>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>자동 전투가 열렸다! 이제 알아서 싸운다 · AUTO 로 끄고 켠다</t>
+        </is>
+      </c>
+      <c r="C2142" t="inlineStr">
+        <is>
+          <t>AUTO BATTLE UNLOCKED! TOGGLE IT WITH AUTO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2142"/>
+  <dimension ref="A1:C2148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38949,6 +38949,108 @@
         </is>
       </c>
     </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>MissionPassTabText</t>
+        </is>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>패스</t>
+        </is>
+      </c>
+      <c r="C2143" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>PassTitleText</t>
+        </is>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>성장 패스</t>
+        </is>
+      </c>
+      <c r="C2144" t="inlineStr">
+        <is>
+          <t>GROWTH PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>PassHeaderFormat</t>
+        </is>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>스테이지 돌파 {0}/{1} · 5곳마다 보상</t>
+        </is>
+      </c>
+      <c r="C2145" t="inlineStr">
+        <is>
+          <t>STAGES {0}/{1} · REWARD EVERY 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>PassPremiumOnText</t>
+        </is>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>프리미엄</t>
+        </is>
+      </c>
+      <c r="C2146" t="inlineStr">
+        <is>
+          <t>PREMIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>PassPremiumFormat</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>프리미엄 {0}</t>
+        </is>
+      </c>
+      <c r="C2147" t="inlineStr">
+        <is>
+          <t>PREMIUM {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>ProductGrowthPassText</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>성장 패스</t>
+        </is>
+      </c>
+      <c r="C2148" t="inlineStr">
+        <is>
+          <t>GROWTH PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2148"/>
+  <dimension ref="A1:C2173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39051,6 +39051,431 @@
         </is>
       </c>
     </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>MissionAchieveTabText</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>업적</t>
+        </is>
+      </c>
+      <c r="C2149" t="inlineStr">
+        <is>
+          <t>FEATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>AchieveTitleText</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>업적</t>
+        </is>
+      </c>
+      <c r="C2150" t="inlineStr">
+        <is>
+          <t>ACHIEVEMENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>HonorRowFormat</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>칭호: {0}  ({1}/{2} 모음)</t>
+        </is>
+      </c>
+      <c r="C2151" t="inlineStr">
+        <is>
+          <t>TITLE: {0}  ({1}/{2})</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>HonorNoneText</t>
+        </is>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="C2152" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>HonorChangeText</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>바꾸기</t>
+        </is>
+      </c>
+      <c r="C2153" t="inlineStr">
+        <is>
+          <t>CHANGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>HonorTagFormat</t>
+        </is>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>칭호 [{0}]</t>
+        </is>
+      </c>
+      <c r="C2154" t="inlineStr">
+        <is>
+          <t>TITLE [{0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>HonorGetFormat</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>칭호 획득! [{0}]</t>
+        </is>
+      </c>
+      <c r="C2155" t="inlineStr">
+        <is>
+          <t>NEW TITLE! [{0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>HonorHunterText</t>
+        </is>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>사냥꾼</t>
+        </is>
+      </c>
+      <c r="C2156" t="inlineStr">
+        <is>
+          <t>HUNTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>HonorSlayerText</t>
+        </is>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>마물 학살자</t>
+        </is>
+      </c>
+      <c r="C2157" t="inlineStr">
+        <is>
+          <t>SLAYER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>HonorLegendText</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>전설의 사냥꾼</t>
+        </is>
+      </c>
+      <c r="C2158" t="inlineStr">
+        <is>
+          <t>LEGEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>HonorBossHunterText</t>
+        </is>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>보스 사냥꾼</t>
+        </is>
+      </c>
+      <c r="C2159" t="inlineStr">
+        <is>
+          <t>BOSSBANE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>HonorPioneerText</t>
+        </is>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>개척자</t>
+        </is>
+      </c>
+      <c r="C2160" t="inlineStr">
+        <is>
+          <t>PIONEER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>HonorConquerorText</t>
+        </is>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>대륙 정복자</t>
+        </is>
+      </c>
+      <c r="C2161" t="inlineStr">
+        <is>
+          <t>CONQUEROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>HonorMaxText</t>
+        </is>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>만렙 여행자</t>
+        </is>
+      </c>
+      <c r="C2162" t="inlineStr">
+        <is>
+          <t>MAX LEVEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>HonorScholarText</t>
+        </is>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>마물 학자</t>
+        </is>
+      </c>
+      <c r="C2163" t="inlineStr">
+        <is>
+          <t>SCHOLAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>HonorCodexText</t>
+        </is>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>살아있는 도감</t>
+        </is>
+      </c>
+      <c r="C2164" t="inlineStr">
+        <is>
+          <t>CODEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>HonorTamerText</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>조련사</t>
+        </is>
+      </c>
+      <c r="C2165" t="inlineStr">
+        <is>
+          <t>TAMER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>HonorParryText</t>
+        </is>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>패링 달인</t>
+        </is>
+      </c>
+      <c r="C2166" t="inlineStr">
+        <is>
+          <t>PARRY ACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>HonorIronWallText</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>철벽</t>
+        </is>
+      </c>
+      <c r="C2167" t="inlineStr">
+        <is>
+          <t>IRON WALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>HonorGrinderText</t>
+        </is>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>수련광</t>
+        </is>
+      </c>
+      <c r="C2168" t="inlineStr">
+        <is>
+          <t>GRINDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>HonorSmithText</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>대장간 단골</t>
+        </is>
+      </c>
+      <c r="C2169" t="inlineStr">
+        <is>
+          <t>SMITHY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>HonorDungeonText</t>
+        </is>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>던전 탐험가</t>
+        </is>
+      </c>
+      <c r="C2170" t="inlineStr">
+        <is>
+          <t>DELVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>HonorFixerText</t>
+        </is>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>마을의 해결사</t>
+        </is>
+      </c>
+      <c r="C2171" t="inlineStr">
+        <is>
+          <t>FIXER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>HonorDiligentText</t>
+        </is>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>성실한 여행자</t>
+        </is>
+      </c>
+      <c r="C2172" t="inlineStr">
+        <is>
+          <t>DILIGENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>HonorGetManyFormat</t>
+        </is>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>칭호 획득! [{0}] 외 {1}개</t>
+        </is>
+      </c>
+      <c r="C2173" t="inlineStr">
+        <is>
+          <t>NEW TITLES! [{0}] +{1}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2173"/>
+  <dimension ref="A1:C2182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39476,6 +39476,159 @@
         </is>
       </c>
     </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>OffDutyRowFormat</t>
+        </is>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>비번 일정: {0} — {1}</t>
+        </is>
+      </c>
+      <c r="C2174" t="inlineStr">
+        <is>
+          <t>OFF-DUTY: {0} — {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>OffDutyHuntText</t>
+        </is>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>사냥</t>
+        </is>
+      </c>
+      <c r="C2175" t="inlineStr">
+        <is>
+          <t>HUNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>OffDutyHuntDesc</t>
+        </is>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>골드·경험치</t>
+        </is>
+      </c>
+      <c r="C2176" t="inlineStr">
+        <is>
+          <t>GOLD &amp; EXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>OffDutyGatherText</t>
+        </is>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>채집</t>
+        </is>
+      </c>
+      <c r="C2177" t="inlineStr">
+        <is>
+          <t>GATHER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>OffDutyGatherDesc</t>
+        </is>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>재료 (골드·경험치 20%)</t>
+        </is>
+      </c>
+      <c r="C2178" t="inlineStr">
+        <is>
+          <t>MATERIALS (20% GOLD &amp; EXP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>OffDutyHelpText</t>
+        </is>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>마을 일</t>
+        </is>
+      </c>
+      <c r="C2179" t="inlineStr">
+        <is>
+          <t>TOWN WORK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>OffDutyHelpDesc</t>
+        </is>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>모두의 호감도 (골드·경험치 20%)</t>
+        </is>
+      </c>
+      <c r="C2180" t="inlineStr">
+        <is>
+          <t>BOND WITH ALL (20% GOLD &amp; EXP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>OffDutyGatherResultFormat</t>
+        </is>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>채집: 재료 {0}개 · {1}</t>
+        </is>
+      </c>
+      <c r="C2181" t="inlineStr">
+        <is>
+          <t>GATHERED {0} MATERIALS · {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>OffDutyHelpResultFormat</t>
+        </is>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>마을 일: 모두의 호감도 +{0}</t>
+        </is>
+      </c>
+      <c r="C2182" t="inlineStr">
+        <is>
+          <t>TOWN WORK: BOND +{0} WITH ALL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2182"/>
+  <dimension ref="A1:C2185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38498,12 +38498,12 @@
       </c>
       <c r="B2116" t="inlineStr">
         <is>
-          <t>마을 사람들 · 선물 = 가장 많은 재료 {0}개</t>
+          <t>마을 사람들 · 선물 = 재료 {0}개 (♡ 좋아하는 재료면 호감도 2배)</t>
         </is>
       </c>
       <c r="C2116" t="inlineStr">
         <is>
-          <t>VILLAGERS · GIFT = {0} OF YOUR MOST COMMON MATERIAL</t>
+          <t>VILLAGERS · GIFT = {0} MATERIALS (♡ LIKED = DOUBLE BOND)</t>
         </is>
       </c>
     </row>
@@ -39626,6 +39626,57 @@
       <c r="C2182" t="inlineStr">
         <is>
           <t>TOWN WORK: BOND +{0} WITH ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>BondSceneNewText</t>
+        </is>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>새 이야기!</t>
+        </is>
+      </c>
+      <c r="C2183" t="inlineStr">
+        <is>
+          <t>NEW STORY!</t>
+        </is>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>BondSceneDoneFormat</t>
+        </is>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>{0}와(과)의 이야기 · 크리스탈 +{1}</t>
+        </is>
+      </c>
+      <c r="C2184" t="inlineStr">
+        <is>
+          <t>A STORY WITH {0} · +{1} CRYSTALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>BondLikedGiftFormat</t>
+        </is>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>{0}: 좋아한다! 호감도 +{1}</t>
+        </is>
+      </c>
+      <c r="C2185" t="inlineStr">
+        <is>
+          <t>{0}: LOVES IT! BOND +{1}</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2185"/>
+  <dimension ref="A1:C2205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39680,6 +39680,346 @@
         </is>
       </c>
     </row>
+    <row r="2186">
+      <c r="A2186" t="inlineStr">
+        <is>
+          <t>MissionCostumeTabText</t>
+        </is>
+      </c>
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>의상</t>
+        </is>
+      </c>
+      <c r="C2186" t="inlineStr">
+        <is>
+          <t>OUTFITS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>CostumeTitleText</t>
+        </is>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>의상실</t>
+        </is>
+      </c>
+      <c r="C2187" t="inlineStr">
+        <is>
+          <t>WARDROBE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
+        <is>
+          <t>CostumeTotalText</t>
+        </is>
+      </c>
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>모은 의상</t>
+        </is>
+      </c>
+      <c r="C2188" t="inlineStr">
+        <is>
+          <t>COLLECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>CostumeCountFormat</t>
+        </is>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>{0}/{1}벌</t>
+        </is>
+      </c>
+      <c r="C2189" t="inlineStr">
+        <is>
+          <t>{0}/{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
+        <is>
+          <t>CostumeWornText</t>
+        </is>
+      </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>착용 중</t>
+        </is>
+      </c>
+      <c r="C2190" t="inlineStr">
+        <is>
+          <t>WORN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>CostumeWearText</t>
+        </is>
+      </c>
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>입기</t>
+        </is>
+      </c>
+      <c r="C2191" t="inlineStr">
+        <is>
+          <t>WEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
+        <is>
+          <t>CostumeBuyConfirmText</t>
+        </is>
+      </c>
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>다시 눌러 구매</t>
+        </is>
+      </c>
+      <c r="C2192" t="inlineStr">
+        <is>
+          <t>TAP TO CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>CostumeLevelFormat</t>
+        </is>
+      </c>
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>Lv {0} 달성</t>
+        </is>
+      </c>
+      <c r="C2193" t="inlineStr">
+        <is>
+          <t>REACH LV {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t>CostumePromotionFormat</t>
+        </is>
+      </c>
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t>시련 {0}단계</t>
+        </is>
+      </c>
+      <c r="C2194" t="inlineStr">
+        <is>
+          <t>TRIAL {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>CostumeAbyssFormat</t>
+        </is>
+      </c>
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>심연 {0}층</t>
+        </is>
+      </c>
+      <c r="C2195" t="inlineStr">
+        <is>
+          <t>ABYSS {0}F</t>
+        </is>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
+        <is>
+          <t>CostumeNewFormat</t>
+        </is>
+      </c>
+      <c r="B2196" t="inlineStr">
+        <is>
+          <t>새 의상: {0}! 미션 창 의상 탭에서 입을 수 있다</t>
+        </is>
+      </c>
+      <c r="C2196" t="inlineStr">
+        <is>
+          <t>NEW OUTFIT: {0}! WEAR IT FROM THE OUTFITS TAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>CostumeBoughtFormat</t>
+        </is>
+      </c>
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>{0} 획득! 바로 입었다</t>
+        </is>
+      </c>
+      <c r="C2197" t="inlineStr">
+        <is>
+          <t>{0} GET! NOW WEARING IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="inlineStr">
+        <is>
+          <t>CostumeBaseName</t>
+        </is>
+      </c>
+      <c r="B2198" t="inlineStr">
+        <is>
+          <t>떠돌이 모험가</t>
+        </is>
+      </c>
+      <c r="C2198" t="inlineStr">
+        <is>
+          <t>WANDERER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>CostumeCrimsonName</t>
+        </is>
+      </c>
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>진홍 기사</t>
+        </is>
+      </c>
+      <c r="C2199" t="inlineStr">
+        <is>
+          <t>CRIMSON KNIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>CostumeForestName</t>
+        </is>
+      </c>
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>숲의 수호자</t>
+        </is>
+      </c>
+      <c r="C2200" t="inlineStr">
+        <is>
+          <t>FOREST WARDEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>CostumeFrostName</t>
+        </is>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>서리 방랑자</t>
+        </is>
+      </c>
+      <c r="C2201" t="inlineStr">
+        <is>
+          <t>FROST NOMAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>CostumeNightName</t>
+        </is>
+      </c>
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>밤의 추적자</t>
+        </is>
+      </c>
+      <c r="C2202" t="inlineStr">
+        <is>
+          <t>NIGHT STALKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>CostumeSakuraName</t>
+        </is>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>벚꽃 검사</t>
+        </is>
+      </c>
+      <c r="C2203" t="inlineStr">
+        <is>
+          <t>BLOSSOM BLADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>CostumeGoldName</t>
+        </is>
+      </c>
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>황금 영웅</t>
+        </is>
+      </c>
+      <c r="C2204" t="inlineStr">
+        <is>
+          <t>GOLDEN HERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>CostumeAbyssName</t>
+        </is>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>심연 순례자</t>
+        </is>
+      </c>
+      <c r="C2205" t="inlineStr">
+        <is>
+          <t>ABYSS PILGRIM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2205"/>
+  <dimension ref="A1:C2207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40020,6 +40020,40 @@
         </is>
       </c>
     </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>AdNotReadyText</t>
+        </is>
+      </c>
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>광고를 불러오는 중입니다. 잠시 후 다시 눌러 주세요</t>
+        </is>
+      </c>
+      <c r="C2206" t="inlineStr">
+        <is>
+          <t>AD IS LOADING. TRY AGAIN IN A MOMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>AdPrivacyText</t>
+        </is>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>광고 개인정보 설정</t>
+        </is>
+      </c>
+      <c r="C2207" t="inlineStr">
+        <is>
+          <t>AD PRIVACY SETTINGS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2207"/>
+  <dimension ref="A1:C2211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40054,6 +40054,74 @@
         </is>
       </c>
     </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>RelicSummonTitleText</t>
+        </is>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>유물 소환</t>
+        </is>
+      </c>
+      <c r="C2208" t="inlineStr">
+        <is>
+          <t>RELIC SUMMON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>RelicSummonPityFormat</t>
+        </is>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>전설 확정까지 {0}회</t>
+        </is>
+      </c>
+      <c r="C2209" t="inlineStr">
+        <is>
+          <t>LEGENDARY GUARANTEED IN {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>RelicSummonRefundFormat</t>
+        </is>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>최대 레벨 유물 → 크리스탈 {0} 돌려받음</t>
+        </is>
+      </c>
+      <c r="C2210" t="inlineStr">
+        <is>
+          <t>MAXED RELICS → {0} CRYSTALS BACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>RelicSummonAgainFormat</t>
+        </is>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>{0}회 더 ({1})</t>
+        </is>
+      </c>
+      <c r="C2211" t="inlineStr">
+        <is>
+          <t>x{0} AGAIN ({1})</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/LocalizationData.xlsx
+++ b/Assets/@Resources/Data/Excel/LocalizationData.xlsx
@@ -328,7 +328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2211"/>
+  <dimension ref="A1:C2221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40122,6 +40122,176 @@
         </is>
       </c>
     </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>SettingPopupPlaytestText</t>
+        </is>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>플레이 기록</t>
+        </is>
+      </c>
+      <c r="C2212" t="inlineStr">
+        <is>
+          <t>PLAY LOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>PlaytestTitleText</t>
+        </is>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>플레이 기록</t>
+        </is>
+      </c>
+      <c r="C2213" t="inlineStr">
+        <is>
+          <t>PLAY LOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>PlaytestCopiedText</t>
+        </is>
+      </c>
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>플레이 기록을 복사했다 — 설문지에 붙여 넣어 주세요</t>
+        </is>
+      </c>
+      <c r="C2214" t="inlineStr">
+        <is>
+          <t>PLAY LOG COPIED — PASTE IT INTO THE SURVEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>PlaytestTimeFormat</t>
+        </is>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>{0}시간 {1}분</t>
+        </is>
+      </c>
+      <c r="C2215" t="inlineStr">
+        <is>
+          <t>{0}h {1}m</t>
+        </is>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>PlaytestTotalFormat</t>
+        </is>
+      </c>
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>총 플레이 {0} · 접속 {1}회 · 한 번에 평균 {2}</t>
+        </is>
+      </c>
+      <c r="C2216" t="inlineStr">
+        <is>
+          <t>PLAYED {0} · {1} SESSIONS · AVG {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>PlaytestLevelFormat</t>
+        </is>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>Lv{0} {1}</t>
+        </is>
+      </c>
+      <c r="C2217" t="inlineStr">
+        <is>
+          <t>LV{0} AT {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>PlaytestStageFormat</t>
+        </is>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>스테이지 {0}곳 돌파(마지막 {1}) · 보스 실패 {2}회 · 쓰러짐 {3}회</t>
+        </is>
+      </c>
+      <c r="C2218" t="inlineStr">
+        <is>
+          <t>{0} STAGES CLEARED (LAST {1}) · BOSS FAILS {2} · DEATHS {3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>PlaytestHardestFormat</t>
+        </is>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>가장 막힌 곳: {0}</t>
+        </is>
+      </c>
+      <c r="C2219" t="inlineStr">
+        <is>
+          <t>TOUGHEST: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>PlaytestEconomyFormat</t>
+        </is>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>광고 {0}회 · 유물 소환 {1}회 · 구매(테스트) {2}회</t>
+        </is>
+      </c>
+      <c r="C2220" t="inlineStr">
+        <is>
+          <t>ADS {0} · SUMMONS {1} · PURCHASES (TEST) {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>PlaytestRecentText</t>
+        </is>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>최근 기록</t>
+        </is>
+      </c>
+      <c r="C2221" t="inlineStr">
+        <is>
+          <t>RECENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
